--- a/pepline/result/Book4.xlsx
+++ b/pepline/result/Book4.xlsx
@@ -3,29 +3,35 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="4460" yWindow="3660" windowWidth="54640" windowHeight="24580" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="11520" yWindow="500" windowWidth="42240" windowHeight="26780" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4+" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4+_greedy" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4+_deconv_greedy" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="greedy_annot" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="12"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <b val="1"/>
+      <sz val="12"/>
     </font>
     <font>
       <name val="Aptos Narrow"/>
@@ -44,12 +50,27 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -77,12 +98,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -2560,7 +2584,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:W53"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="32.83203125" defaultRowHeight="16"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
@@ -5425,107 +5449,2538 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>N=1000</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>All Coverage=84.8%</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>isocolumn:-114.07</t>
         </is>
       </c>
-      <c r="E1" s="2" t="n">
+      <c r="E1" s="3" t="n">
         <v>-114.07</v>
       </c>
-      <c r="F1" s="2" t="n">
+      <c r="F1" s="3" t="n">
         <v>-113.07</v>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>parent(0.002388)</t>
         </is>
       </c>
-      <c r="H1" s="2" t="n">
+      <c r="H1" s="3" t="n">
         <v>-1965.95</v>
       </c>
-      <c r="I1" s="2" t="n">
+      <c r="I1" s="3" t="n">
         <v>-1872.39</v>
       </c>
-      <c r="J1" s="2" t="n">
+      <c r="J1" s="3" t="n">
         <v>-1567.19</v>
       </c>
-      <c r="K1" s="2" t="n">
+      <c r="K1" s="3" t="n">
         <v>-1284.48</v>
       </c>
-      <c r="L1" s="2" t="n">
+      <c r="L1" s="3" t="n">
         <v>-1256.5</v>
       </c>
-      <c r="M1" s="2" t="n">
+      <c r="M1" s="3" t="n">
         <v>-1162.48</v>
       </c>
-      <c r="N1" s="2" t="n">
+      <c r="N1" s="3" t="n">
         <v>-879.76</v>
       </c>
-      <c r="O1" s="2" t="n">
+      <c r="O1" s="3" t="n">
         <v>-597.05</v>
       </c>
-      <c r="P1" s="2" t="n">
+      <c r="P1" s="3" t="n">
         <v>-534.17</v>
       </c>
-      <c r="Q1" s="2" t="n">
+      <c r="Q1" s="3" t="n">
         <v>-348.16</v>
       </c>
-      <c r="R1" s="2" t="n">
+      <c r="R1" s="3" t="n">
         <v>-157.23</v>
       </c>
-      <c r="S1" s="2" t="n">
+      <c r="S1" s="3" t="n">
         <v>-137.27</v>
       </c>
-      <c r="T1" s="2" t="n">
+      <c r="T1" s="3" t="n">
         <v>-131.02</v>
       </c>
-      <c r="U1" s="2" t="n">
+      <c r="U1" s="3" t="n">
         <v>-118.01</v>
       </c>
-      <c r="V1" s="2" t="n">
+      <c r="V1" s="3" t="n">
         <v>-27.98</v>
       </c>
-      <c r="W1" s="2" t="n">
+      <c r="W1" s="3" t="n">
         <v>-17.99</v>
       </c>
-      <c r="X1" s="2" t="n">
+      <c r="X1" s="3" t="n">
         <v>310.9</v>
       </c>
-      <c r="Y1" s="2" t="n">
+      <c r="Y1" s="3" t="n">
         <v>351.42</v>
       </c>
-      <c r="Z1" s="2" t="n">
+      <c r="Z1" s="3" t="n">
         <v>415.96</v>
       </c>
-      <c r="AA1" s="2" t="inlineStr">
+      <c r="AA1" s="3" t="inlineStr">
         <is>
           <t>Row Count</t>
         </is>
       </c>
-      <c r="AB1" s="2" t="inlineStr">
+      <c r="AB1" s="3" t="inlineStr">
         <is>
           <t>theoretical mass</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>b1, y32</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>(138.066, 3627.763)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>b2, y31</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0, 0, [1, 3], (0.001, 0.022), [167]</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>+6, (0)-137.04, [1, 3], (0.017, 0.009), [148] ('used')</t>
+        </is>
+      </c>
+      <c r="AA3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>(209.103, 3556.726)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>b3, y30</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>(324.13, 3441.699)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>b4, y29</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>(381.152, 3384.678)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>b5, y28</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>+3, (0)-350.167, [1, 2], (0.102, 0.092), [94] ('used')</t>
+        </is>
+      </c>
+      <c r="AA6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>(468.184, 3297.646)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>b6, y27</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>(615.252, 3150.578)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>b7, y26</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>(3, 0)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>+3, (0)-116.08, [1, 3], (0.088, 0.083), [171] ('used')</t>
+        </is>
+      </c>
+      <c r="AA8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>(702.284, 3063.545)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>b8, y25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>(1, 0)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>+1, (0)-114.07, [1, 2], (0.152, 0.147), [824] ('used')</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>+1, (0)-114.073, [1, 3], (0.152, 0.147), [114] ('used')</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>0, (0)-157.23, [1, 3], (0.037, 0.4), [496]</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>+1, (0)-28.983, [1, 3], (0.152, 0.148), [427] ('used')</t>
+        </is>
+      </c>
+      <c r="AA9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>(817.311, 2948.519)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>b9, y24</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0, 0, [2, 2], (0.004, 0.016), [216]</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>0, (0)-131.02, [2, 2], (0.004, 0.003), [229] ('used')</t>
+        </is>
+      </c>
+      <c r="AA10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>(946.354, 2819.476)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>b10, y23</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0, 0, [2, 2], (0.005, 0.017), [93]</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>+5, (0)-1261.517, [1, 3], (0.112, 0.112), [201]</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>(0)-160.24, +3, [1, 3], (0.348, 0.343), [414] ('used')</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>(0)-140.28, +3, [1, 3], (0.349, 0.343), [663] ('used')</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>(0)-131.02, 0, [2, 2], (0.016, 0.017), [229] ('used')</t>
+        </is>
+      </c>
+      <c r="AA11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>(1077.394, 2688.435)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>b11, y22</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0, 0, [2, 2], (0.005, 0.014), [80]</t>
+        </is>
+      </c>
+      <c r="AA12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>(1191.437, 2574.393)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>b12, y21</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>(0, 0)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0, (+1)-114.07, [1, 2], (0.009, 0.004), [890] ('used')</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0, (0)-113.07, [2, 2], (0.006, 0.0), [610] ('used')</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0, 0, [2, 2], (0.006, 0.014), [11]</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>(+1)-879.76, 0, [1, 2], (0.488, 0.015), [693]</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>0, (+1)-348.16, [1, 2], (0.009, 0.168), [733]</t>
+        </is>
+      </c>
+      <c r="AA13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>(1292.485, 2473.345)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>b13, y20</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>(0, 0)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>(+1)-114.07, 0, [1, 2], (0.009, 0.014), [890] ('used')</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>(0)-113.07, 0, [2, 2], (0.008, 0.014), [610] ('used')</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0, 0, [2, 2], (0.006, 0.014), [17]</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>+6, (0)-885.78, [3, 1], (0.281, 0.283), [94] ('used')</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>(0)-131.02, 0, [2, 2], (0.069, 0.014), [550]</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>(0)-27.98, 0, [2, 2], (0.009, 0.014), [886]</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>(0)-17.99, 0, [2, 2], (0.014, 0.014), [51]</t>
+        </is>
+      </c>
+      <c r="AA14" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>(1405.569, 2360.261)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>b14, y19</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>(0, 0)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>(0)-113.07, 0, [2, 2], (0.008, 0.013), [820] ('used')</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0, 0, [2, 2], (0.007, 0.012), [19]</t>
+        </is>
+      </c>
+      <c r="AA15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>(1518.653, 2247.177)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>b15, y18</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0, 0, [2, 2], (0.008, 0.011), [135]</t>
+        </is>
+      </c>
+      <c r="AA16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>(1633.68, 2132.15)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>b16, y17</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>+3, (0)-600.06, [3, 1], (0.392, 0.392), [122] ('used')</t>
+        </is>
+      </c>
+      <c r="AA17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>(1747.723, 2018.107)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>b17, y16</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0, 0, [2, 2], (0.009, 0.01), [42]</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>+1, (0)-138.273, [2, 2], (0.285, 0.342), [637] ('used')</t>
+        </is>
+      </c>
+      <c r="AA18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>(1860.807, 1905.023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>b18, y15</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>(0, 0)</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>(0)-113.07, 0, [2, 2], (0.364, 0.01), [508]</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0, 0, [2, 2], (0.01, 0.01), [49]</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>(0)-137.27, 0, [2, 2], (0.17, 0.01), [414] ('used')</t>
+        </is>
+      </c>
+      <c r="AA19" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>(1931.844, 1833.986)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>b19, y14</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>(0, 4)</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>(0)-118.083, +4, [2, 2], (0.37, 0.079), [802]</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>0, 0, [2, 2], (0.01, 0.009), [78]</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>(0)-141.283, +3, [2, 2], (0.498, 0.449), [637] ('used')</t>
+        </is>
+      </c>
+      <c r="AA20" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>(2002.881, 1762.949)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>b20, y13</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0, 0, [2, 2], (0.012, 0.007), [226]</t>
+        </is>
+      </c>
+      <c r="AA21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>(2158.982, 1606.847)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>b21, y12</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>(5, 0)</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>+5, (0)-118.087, [2, 2], (0.427, 0.001), [639]</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>0, 0, [2, 2], (0.012, 0.007), [236]</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>+3, (0)-352.173, [3, 1], (0.467, 0.249), [774]</t>
+        </is>
+      </c>
+      <c r="AA22" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>(2274.009, 1491.821)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>b22, y11</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>(0, 0)</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0, (+1)-114.07, [2, 1], (0.013, 0.01), [232] ('used')</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>0, (0)-113.07, [3, 1], (0.01, 0.007), [373] ('used')</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>0, 0, [2, 2], (0.013, 0.006), [164]</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>0, (+1)-348.16, [2, 1], (0.013, 0.006), [789]</t>
+        </is>
+      </c>
+      <c r="AA23" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>(2421.077, 1344.752)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>b23, y10</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>(0, 0)</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>(+1)-114.07, 0, [2, 1], (0.004, 0.007), [232] ('used')</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>(0)-113.07, 0, [3, 1], (0.004, 0.007), [373] ('used')</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>0, 0, [2, 2], (0.015, 0.005), [25]</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>0, (+1)-348.16, [2, 1], (0.016, 0.007), [450]</t>
+        </is>
+      </c>
+      <c r="AA24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>(2534.162, 1231.668)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>b24, y9</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>0, 0, [2, 2], (0.016, 0.005), [54]</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>(0)-540.19, +6, [3, 1], (0.156, 0.453), [820] ('used')</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>0, (+1)-348.16, [2, 1], (0.016, 0.009), [372]</t>
+        </is>
+      </c>
+      <c r="AA25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>(2648.204, 1117.625)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>b25, y8</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>(0, 0)</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>0, (+1)-114.07, [2, 1], (0.018, 0.013), [824] ('used')</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>0, (0)-113.07, [3, 1], (0.014, 0.009), [114] ('used')</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>0, 0, [3, 1], (0.014, 0.006), [27]</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>0, (+1)-348.16, [2, 1], (0.018, 0.009), [122] ('used')</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>(0)-143.29, +6, [3, 1], (0.109, 0.103), [663] ('used')</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>(0)-27.98, 0, [3, 1], (0.003, 0.006), [162]</t>
+        </is>
+      </c>
+      <c r="AA26" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>(2834.284, 931.546)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>b26, y7</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>(0, 0)</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>(+1)-114.07, 0, [2, 1], (0.001, 0.005), [824] ('used')</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>(0)-113.07, 0, [3, 1], (0.0, 0.005), [114] ('used')</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>0, 0, [3, 1], (0.014, 0.005), [6]</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>0, (+1)-348.16, [2, 1], (0.019, 0.01), [94] ('used')</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>(0)-27.98, 0, [3, 1], (0.001, 0.005), [427] ('used')</t>
+        </is>
+      </c>
+      <c r="AA27" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>(2947.368, 818.462)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>b27, y6</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>(0, 0)</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>(0)-113.07, 0, [3, 1], (0.0, 0.004), [171] ('used')</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>0, 0, [3, 1], (0.015, 0.004), [4]</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>0, (+1)-348.16, [2, 1], (0.02, 0.011), [16] ('used')</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>0, (0)-17.99, [3, 1], (0.015, 0.016), [960]</t>
+        </is>
+      </c>
+      <c r="AA28" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>(3060.452, 705.378)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>b28, y5</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>0, 0, [3, 1], (0.016, 0.003), [15]</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>0, (+1)-348.16, [2, 1], (0.019, 0.011), [21] ('used')</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>+2, (0)-133.027, [3, 1], (0.015, 0.008), [642]</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>0, (0)-118.01, [2, 2], (0.019, 0.015), [21] ('used')</t>
+        </is>
+      </c>
+      <c r="AA29" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>(3188.511, 577.319)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>b29, y4</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>0, 0, [3, 1], (0.017, 0.003), [1]</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>(0)-17.99, 0, [3, 1], (0.008, 0.003), [260]</t>
+        </is>
+      </c>
+      <c r="AA30" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>(3289.558, 476.271)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>b30, y3</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>0, 0, [3, 1], (0.018, 0.002), [7]</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>+2, (0)-133.027, [3, 1], (0.018, 0.01), [148] ('used')</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>(0)-17.99, 0, [3, 1], (0.007, 0.002), [729]</t>
+        </is>
+      </c>
+      <c r="AA31" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>(3417.653, 348.176)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>b31, y2</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>0, 0, [3, 1], (0.018, 0.001), [8]</t>
+        </is>
+      </c>
+      <c r="AA32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>(3530.737, 235.092)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>b32, y1</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>(3631.785, 134.045)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Col Count</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>8</v>
+      </c>
+      <c r="F34" t="n">
+        <v>12</v>
+      </c>
+      <c r="G34" t="n">
+        <v>23</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>2</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1</v>
+      </c>
+      <c r="P34" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>10</v>
+      </c>
+      <c r="R34" t="n">
+        <v>2</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="n">
+        <v>6</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
+      </c>
+      <c r="V34" t="n">
+        <v>4</v>
+      </c>
+      <c r="W34" t="n">
+        <v>4</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>32</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>FFC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>7</v>
+      </c>
+      <c r="F35" t="n">
+        <v>16</v>
+      </c>
+      <c r="G35" t="n">
+        <v>241</v>
+      </c>
+      <c r="H35" t="n">
+        <v>4</v>
+      </c>
+      <c r="I35" t="n">
+        <v>4</v>
+      </c>
+      <c r="J35" t="n">
+        <v>4</v>
+      </c>
+      <c r="K35" t="n">
+        <v>4</v>
+      </c>
+      <c r="L35" t="n">
+        <v>3</v>
+      </c>
+      <c r="M35" t="n">
+        <v>9</v>
+      </c>
+      <c r="N35" t="n">
+        <v>5</v>
+      </c>
+      <c r="O35" t="n">
+        <v>3</v>
+      </c>
+      <c r="P35" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>27</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6</v>
+      </c>
+      <c r="S35" t="n">
+        <v>8</v>
+      </c>
+      <c r="T35" t="n">
+        <v>9</v>
+      </c>
+      <c r="U35" t="n">
+        <v>8</v>
+      </c>
+      <c r="V35" t="n">
+        <v>17</v>
+      </c>
+      <c r="W35" t="n">
+        <v>22</v>
+      </c>
+      <c r="X35" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>FPR0</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>4</v>
+      </c>
+      <c r="J36" t="n">
+        <v>4</v>
+      </c>
+      <c r="K36" t="n">
+        <v>4</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>1</v>
+      </c>
+      <c r="R36" t="n">
+        <v>2</v>
+      </c>
+      <c r="S36" t="n">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>4</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1</v>
+      </c>
+      <c r="X36" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>FPR1</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>24</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>16</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
+        <v>60</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>offset</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>y3</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>y1-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>FPR0_LIST_1</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>(884.504157, 923.203482, [1, 3], 864)</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>(890.456401, 983.46699, [3, 1], 888)</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>(937.4631905, 946.440642, [2, 2], 541)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>(228.13543, 1211.0494195, [3, 1], 254)</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>(242.151227, 1474.1978175, [3, 1], 365)</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>(355.235876, 1417.654872, [3, 1], 87)</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>(850.669374, 904.4531745, [2, 1], 577)</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>(655.359824, 1267.5925285, [3, 1], 119)</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>(850.669374, 856.175188, [1, 3], 474)</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>(883.456071, 908.957161, [1, 3], 405)</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>(904.4531745, 917.5019565, [3, 1], 579)</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>(897.70609, 917.5019565, [1, 3], 414)</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>(909.458425, 1021.844329, [3, 1], 623)</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>(807.7011133333333, 1231.67548, [2, 2], 373)</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>(931.551515, 1324.6143855, [3, 1], 246)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>FPR0_LIST_2</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>(228.13543, 1211.0494195, [3, 1], 290)</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>(242.151227, 1474.1978175, [3, 1], 536)</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>(355.235876, 1417.654872, [3, 1], 103)</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>(655.359824, 1267.5925285, [3, 1], 182)</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>(900.952596, 904.4531745, [2, 2], 659)</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>(897.70609, 927.209388, [2, 2], 426)</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>(941.171129, 1098.199865, [2, 2], 607)</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>(931.551515, 1324.6143855, [3, 1], 263)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>FPR0_LIST_3</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>(228.13543, 1211.0494195, [3, 1], 403)</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>(242.151227, 1474.1978175, [3, 1], 806)</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>(355.235876, 1417.654872, [3, 1], 174)</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>(655.359824, 1267.5925285, [3, 1], 327)</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>(897.70609, 917.5019565, [1, 3], 764)</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>(807.701273, 1231.675462, [2, 2], 731)</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>(931.551515, 1324.6143855, [3, 1], 265)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>TFPR0_LIST_1</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>(884.5042, 2769.6104, 3654.1146)</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>(2671.3692, 983.467, 3654.8362)</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>(1874.9264, 1892.8813, 3767.8077)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>(684.4063, 1211.0494, 1895.4557)</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>(726.4537, 1474.1978, 2200.6515)</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>(1065.7076, 1417.6549, 2483.3625)</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>(1701.3387, 904.4532, 2605.7919)</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>(1966.0795, 1267.5925, 3233.672)</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>(850.6694, 2568.5256, 3419.1949)</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>(883.4561, 2726.8715, 3610.3276)</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>(2713.3595, 917.502, 3630.8615)</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>(897.7061, 2752.5059, 3650.212)</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>(2728.3753, 1021.8443, 3750.2196)</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>(1615.4022, 2463.351, 4078.7532)</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>(2794.6545, 1324.6144, 4119.2689)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>TFPR0_LIST_2</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>(684.4063, 1211.0494, 1895.4557)</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>(726.4537, 1474.1978, 2200.6515)</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>(1065.7076, 1417.6549, 2483.3625)</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>(1966.0795, 1267.5925, 3233.672)</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>(1801.9052, 1808.9063, 3610.8115)</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>(1795.4122, 1854.4188, 3649.831)</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>(1882.3423, 2196.3997, 4078.742)</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>(2794.6545, 1324.6144, 4119.2689)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>TFPR0_LIST_3</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>(684.4063, 1211.0494, 1895.4557)</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>(726.4537, 1474.1978, 2200.6515)</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>(1065.7076, 1417.6549, 2483.3625)</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>(1966.0795, 1267.5925, 3233.672)</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>(897.7061, 2752.5059, 3650.212)</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>(1615.4025, 2463.3509, 4078.7535)</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>(2794.6545, 1324.6144, 4119.2689)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>FPR1_LIST_1</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(+1)-1965.95, ???, [1, 3], (0.003, 'n/a'), [14]| ('used')</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>???, (+5)-1162.48, [3, 1], ('n/a', 0.233), [16]| ('used')</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>FPR1_LIST_2</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(+3)-1967.957, ???, [1, 3], (0.003, 'n/a'), [14]| ('used')</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>???, (+6)-1163.483, [3, 1], ('n/a', 0.233), [16]| ('used')</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>FPR1_LIST_3</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(+6)-1970.967, ???, [1, 3], (0.003, 'n/a'), [14]| ('used')</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>???, (+6)-1163.483, [3, 1], ('n/a', 0.233), [23]|</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>TFPR1_LIST_1</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(477.2775, 1324.6144, 1801.8919)</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>(1074.6314, 1530.7397, 2605.3711)</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>(2794.6544, 945.4378, 3740.0923)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>TFPR1_LIST_2</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(477.2775, 1324.6144, 1801.8919)</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>(1074.6314, 1530.7397, 2605.3711)</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>(2794.6544, 945.4378, 3740.0923)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>TFPR1_LIST_3</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(477.2775, 1324.6144, 1801.8919)</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>(1074.6314, 1530.7397, 2605.3711)</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>(2794.6544, 945.4378, 3740.0923)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>Modifications_Count</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>0</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" t="n">
+        <v>7</v>
+      </c>
+      <c r="F51" t="n">
+        <v>10</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>3</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
+        <v>2</v>
+      </c>
+      <c r="N51" t="n">
+        <v>1</v>
+      </c>
+      <c r="O51" t="n">
+        <v>1</v>
+      </c>
+      <c r="P51" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>5</v>
+      </c>
+      <c r="R51" t="n">
+        <v>1</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="n">
+        <v>4</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
+      </c>
+      <c r="V51" t="n">
+        <v>5</v>
+      </c>
+      <c r="W51" t="n">
+        <v>0</v>
+      </c>
+      <c r="X51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>|SIM(A*,B)|</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>7</v>
+      </c>
+      <c r="F52" t="n">
+        <v>10</v>
+      </c>
+      <c r="G52" t="n">
+        <v>23</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" t="n">
+        <v>1</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" t="n">
+        <v>2</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>9</v>
+      </c>
+      <c r="R52" t="n">
+        <v>1</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="n">
+        <v>6</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
+      </c>
+      <c r="V52" t="n">
+        <v>3</v>
+      </c>
+      <c r="W52" t="n">
+        <v>4</v>
+      </c>
+      <c r="X52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>|DIFF(A*,B)|</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>1</v>
+      </c>
+      <c r="F53" t="n">
+        <v>2</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" t="n">
+        <v>1</v>
+      </c>
+      <c r="P53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>1</v>
+      </c>
+      <c r="R53" t="n">
+        <v>1</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
+      </c>
+      <c r="V53" t="n">
+        <v>1</v>
+      </c>
+      <c r="W53" t="n">
+        <v>0</v>
+      </c>
+      <c r="X53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AA49"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Bond</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Coverage=72.7%</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>(2,2) +1.02</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>(2,2) +2.03</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>(2,2) +0.02</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>(1,3) +1.02</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>(1,3) +2.03</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>(1,3) +0.02</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>(1,2) -347.15</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>(3,1) +1.02</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>(1,3) -112.06</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>(3,1) +2.02</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>(1,3) -13.99</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>(2,2) -15.99</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>(1,3) -110.05</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>(1,2) -346.15</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>(2,2) -14.99</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>(1,3) +3.03</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
+          <t>(2,2) +4.03</t>
+        </is>
+      </c>
+      <c r="U1" s="3" t="inlineStr">
+        <is>
+          <t>(2,2) +3.03</t>
+        </is>
+      </c>
+      <c r="V1" s="3" t="inlineStr">
+        <is>
+          <t>(3,1) +3.03</t>
+        </is>
+      </c>
+      <c r="W1" s="3" t="inlineStr">
+        <is>
+          <t>(1,3) -130.01</t>
+        </is>
+      </c>
+      <c r="X1" s="3" t="inlineStr">
+        <is>
+          <t>(1,3) +4.03</t>
+        </is>
+      </c>
+      <c r="Y1" s="3" t="inlineStr">
+        <is>
+          <t>(1,2) -345.15</t>
+        </is>
+      </c>
+      <c r="Z1" s="3" t="inlineStr">
+        <is>
+          <t>Row Count</t>
+        </is>
+      </c>
+      <c r="AA1" s="3" t="inlineStr">
+        <is>
+          <t>theoretical mass</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>b1, y32</t>
         </is>
@@ -5562,18 +8017,17 @@
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB2" t="inlineStr">
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="inlineStr">
         <is>
           <t>(138.066, 3627.763)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>b2, y31</t>
         </is>
@@ -5593,7 +8047,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0, 0, [1, 3], (0.001, 0.022), [167]</t>
+          <t>0, +1, [1, 3], (0.001, 0.018), [244]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
@@ -5608,28 +8062,23 @@
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>+6, (0)-137.04, [1, 3], (0.017, 0.009), [148] ('used')</t>
-        </is>
-      </c>
+      <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="Z3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA3" t="inlineStr">
         <is>
           <t>(209.103, 3556.726)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>b3, y30</t>
         </is>
@@ -5666,18 +8115,17 @@
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" t="inlineStr">
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="inlineStr">
         <is>
           <t>(324.13, 3441.699)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>b4, y29</t>
         </is>
@@ -5714,18 +8162,17 @@
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB5" t="inlineStr">
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="inlineStr">
         <is>
           <t>(381.152, 3384.678)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>b5, y28</t>
         </is>
@@ -5737,7 +8184,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -5753,11 +8200,7 @@
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>+3, (0)-350.167, [1, 2], (0.102, 0.092), [94] ('used')</t>
-        </is>
-      </c>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
@@ -5766,18 +8209,17 @@
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB6" t="inlineStr">
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="inlineStr">
         <is>
           <t>(468.184, 3297.646)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>b6, y27</t>
         </is>
@@ -5814,18 +8256,17 @@
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB7" t="inlineStr">
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="inlineStr">
         <is>
           <t>(615.252, 3150.578)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>b7, y26</t>
         </is>
@@ -5837,20 +8278,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>(3, 0)</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>+3, (0)-116.08, [1, 3], (0.088, 0.083), [171] ('used')</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
@@ -5870,18 +8303,17 @@
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB8" t="inlineStr">
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="inlineStr">
         <is>
           <t>(702.284, 3063.545)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>b8, y25</t>
         </is>
@@ -5893,24 +8325,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>(1, 0)</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>+1, (0)-114.07, [1, 2], (0.152, 0.147), [824] ('used')</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>+1, (0)-114.073, [1, 3], (0.152, 0.147), [114] ('used')</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
@@ -5922,34 +8342,25 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>0, (0)-157.23, [1, 3], (0.037, 0.4), [496]</t>
-        </is>
-      </c>
+      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>+1, (0)-28.983, [1, 3], (0.152, 0.148), [427] ('used')</t>
-        </is>
-      </c>
+      <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB9" t="inlineStr">
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="inlineStr">
         <is>
           <t>(817.311, 2948.519)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>b9, y24</t>
         </is>
@@ -5964,14 +8375,18 @@
           <t>+</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>0, +1, [2, 2], (0.004, 0.017), [216]</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>+1, +1, [2, 2], (0.003, 0.017), [447]</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0, 0, [2, 2], (0.004, 0.016), [216]</t>
-        </is>
-      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
@@ -5984,28 +8399,23 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>0, (0)-131.02, [2, 2], (0.004, 0.003), [229] ('used')</t>
-        </is>
-      </c>
+      <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="n">
+      <c r="Z10" t="n">
         <v>2</v>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>(946.354, 2819.476)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>b10, y23</t>
         </is>
@@ -6020,60 +8430,59 @@
           <t>+</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0, 0, [2, 2], (0.005, 0.017), [93]</t>
-        </is>
-      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>+1, 0, [2, 2], (0.005, 0.017), [295]</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>+1, +1, [2, 2], (0.005, 0.017), [115]</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0, 0, [2, 2], (0.005, 0.017), [212]</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>+5, (0)-1261.517, [1, 3], (0.112, 0.112), [201]</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0, +1, [1, 3], (0.006, 0.013), [361]</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>+1, +1, [1, 3], (0.006, 0.013), [399]</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>(0)-160.24, +3, [1, 3], (0.348, 0.343), [414] ('used')</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>(0)-140.28, +3, [1, 3], (0.349, 0.343), [663] ('used')</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>(0)-131.02, 0, [2, 2], (0.016, 0.017), [229] ('used')</t>
-        </is>
-      </c>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="n">
+      <c r="Z11" t="n">
         <v>5</v>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>(1077.394, 2688.435)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>b11, y22</t>
         </is>
@@ -6088,14 +8497,22 @@
           <t>+</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0, 0, [2, 2], (0.005, 0.014), [80]</t>
-        </is>
-      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>0, +1, [2, 2], (0.005, 0.014), [80]</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>+1, +1, [2, 2], (0.005, 0.014), [184]</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>0, 0, [2, 2], (0.005, 0.016), [901]</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
@@ -6114,18 +8531,17 @@
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr"/>
       <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
-      <c r="AA12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB12" t="inlineStr">
+      <c r="Z12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA12" t="inlineStr">
         <is>
           <t>(1191.437, 2574.393)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>b12, y21</t>
         </is>
@@ -6142,42 +8558,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>(0, 0)</t>
+          <t>+1, 0, [2, 2], (0.006, 0.014), [110]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0, (+1)-114.07, [1, 2], (0.009, 0.004), [890] ('used')</t>
+          <t>+1, +1, [2, 2], (0.006, 0.014), [56]</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0, (0)-113.07, [2, 2], (0.006, 0.0), [610] ('used')</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>0, 0, [2, 2], (0.006, 0.014), [11]</t>
-        </is>
-      </c>
+          <t>0, 0, [2, 2], (0.006, 0.014), [314]</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>(+1)-879.76, 0, [1, 2], (0.488, 0.015), [693]</t>
-        </is>
-      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>0, (+1)-348.16, [1, 2], (0.009, 0.168), [733]</t>
-        </is>
-      </c>
+      <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
@@ -6186,18 +8590,17 @@
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr"/>
       <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
-      <c r="AA13" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB13" t="inlineStr">
+      <c r="Z13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA13" t="inlineStr">
         <is>
           <t>(1292.485, 2473.345)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>b13, y20</t>
         </is>
@@ -6214,70 +8617,57 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>(0, 0)</t>
+          <t>0, +1, [2, 2], (0.006, 0.014), [58]</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>(+1)-114.07, 0, [1, 2], (0.009, 0.014), [890] ('used')</t>
+          <t>+1, +1, [2, 2], (0.006, 0.014), [17]</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>(0)-113.07, 0, [2, 2], (0.008, 0.014), [610] ('used')</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>0, 0, [2, 2], (0.006, 0.014), [17]</t>
-        </is>
-      </c>
+          <t>0, 0, [2, 2], (0.006, 0.014), [230]</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>+6, (0)-885.78, [3, 1], (0.281, 0.283), [94] ('used')</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>(0)-15.986, 0, [2, 2], (0.015, 0.014), [157]</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>(0)-14.985, 0, [2, 2], (0.017, 0.014), [134]</t>
+        </is>
+      </c>
       <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>(0)-131.02, 0, [2, 2], (0.069, 0.014), [550]</t>
-        </is>
-      </c>
+      <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>(0)-27.98, 0, [2, 2], (0.009, 0.014), [886]</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>(0)-17.99, 0, [2, 2], (0.014, 0.014), [51]</t>
-        </is>
-      </c>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr"/>
       <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
-      <c r="AA14" t="n">
-        <v>7</v>
-      </c>
-      <c r="AB14" t="inlineStr">
+      <c r="Z14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA14" t="inlineStr">
         <is>
           <t>(1405.569, 2360.261)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>b14, y19</t>
         </is>
@@ -6294,20 +8684,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>(0, 0)</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
+          <t>0, +1, [2, 2], (0.007, 0.012), [20]</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>+1, +1, [2, 2], (0.006, 0.012), [19]</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>(0)-113.07, 0, [2, 2], (0.008, 0.013), [820] ('used')</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>0, 0, [2, 2], (0.007, 0.012), [19]</t>
-        </is>
-      </c>
+          <t>0, 0, [2, 2], (0.007, 0.013), [297]</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
@@ -6315,7 +8705,11 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>(0)-16.99, +1, [2, 2], (0.011, 0.012), [367]</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
@@ -6326,18 +8720,17 @@
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr"/>
       <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr"/>
-      <c r="AA15" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB15" t="inlineStr">
+      <c r="Z15" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA15" t="inlineStr">
         <is>
           <t>(1518.653, 2247.177)</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>b15, y18</t>
         </is>
@@ -6352,14 +8745,18 @@
           <t>+</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>0, +1, [2, 2], (0.008, 0.011), [135]</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>+1, +1, [2, 2], (0.007, 0.011), [136]</t>
+        </is>
+      </c>
       <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>0, 0, [2, 2], (0.008, 0.011), [135]</t>
-        </is>
-      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
@@ -6378,18 +8775,17 @@
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr"/>
       <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr"/>
-      <c r="AA16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB16" t="inlineStr">
+      <c r="Z16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA16" t="inlineStr">
         <is>
           <t>(1633.68, 2132.15)</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>b16, y17</t>
         </is>
@@ -6401,7 +8797,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -6415,11 +8811,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>+3, (0)-600.06, [3, 1], (0.392, 0.392), [122] ('used')</t>
-        </is>
-      </c>
+      <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
@@ -6430,18 +8822,17 @@
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr"/>
       <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr"/>
-      <c r="AA17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB17" t="inlineStr">
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="inlineStr">
         <is>
           <t>(1747.723, 2018.107)</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>b17, y16</t>
         </is>
@@ -6456,14 +8847,22 @@
           <t>+</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>0, 0, [2, 2], (0.009, 0.01), [42]</t>
-        </is>
-      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>0, +1, [2, 2], (0.009, 0.01), [53]</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>+1, +1, [2, 2], (0.009, 0.01), [42]</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>0, 0, [2, 2], (0.009, 0.01), [68]</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
@@ -6475,29 +8874,24 @@
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>+1, (0)-138.273, [2, 2], (0.285, 0.342), [637] ('used')</t>
-        </is>
-      </c>
+      <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr"/>
       <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
-      <c r="AA18" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB18" t="inlineStr">
+      <c r="Z18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA18" t="inlineStr">
         <is>
           <t>(1860.807, 1905.023)</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>b18, y15</t>
         </is>
@@ -6514,20 +8908,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>(0, 0)</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr"/>
+          <t>+1, 0, [2, 2], (0.01, 0.01), [79]</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>+1, +1, [2, 2], (0.01, 0.01), [49]</t>
+        </is>
+      </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>(0)-113.07, 0, [2, 2], (0.364, 0.01), [508]</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>0, 0, [2, 2], (0.01, 0.01), [49]</t>
-        </is>
-      </c>
+          <t>0, 0, [2, 2], (0.01, 0.01), [237]</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
@@ -6539,29 +8933,24 @@
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>(0)-137.27, 0, [2, 2], (0.17, 0.01), [414] ('used')</t>
-        </is>
-      </c>
+      <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr"/>
       <c r="Y19" t="inlineStr"/>
-      <c r="Z19" t="inlineStr"/>
-      <c r="AA19" t="n">
+      <c r="Z19" t="n">
         <v>3</v>
       </c>
-      <c r="AB19" t="inlineStr">
+      <c r="AA19" t="inlineStr">
         <is>
           <t>(1931.844, 1833.986)</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>b19, y14</t>
         </is>
@@ -6578,20 +8967,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>(0, 4)</t>
+          <t>+1, 0, [2, 2], (0.01, 0.008), [97]</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>(0)-118.083, +4, [2, 2], (0.37, 0.079), [802]</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>0, 0, [2, 2], (0.01, 0.009), [78]</t>
-        </is>
-      </c>
+          <t>+1, +1, [2, 2], (0.01, 0.009), [78]</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>0, 0, [2, 2], (0.011, 0.008), [262]</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
@@ -6603,29 +8992,24 @@
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>(0)-141.283, +3, [2, 2], (0.498, 0.449), [637] ('used')</t>
-        </is>
-      </c>
+      <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr"/>
       <c r="X20" t="inlineStr"/>
       <c r="Y20" t="inlineStr"/>
-      <c r="Z20" t="inlineStr"/>
-      <c r="AA20" t="n">
+      <c r="Z20" t="n">
         <v>3</v>
       </c>
-      <c r="AB20" t="inlineStr">
+      <c r="AA20" t="inlineStr">
         <is>
           <t>(2002.881, 1762.949)</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>b20, y13</t>
         </is>
@@ -6640,14 +9024,22 @@
           <t>+</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>0, 0, [2, 2], (0.012, 0.007), [226]</t>
-        </is>
-      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>+1, 0, [2, 2], (0.012, 0.007), [228]</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>+1, +1, [2, 2], (0.012, 0.007), [226]</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>0, 0, [2, 2], (0.014, 0.007), [381]</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
@@ -6666,18 +9058,17 @@
       <c r="W21" t="inlineStr"/>
       <c r="X21" t="inlineStr"/>
       <c r="Y21" t="inlineStr"/>
-      <c r="Z21" t="inlineStr"/>
-      <c r="AA21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB21" t="inlineStr">
+      <c r="Z21" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA21" t="inlineStr">
         <is>
           <t>(2158.982, 1606.847)</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>b21, y12</t>
         </is>
@@ -6694,20 +9085,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>(5, 0)</t>
+          <t>+1, 0, [2, 2], (0.012, 0.007), [236]</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>+5, (0)-118.087, [2, 2], (0.427, 0.001), [639]</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>0, 0, [2, 2], (0.012, 0.007), [236]</t>
-        </is>
-      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
@@ -6717,11 +9100,7 @@
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>+3, (0)-352.173, [3, 1], (0.467, 0.249), [774]</t>
-        </is>
-      </c>
+      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr"/>
@@ -6730,18 +9109,17 @@
       <c r="W22" t="inlineStr"/>
       <c r="X22" t="inlineStr"/>
       <c r="Y22" t="inlineStr"/>
-      <c r="Z22" t="inlineStr"/>
-      <c r="AA22" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB22" t="inlineStr">
+      <c r="Z22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA22" t="inlineStr">
         <is>
           <t>(2274.009, 1491.821)</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>b22, y11</t>
         </is>
@@ -6758,38 +9136,34 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>(0, 0)</t>
+          <t>+1, 0, [2, 2], (0.013, 0.006), [164]</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0, (+1)-114.07, [2, 1], (0.013, 0.01), [232] ('used')</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>0, (0)-113.07, [3, 1], (0.01, 0.007), [373] ('used')</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>0, 0, [2, 2], (0.013, 0.006), [164]</t>
-        </is>
-      </c>
+          <t>+1, +1, [2, 2], (0.013, 0.006), [183]</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>+1, (0)-347.154, [2, 1], (0.013, 0.009), [789]</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>+1, 0, [3, 1], (0.01, 0.008), [194]</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>0, (+1)-348.16, [2, 1], (0.013, 0.006), [789]</t>
-        </is>
-      </c>
+      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
@@ -6798,18 +9172,17 @@
       <c r="W23" t="inlineStr"/>
       <c r="X23" t="inlineStr"/>
       <c r="Y23" t="inlineStr"/>
-      <c r="Z23" t="inlineStr"/>
-      <c r="AA23" t="n">
+      <c r="Z23" t="n">
         <v>4</v>
       </c>
-      <c r="AB23" t="inlineStr">
+      <c r="AA23" t="inlineStr">
         <is>
           <t>(2421.077, 1344.752)</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>b23, y10</t>
         </is>
@@ -6826,36 +9199,40 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>(0, 0)</t>
+          <t>+1, 0, [2, 2], (0.015, 0.005), [25]</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>(+1)-114.07, 0, [2, 1], (0.004, 0.007), [232] ('used')</t>
+          <t>+1, +1, [2, 2], (0.015, 0.005), [44]</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>(0)-113.07, 0, [3, 1], (0.004, 0.007), [373] ('used')</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>0, 0, [2, 2], (0.015, 0.005), [25]</t>
-        </is>
-      </c>
+          <t>0, 0, [2, 2], (0.016, 0.005), [218]</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>+1, 0, [3, 1], (0.011, 0.007), [45]</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>0, ???, [3, 1], (0.012, 'n/a'), [175]</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0, (+1)-348.16, [2, 1], (0.016, 0.007), [450]</t>
+          <t>+1, (0)-346.151, [2, 1], (0.015, 0.01), [463]</t>
         </is>
       </c>
       <c r="R24" t="inlineStr"/>
@@ -6866,18 +9243,17 @@
       <c r="W24" t="inlineStr"/>
       <c r="X24" t="inlineStr"/>
       <c r="Y24" t="inlineStr"/>
-      <c r="Z24" t="inlineStr"/>
-      <c r="AA24" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB24" t="inlineStr">
+      <c r="Z24" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA24" t="inlineStr">
         <is>
           <t>(2534.162, 1231.668)</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>b24, y9</t>
         </is>
@@ -6892,32 +9268,40 @@
           <t>+</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>+1, 0, [2, 2], (0.016, 0.005), [63]</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>+1, +1, [2, 2], (0.016, 0.004), [85]</t>
+        </is>
+      </c>
       <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>0, 0, [2, 2], (0.016, 0.005), [54]</t>
-        </is>
-      </c>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>+1, (0)-347.154, [2, 1], (0.016, 0.011), [372]</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>+1, 0, [3, 1], (0.012, 0.007), [128]</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>+1, +1, [3, 1], (0.012, 0.007), [151]</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>(0)-540.19, +6, [3, 1], (0.156, 0.453), [820] ('used')</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>0, (+1)-348.16, [2, 1], (0.016, 0.009), [372]</t>
-        </is>
-      </c>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr"/>
@@ -6926,18 +9310,17 @@
       <c r="W25" t="inlineStr"/>
       <c r="X25" t="inlineStr"/>
       <c r="Y25" t="inlineStr"/>
-      <c r="Z25" t="inlineStr"/>
-      <c r="AA25" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB25" t="inlineStr">
+      <c r="Z25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA25" t="inlineStr">
         <is>
           <t>(2648.204, 1117.625)</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>b25, y8</t>
         </is>
@@ -6954,66 +9337,65 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>(0, 0)</t>
+          <t>+1, 0, [2, 2], (0.018, 0.004), [108]</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0, (+1)-114.07, [2, 1], (0.018, 0.013), [824] ('used')</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>0, (0)-113.07, [3, 1], (0.014, 0.009), [114] ('used')</t>
-        </is>
-      </c>
+          <t>+1, +1, [2, 2], (0.018, 0.004), [159]</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>0, 0, [3, 1], (0.014, 0.006), [27]</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+          <t>+1, 0, [3, 1], (0.014, 0.006), [27]</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>+1, +1, [3, 1], (0.014, 0.006), [92]</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>0, 0, [3, 1], (0.014, 0.006), [348]</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>+1, (0)-347.154, [2, 1], (0.018, 0.012), [292]</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>0, (0)-112.063, [3, 1], (0.014, 0.013), [363]</t>
+        </is>
+      </c>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>0, (+1)-348.16, [2, 1], (0.018, 0.009), [122] ('used')</t>
-        </is>
-      </c>
+      <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>(0)-143.29, +6, [3, 1], (0.109, 0.103), [663] ('used')</t>
-        </is>
-      </c>
+      <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>(0)-27.98, 0, [3, 1], (0.003, 0.006), [162]</t>
-        </is>
-      </c>
+      <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr"/>
       <c r="X26" t="inlineStr"/>
       <c r="Y26" t="inlineStr"/>
-      <c r="Z26" t="inlineStr"/>
-      <c r="AA26" t="n">
-        <v>6</v>
-      </c>
-      <c r="AB26" t="inlineStr">
+      <c r="Z26" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA26" t="inlineStr">
         <is>
           <t>(2834.284, 931.546)</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>b26, y7</t>
         </is>
@@ -7030,62 +9412,77 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>(0, 0)</t>
+          <t>0, +1, [2, 2], (0.018, 0.003), [519]</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>(+1)-114.07, 0, [2, 1], (0.001, 0.005), [824] ('used')</t>
+          <t>+1, +1, [2, 2], (0.019, 0.003), [106]</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>(0)-113.07, 0, [3, 1], (0.0, 0.005), [114] ('used')</t>
+          <t>0, 0, [2, 2], (0.018, 0.003), [293]</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>0, 0, [3, 1], (0.014, 0.005), [6]</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+          <t>0, +1, [3, 1], (0.014, 0.005), [18]</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>+1, +1, [3, 1], (0.014, 0.005), [33]</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>0, 0, [3, 1], (0.014, 0.005), [117]</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>+1, (0)-347.154, [2, 1], (0.019, 0.013), [94]</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>(0)-112.063, 0, [3, 1], (0.003, 0.005), [114]</t>
+        </is>
+      </c>
       <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>(0)-13.989, 0, [3, 1], (0.006, 0.005), [441]</t>
+        </is>
+      </c>
       <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>0, (+1)-348.16, [2, 1], (0.019, 0.01), [94] ('used')</t>
-        </is>
-      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>(0)-110.053, 0, [3, 1], (0.009, 0.005), [366]</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>(0)-27.98, 0, [3, 1], (0.001, 0.005), [427] ('used')</t>
-        </is>
-      </c>
+      <c r="V27" t="inlineStr"/>
       <c r="W27" t="inlineStr"/>
       <c r="X27" t="inlineStr"/>
       <c r="Y27" t="inlineStr"/>
-      <c r="Z27" t="inlineStr"/>
-      <c r="AA27" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB27" t="inlineStr">
+      <c r="Z27" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA27" t="inlineStr">
         <is>
           <t>(2947.368, 818.462)</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>b27, y6</t>
         </is>
@@ -7100,34 +9497,46 @@
           <t>+</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>(0, 0)</t>
-        </is>
-      </c>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>(0)-113.07, 0, [3, 1], (0.0, 0.004), [171] ('used')</t>
-        </is>
-      </c>
+      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0, 0, [3, 1], (0.015, 0.004), [4]</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+          <t>+1, 0, [3, 1], (0.015, 0.004), [5]</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>+1, +1, [3, 1], (0.015, 0.004), [41]</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>0, 0, [3, 1], (0.016, 0.004), [86]</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>0, (+1)-347.154, [2, 1], (0.019, 0.014), [387]</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>(0)-112.063, 0, [3, 1], (0.003, 0.004), [171]</t>
+        </is>
+      </c>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>(0)-110.053, 0, [3, 1], (0.009, 0.004), [428]</t>
+        </is>
+      </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>0, (+1)-348.16, [2, 1], (0.02, 0.011), [16] ('used')</t>
+          <t>+1, (0)-346.151, [2, 1], (0.02, 0.013), [261]</t>
         </is>
       </c>
       <c r="R28" t="inlineStr"/>
@@ -7135,25 +9544,20 @@
       <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr"/>
       <c r="V28" t="inlineStr"/>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>0, (0)-17.99, [3, 1], (0.015, 0.016), [960]</t>
-        </is>
-      </c>
+      <c r="W28" t="inlineStr"/>
       <c r="X28" t="inlineStr"/>
       <c r="Y28" t="inlineStr"/>
-      <c r="Z28" t="inlineStr"/>
-      <c r="AA28" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB28" t="inlineStr">
+      <c r="Z28" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA28" t="inlineStr">
         <is>
           <t>(3060.452, 705.378)</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>b28, y5</t>
         </is>
@@ -7173,51 +9577,54 @@
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>0, 0, [3, 1], (0.016, 0.003), [15]</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+          <t>0, +1, [3, 1], (0.016, 0.003), [332]</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>+1, +1, [3, 1], (0.016, 0.003), [334]</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>0, 0, [3, 1], (0.016, 0.003), [102]</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>+1, (0)-347.154, [2, 1], (0.022, 0.014), [34]</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>(0)-13.989, 0, [3, 1], (0.007, 0.003), [462]</t>
+        </is>
+      </c>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>0, (+1)-348.16, [2, 1], (0.019, 0.011), [21] ('used')</t>
-        </is>
-      </c>
+      <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>+2, (0)-133.027, [3, 1], (0.015, 0.008), [642]</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>0, (0)-118.01, [2, 2], (0.019, 0.015), [21] ('used')</t>
-        </is>
-      </c>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
       <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr"/>
       <c r="X29" t="inlineStr"/>
       <c r="Y29" t="inlineStr"/>
-      <c r="Z29" t="inlineStr"/>
-      <c r="AA29" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB29" t="inlineStr">
+      <c r="Z29" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA29" t="inlineStr">
         <is>
           <t>(3188.511, 577.319)</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>b29, y4</t>
         </is>
@@ -7237,16 +9644,28 @@
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0, 0, [3, 1], (0.017, 0.003), [1]</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
+          <t>+1, 0, [3, 1], (0.018, 0.003), [3]</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>+1, +1, [3, 1], (0.018, 0.003), [37]</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>0, 0, [3, 1], (0.018, 0.003), [101]</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>(0)-13.989, 0, [3, 1], (0.004, 0.003), [203]</t>
+        </is>
+      </c>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr"/>
@@ -7255,25 +9674,20 @@
       <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr"/>
       <c r="V30" t="inlineStr"/>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>(0)-17.99, 0, [3, 1], (0.008, 0.003), [260]</t>
-        </is>
-      </c>
+      <c r="W30" t="inlineStr"/>
       <c r="X30" t="inlineStr"/>
       <c r="Y30" t="inlineStr"/>
-      <c r="Z30" t="inlineStr"/>
-      <c r="AA30" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB30" t="inlineStr">
+      <c r="Z30" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA30" t="inlineStr">
         <is>
           <t>(3289.558, 476.271)</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>b30, y3</t>
         </is>
@@ -7293,11 +9707,19 @@
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0, 0, [3, 1], (0.018, 0.002), [7]</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
+          <t>+1, 0, [3, 1], (0.018, 0.002), [9]</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>+1, +1, [3, 1], (0.018, 0.002), [521]</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>0, 0, [3, 1], (0.019, 0.002), [443]</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
@@ -7308,32 +9730,23 @@
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>+2, (0)-133.027, [3, 1], (0.018, 0.01), [148] ('used')</t>
-        </is>
-      </c>
+      <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr"/>
       <c r="V31" t="inlineStr"/>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>(0)-17.99, 0, [3, 1], (0.007, 0.002), [729]</t>
-        </is>
-      </c>
+      <c r="W31" t="inlineStr"/>
       <c r="X31" t="inlineStr"/>
       <c r="Y31" t="inlineStr"/>
-      <c r="Z31" t="inlineStr"/>
-      <c r="AA31" t="n">
+      <c r="Z31" t="n">
         <v>3</v>
       </c>
-      <c r="AB31" t="inlineStr">
+      <c r="AA31" t="inlineStr">
         <is>
           <t>(3417.653, 348.176)</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="A32" s="3" t="inlineStr">
         <is>
           <t>b31, y2</t>
         </is>
@@ -7353,11 +9766,19 @@
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0, 0, [3, 1], (0.018, 0.001), [8]</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
+          <t>+1, 0, [3, 1], (0.019, 0.001), [32]</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>+1, +1, [3, 1], (0.019, 0.001), [161]</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>0, 0, [3, 1], (0.02, 0.001), [269]</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
@@ -7374,18 +9795,17 @@
       <c r="W32" t="inlineStr"/>
       <c r="X32" t="inlineStr"/>
       <c r="Y32" t="inlineStr"/>
-      <c r="Z32" t="inlineStr"/>
-      <c r="AA32" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB32" t="inlineStr">
+      <c r="Z32" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA32" t="inlineStr">
         <is>
           <t>(3530.737, 235.092)</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>b32, y1</t>
         </is>
@@ -7422,18 +9842,17 @@
       <c r="W33" t="inlineStr"/>
       <c r="X33" t="inlineStr"/>
       <c r="Y33" t="inlineStr"/>
-      <c r="Z33" t="inlineStr"/>
-      <c r="AA33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB33" t="inlineStr">
+      <c r="Z33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA33" t="inlineStr">
         <is>
           <t>(3631.785, 134.045)</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>Col Count</t>
         </is>
@@ -7448,63 +9867,65 @@
           <t>+</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="n">
+        <v>17</v>
+      </c>
       <c r="E34" t="n">
+        <v>16</v>
+      </c>
+      <c r="F34" t="n">
+        <v>11</v>
+      </c>
+      <c r="G34" t="n">
         <v>8</v>
       </c>
-      <c r="F34" t="n">
-        <v>12</v>
-      </c>
-      <c r="G34" t="n">
-        <v>23</v>
-      </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L34" t="n">
+        <v>3</v>
+      </c>
+      <c r="M34" t="n">
+        <v>3</v>
+      </c>
+      <c r="N34" t="n">
+        <v>3</v>
+      </c>
+      <c r="O34" t="n">
+        <v>2</v>
+      </c>
+      <c r="P34" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>2</v>
+      </c>
+      <c r="R34" t="n">
         <v>1</v>
       </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
-        <v>2</v>
-      </c>
-      <c r="O34" t="n">
-        <v>1</v>
-      </c>
-      <c r="P34" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>10</v>
-      </c>
-      <c r="R34" t="n">
-        <v>2</v>
-      </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
         <v>0</v>
@@ -7513,182 +9934,179 @@
         <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AA34" t="n">
         <v>32</v>
       </c>
-      <c r="AB34" t="n">
-        <v>32</v>
-      </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>FFC</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="n">
+        <v>32</v>
+      </c>
       <c r="E35" t="n">
+        <v>41</v>
+      </c>
+      <c r="F35" t="n">
+        <v>11</v>
+      </c>
+      <c r="G35" t="n">
+        <v>16</v>
+      </c>
+      <c r="H35" t="n">
+        <v>21</v>
+      </c>
+      <c r="I35" t="n">
         <v>7</v>
       </c>
-      <c r="F35" t="n">
-        <v>16</v>
-      </c>
-      <c r="G35" t="n">
-        <v>241</v>
-      </c>
-      <c r="H35" t="n">
-        <v>4</v>
-      </c>
-      <c r="I35" t="n">
-        <v>4</v>
-      </c>
       <c r="J35" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K35" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L35" t="n">
         <v>3</v>
       </c>
       <c r="M35" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="N35" t="n">
         <v>5</v>
       </c>
       <c r="O35" t="n">
+        <v>4</v>
+      </c>
+      <c r="P35" t="n">
         <v>3</v>
       </c>
-      <c r="P35" t="n">
+      <c r="Q35" t="n">
+        <v>7</v>
+      </c>
+      <c r="R35" t="n">
         <v>4</v>
       </c>
-      <c r="Q35" t="n">
-        <v>27</v>
-      </c>
-      <c r="R35" t="n">
+      <c r="S35" t="n">
+        <v>21</v>
+      </c>
+      <c r="T35" t="n">
+        <v>17</v>
+      </c>
+      <c r="U35" t="n">
+        <v>37</v>
+      </c>
+      <c r="V35" t="n">
         <v>6</v>
       </c>
-      <c r="S35" t="n">
-        <v>8</v>
-      </c>
-      <c r="T35" t="n">
-        <v>9</v>
-      </c>
-      <c r="U35" t="n">
-        <v>8</v>
-      </c>
-      <c r="V35" t="n">
-        <v>17</v>
-      </c>
       <c r="W35" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="X35" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="Y35" t="n">
         <v>5</v>
       </c>
-      <c r="Z35" t="n">
-        <v>6</v>
-      </c>
+      <c r="Z35" t="inlineStr"/>
       <c r="AA35" t="inlineStr"/>
-      <c r="AB35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t>FPR0</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
       <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
         <v>1</v>
       </c>
-      <c r="F36" t="n">
+      <c r="O36" t="n">
         <v>1</v>
       </c>
-      <c r="G36" t="n">
+      <c r="P36" t="n">
         <v>1</v>
       </c>
-      <c r="H36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" t="n">
-        <v>4</v>
-      </c>
-      <c r="J36" t="n">
-        <v>4</v>
-      </c>
-      <c r="K36" t="n">
-        <v>4</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" t="n">
-        <v>1</v>
-      </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
-        <v>3</v>
-      </c>
       <c r="Q36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
         <v>2</v>
       </c>
       <c r="S36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" t="n">
+        <v>3</v>
+      </c>
+      <c r="X36" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y36" t="n">
         <v>4</v>
       </c>
-      <c r="V36" t="n">
-        <v>0</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1</v>
-      </c>
-      <c r="X36" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>0</v>
-      </c>
+      <c r="Z36" t="inlineStr"/>
       <c r="AA36" t="inlineStr"/>
-      <c r="AB36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>FPR1</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
@@ -7697,7 +10115,7 @@
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
@@ -7712,7 +10130,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
@@ -7724,42 +10142,39 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="V37" t="n">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="W37" t="n">
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="Z37" t="inlineStr"/>
       <c r="AA37" t="inlineStr"/>
-      <c r="AB37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>offset</t>
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>FPR0_LIST_1</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -7774,128 +10189,110 @@
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>y3</t>
-        </is>
-      </c>
-      <c r="R38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>(np.float64(687.371323), np.float64(1022.164268), [np.float64(1.0), np.float64(3.0)], np.float64(960.0))</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>(np.float64(694.286283), np.float64(1181.644298), [np.float64(2.0), np.float64(2.0)], np.float64(51.0))</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>(np.float64(855.172902), np.float64(934.210524), [np.float64(1.0), np.float64(3.0)], np.float64(933.0))</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>(np.float64(694.286283), np.float64(1182.145538), [np.float64(2.0), np.float64(2.0)], np.float64(124.0))</t>
+        </is>
+      </c>
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr">
         <is>
-          <t>y1-3</t>
+          <t>(np.float64(942.717789), np.float64(943.218563), [np.float64(2.0), np.float64(2.0)], np.float64(283.0))</t>
         </is>
       </c>
       <c r="U38" t="inlineStr"/>
       <c r="V38" t="inlineStr"/>
-      <c r="W38" t="inlineStr"/>
-      <c r="X38" t="inlineStr"/>
-      <c r="Y38" t="inlineStr"/>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>(np.float64(444.284081), np.float64(1064.516692), [np.float64(1.0), np.float64(3.0)], np.float64(984.0))</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>(np.float64(820.472043), np.float64(983.801129), [np.float64(1.0), np.float64(3.0)], np.float64(530.0))</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>(np.float64(471.295231), np.float64(1475.69991), [np.float64(1.0), np.float64(2.0)], np.float64(356.0))</t>
+        </is>
+      </c>
       <c r="Z38" t="inlineStr"/>
       <c r="AA38" t="inlineStr"/>
-      <c r="AB38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>FPR0_LIST_1</t>
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>FPR0_LIST_2</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>(884.504157, 923.203482, [1, 3], 864)</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>(890.456401, 983.46699, [3, 1], 888)</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>(937.4631905, 946.440642, [2, 2], 541)</t>
-        </is>
-      </c>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>(228.13543, 1211.0494195, [3, 1], 254)</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>(242.151227, 1474.1978175, [3, 1], 365)</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>(355.235876, 1417.654872, [3, 1], 87)</t>
-        </is>
-      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>(850.669374, 904.4531745, [2, 1], 577)</t>
-        </is>
-      </c>
+      <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>(655.359824, 1267.5925285, [3, 1], 119)</t>
-        </is>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>(850.669374, 856.175188, [1, 3], 474)</t>
-        </is>
-      </c>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr">
         <is>
-          <t>(883.456071, 908.957161, [1, 3], 405)</t>
-        </is>
-      </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>(904.4531745, 917.5019565, [3, 1], 579)</t>
-        </is>
-      </c>
-      <c r="T39" t="inlineStr"/>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>(897.70609, 917.5019565, [1, 3], 414)</t>
-        </is>
-      </c>
+          <t>(np.float64(694.787583), np.float64(1181.644298), [np.float64(2.0), np.float64(2.0)], np.float64(67.0))</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>(np.float64(931.913984), np.float64(954.02316), [np.float64(2.0), np.float64(2.0)], np.float64(213.0))</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr"/>
       <c r="V39" t="inlineStr"/>
       <c r="W39" t="inlineStr">
         <is>
-          <t>(909.458425, 1021.844329, [3, 1], 623)</t>
+          <t>(np.float64(343.235955), np.float64(1098.199865), [np.float64(1.0), np.float64(3.0)], np.float64(325.0))</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>(807.7011133333333, 1231.67548, [2, 2], 373)</t>
+          <t>(np.float64(350.18378), np.float64(1140.564372), [np.float64(1.0), np.float64(3.0)], np.float64(296.0))</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>(931.551515, 1324.6143855, [3, 1], 246)</t>
+          <t>(np.float64(584.380033), np.float64(1419.158458), [np.float64(1.0), np.float64(2.0)], np.float64(432.0))</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr"/>
       <c r="AA39" t="inlineStr"/>
-      <c r="AB39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>FPR0_LIST_2</t>
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>FPR0_LIST_3</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -7905,63 +10302,42 @@
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>(228.13543, 1211.0494195, [3, 1], 290)</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>(242.151227, 1474.1978175, [3, 1], 536)</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>(355.235876, 1417.654872, [3, 1], 103)</t>
-        </is>
-      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>(655.359824, 1267.5925285, [3, 1], 182)</t>
-        </is>
-      </c>
+      <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="inlineStr">
-        <is>
-          <t>(900.952596, 904.4531745, [2, 2], 659)</t>
-        </is>
-      </c>
+      <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr"/>
-      <c r="T40" t="inlineStr"/>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>(897.70609, 927.209388, [2, 2], 426)</t>
-        </is>
-      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>(np.float64(647.751052), np.float64(1238.186551), [np.float64(2.0), np.float64(2.0)], np.float64(224.0))</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr"/>
       <c r="V40" t="inlineStr"/>
-      <c r="W40" t="inlineStr"/>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>(941.171129, 1098.199865, [2, 2], 607)</t>
-        </is>
-      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>(np.float64(215.140168), np.float64(1140.89863), [np.float64(1.0), np.float64(3.0)], np.float64(317.0))</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr"/>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>(931.551515, 1324.6143855, [3, 1], 263)</t>
+          <t>(np.float64(358.210464), np.float64(1532.243365), [np.float64(1.0), np.float64(2.0)], np.float64(52.0))</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr"/>
       <c r="AA40" t="inlineStr"/>
-      <c r="AB40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>FPR0_LIST_3</t>
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>TFPR0_LIST_1</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -7971,153 +10347,115 @@
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>(228.13543, 1211.0494195, [3, 1], 403)</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>(242.151227, 1474.1978175, [3, 1], 806)</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>(355.235876, 1417.654872, [3, 1], 174)</t>
-        </is>
-      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>(np.float64(687.3713), np.float64(3066.4928), np.float64(3753.8641))</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>(np.float64(1388.5726), np.float64(2363.2886), np.float64(3751.8612))</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>(655.359824, 1267.5925285, [3, 1], 327)</t>
+          <t>(np.float64(855.1729), np.float64(2802.6316), np.float64(3657.8045))</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="inlineStr"/>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>(np.float64(1388.5726), np.float64(2364.2911), np.float64(3752.8636))</t>
+        </is>
+      </c>
       <c r="S41" t="inlineStr"/>
-      <c r="T41" t="inlineStr"/>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>(897.70609, 917.5019565, [1, 3], 764)</t>
-        </is>
-      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>(np.float64(1885.4356), np.float64(1886.4371), np.float64(3771.8727))</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr"/>
       <c r="V41" t="inlineStr"/>
-      <c r="W41" t="inlineStr"/>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>(np.float64(444.2841), np.float64(3193.5501), np.float64(3637.8342))</t>
+        </is>
+      </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>(807.701273, 1231.675462, [2, 2], 731)</t>
+          <t>(np.float64(820.472), np.float64(2951.4034), np.float64(3771.8754))</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>(931.551515, 1324.6143855, [3, 1], 265)</t>
+          <t>(np.float64(471.2952), np.float64(2951.3998), np.float64(3422.6951))</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr"/>
       <c r="AA41" t="inlineStr"/>
-      <c r="AB41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>TFPR0_LIST_1</t>
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>TFPR0_LIST_2</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>(884.5042, 2769.6104, 3654.1146)</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>(2671.3692, 983.467, 3654.8362)</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>(1874.9264, 1892.8813, 3767.8077)</t>
-        </is>
-      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>(684.4063, 1211.0494, 1895.4557)</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>(726.4537, 1474.1978, 2200.6515)</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>(1065.7076, 1417.6549, 2483.3625)</t>
-        </is>
-      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>(1701.3387, 904.4532, 2605.7919)</t>
-        </is>
-      </c>
+      <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>(1966.0795, 1267.5925, 3233.672)</t>
-        </is>
-      </c>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>(850.6694, 2568.5256, 3419.1949)</t>
-        </is>
-      </c>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr">
         <is>
-          <t>(883.4561, 2726.8715, 3610.3276)</t>
-        </is>
-      </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>(2713.3595, 917.502, 3630.8615)</t>
-        </is>
-      </c>
-      <c r="T42" t="inlineStr"/>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>(897.7061, 2752.5059, 3650.212)</t>
-        </is>
-      </c>
+          <t>(np.float64(1389.5752), np.float64(2363.2886), np.float64(3752.8638))</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>(np.float64(1863.828), np.float64(1908.0463), np.float64(3771.8743))</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr"/>
       <c r="V42" t="inlineStr"/>
       <c r="W42" t="inlineStr">
         <is>
-          <t>(2728.3753, 1021.8443, 3750.2196)</t>
+          <t>(np.float64(343.236), np.float64(3294.5996), np.float64(3637.8356))</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>(1615.4022, 2463.351, 4078.7532)</t>
+          <t>(np.float64(350.1838), np.float64(3421.6931), np.float64(3771.8769))</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>(2794.6545, 1324.6144, 4119.2689)</t>
+          <t>(np.float64(584.38), np.float64(2838.3169), np.float64(3422.6969))</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr"/>
       <c r="AA42" t="inlineStr"/>
-      <c r="AB42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>TFPR0_LIST_2</t>
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>TFPR0_LIST_3</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -8127,136 +10465,130 @@
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>(684.4063, 1211.0494, 1895.4557)</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>(726.4537, 1474.1978, 2200.6515)</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>(1065.7076, 1417.6549, 2483.3625)</t>
-        </is>
-      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>(1966.0795, 1267.5925, 3233.672)</t>
-        </is>
-      </c>
+      <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr"/>
-      <c r="R43" t="inlineStr">
-        <is>
-          <t>(1801.9052, 1808.9063, 3610.8115)</t>
-        </is>
-      </c>
+      <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr"/>
-      <c r="T43" t="inlineStr"/>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>(1795.4122, 1854.4188, 3649.831)</t>
-        </is>
-      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>(np.float64(1295.5021), np.float64(2476.3731), np.float64(3771.8752))</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr"/>
       <c r="V43" t="inlineStr"/>
-      <c r="W43" t="inlineStr"/>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>(1882.3423, 2196.3997, 4078.742)</t>
-        </is>
-      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>(np.float64(215.1402), np.float64(3422.6959), np.float64(3637.8361))</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr"/>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>(2794.6545, 1324.6144, 4119.2689)</t>
+          <t>(np.float64(358.2105), np.float64(3064.4867), np.float64(3422.6972))</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr"/>
       <c r="AA43" t="inlineStr"/>
-      <c r="AB43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>TFPR0_LIST_3</t>
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>FPR1_LIST_1</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>???, 0, [2, 2], ('n/a', 0.014), [100]|</t>
+        </is>
+      </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>(684.4063, 1211.0494, 1895.4557)</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>(726.4537, 1474.1978, 2200.6515)</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>(1065.7076, 1417.6549, 2483.3625)</t>
-        </is>
-      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>0, ???, [3, 1], (0.014, 'n/a'), [144]|</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>???, 0, [3, 1], ('n/a', 0.007), [57]|</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>(1966.0795, 1267.5925, 3233.672)</t>
-        </is>
-      </c>
-      <c r="Q44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>???, (0)-347.155, [2, 1], ('n/a', 0.011), [394]|</t>
+        </is>
+      </c>
       <c r="R44" t="inlineStr"/>
-      <c r="S44" t="inlineStr"/>
-      <c r="T44" t="inlineStr"/>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>???, 0, [3, 1], ('n/a', 0.005), [28]|</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>???, 0, [2, 2], ('n/a', 0.005), [225]|</t>
+        </is>
+      </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>(897.7061, 2752.5059, 3650.212)</t>
-        </is>
-      </c>
-      <c r="V44" t="inlineStr"/>
+          <t>???, 0, [2, 2], ('n/a', 0.014), [199]|</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>???, 0, [3, 1], ('n/a', 0.007), [146]|</t>
+        </is>
+      </c>
       <c r="W44" t="inlineStr"/>
       <c r="X44" t="inlineStr">
         <is>
-          <t>(1615.4025, 2463.3509, 4078.7535)</t>
+          <t>???, 0, [3, 1], ('n/a', 0.005), [47]|</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>(2794.6545, 1324.6144, 4119.2689)</t>
+          <t>???, (0)-346.152, [2, 1], ('n/a', 0.012), [215]|</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr"/>
       <c r="AA44" t="inlineStr"/>
-      <c r="AB44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>FPR1_LIST_1</t>
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>FPR1_LIST_2</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>???, 0, [2, 2], ('n/a', 0.01), [83]|</t>
+        </is>
+      </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(+1)-1965.95, ???, [1, 3], (0.003, 'n/a'), [14]| ('used')</t>
+          <t>???, 0, [3, 1], ('n/a', 0.005), [10]|</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -8265,40 +10597,67 @@
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>???, (+5)-1162.48, [3, 1], ('n/a', 0.233), [16]| ('used')</t>
+          <t>???, 0, [3, 1], ('n/a', 0.007), [206]|</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>???, (0)-347.155, [2, 1], ('n/a', 0.013), [21]|</t>
+        </is>
+      </c>
       <c r="R45" t="inlineStr"/>
-      <c r="S45" t="inlineStr"/>
-      <c r="T45" t="inlineStr"/>
-      <c r="U45" t="inlineStr"/>
-      <c r="V45" t="inlineStr"/>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>???, 0, [3, 1], ('n/a', 0.003), [35]|</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>???, +1, [2, 2], ('n/a', 0.014), [359]|</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>0, ???, [2, 2], (0.005, 'n/a'), [658]|</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>???, 0, [3, 1], ('n/a', 0.007), [143]|</t>
+        </is>
+      </c>
       <c r="W45" t="inlineStr"/>
-      <c r="X45" t="inlineStr"/>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>???, 0, [3, 1], ('n/a', 0.006), [189]|</t>
+        </is>
+      </c>
       <c r="Y45" t="inlineStr"/>
       <c r="Z45" t="inlineStr"/>
       <c r="AA45" t="inlineStr"/>
-      <c r="AB45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>FPR1_LIST_2</t>
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>FPR1_LIST_3</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>0, ???, [2, 2], (0.009, 'n/a'), [72]|</t>
+        </is>
+      </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(+3)-1967.957, ???, [1, 3], (0.003, 'n/a'), [14]| ('used')</t>
+          <t>0, ???, [3, 1], (0.016, 'n/a'), [791]|</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -8307,40 +10666,67 @@
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>???, (+6)-1163.483, [3, 1], ('n/a', 0.233), [16]| ('used')</t>
+          <t>0, ???, [3, 1], (0.012, 'n/a'), [175]|</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>???, (0)-347.155, [2, 1], ('n/a', 0.013), [23]|</t>
+        </is>
+      </c>
       <c r="R46" t="inlineStr"/>
-      <c r="S46" t="inlineStr"/>
-      <c r="T46" t="inlineStr"/>
-      <c r="U46" t="inlineStr"/>
-      <c r="V46" t="inlineStr"/>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>???, 0, [3, 1], ('n/a', 0.004), [12]|</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>+1, ???, [2, 2], (0.005, 'n/a'), [379]|</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>???, +1, [2, 2], ('n/a', 0.014), [98]|</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>???, +1, [3, 1], ('n/a', 0.008), [968]|</t>
+        </is>
+      </c>
       <c r="W46" t="inlineStr"/>
-      <c r="X46" t="inlineStr"/>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>???, 0, [3, 1], ('n/a', 0.004), [39]|</t>
+        </is>
+      </c>
       <c r="Y46" t="inlineStr"/>
       <c r="Z46" t="inlineStr"/>
       <c r="AA46" t="inlineStr"/>
-      <c r="AB46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>FPR1_LIST_3</t>
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>TFPR1_LIST_1</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>(1295.5021, 2474.3669, 3769.869)</t>
+        </is>
+      </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(+6)-1970.967, ???, [1, 3], (0.003, 'n/a'), [14]| ('used')</t>
+          <t>(820.472, 2949.3978, 3769.8698)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -8349,40 +10735,71 @@
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>???, (+6)-1163.483, [3, 1], ('n/a', 0.233), [23]|</t>
+          <t>(2538.194, 1231.6755, 3769.8694)</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>(770.46, 2651.2346, 3421.6946)</t>
+        </is>
+      </c>
       <c r="R47" t="inlineStr"/>
-      <c r="S47" t="inlineStr"/>
-      <c r="T47" t="inlineStr"/>
-      <c r="U47" t="inlineStr"/>
-      <c r="V47" t="inlineStr"/>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>(818.4665, 2952.406, 3770.8725)</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>(1232.6812, 2539.1912, 3771.8724)</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>(1296.5037, 2474.3669, 3770.8706)</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>(2653.2395, 1117.6318, 3770.8713)</t>
+        </is>
+      </c>
       <c r="W47" t="inlineStr"/>
-      <c r="X47" t="inlineStr"/>
-      <c r="Y47" t="inlineStr"/>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>(818.4665, 2953.4075, 3771.874)</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>(359.2137, 3063.4845, 3422.6982)</t>
+        </is>
+      </c>
       <c r="Z47" t="inlineStr"/>
       <c r="AA47" t="inlineStr"/>
-      <c r="AB47" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>TFPR1_LIST_1</t>
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>TFPR1_LIST_2</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>(1863.828, 1906.041, 3769.869)</t>
+        </is>
+      </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(477.2775, 1324.6144, 1801.8919)</t>
+          <t>(818.4665, 2951.4034, 3769.8699)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -8391,44 +10808,67 @@
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>(1074.6314, 1530.7397, 2605.3711)</t>
+          <t>(2652.2377, 1117.6318, 3769.8695)</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>(230.1511, 3191.5438, 3421.6949)</t>
+        </is>
+      </c>
       <c r="R48" t="inlineStr"/>
-      <c r="S48" t="inlineStr"/>
-      <c r="T48" t="inlineStr"/>
-      <c r="U48" t="inlineStr"/>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>(577.3225, 3193.5501, 3770.8726)</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>(1296.5037, 2475.3702, 3771.8739)</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>(1192.4502, 2578.4215, 3770.8717)</t>
+        </is>
+      </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>(2794.6544, 945.4378, 3740.0923)</t>
+          <t>(2539.1962, 1231.6755, 3770.8717)</t>
         </is>
       </c>
       <c r="W48" t="inlineStr"/>
-      <c r="X48" t="inlineStr"/>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>(931.5515, 2840.3228, 3771.8743)</t>
+        </is>
+      </c>
       <c r="Y48" t="inlineStr"/>
       <c r="Z48" t="inlineStr"/>
       <c r="AA48" t="inlineStr"/>
-      <c r="AB48" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>TFPR1_LIST_2</t>
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>TFPR1_LIST_3</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>(1861.8235, 1908.0463, 3769.8698)</t>
+        </is>
+      </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(477.2775, 1324.6144, 1801.8919)</t>
+          <t>(707.3871, 3062.4832, 3769.8702)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -8437,316 +10877,47 @@
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>(1074.6314, 1530.7397, 2605.3711)</t>
+          <t>(2536.1889, 1233.6823, 3769.8712)</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>(358.2105, 3063.4845, 3421.695)</t>
+        </is>
+      </c>
       <c r="R49" t="inlineStr"/>
-      <c r="S49" t="inlineStr"/>
-      <c r="T49" t="inlineStr"/>
-      <c r="U49" t="inlineStr"/>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>(705.3817, 3065.491, 3770.8728)</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>(1193.4532, 2578.4215, 3771.8747)</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>(1295.5021, 2475.3702, 3770.8723)</t>
+        </is>
+      </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>(2794.6544, 945.4378, 3740.0923)</t>
+          <t>(2425.1094, 1345.7632, 3770.8725)</t>
         </is>
       </c>
       <c r="W49" t="inlineStr"/>
-      <c r="X49" t="inlineStr"/>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>(705.3817, 3066.4928, 3771.8745)</t>
+        </is>
+      </c>
       <c r="Y49" t="inlineStr"/>
       <c r="Z49" t="inlineStr"/>
       <c r="AA49" t="inlineStr"/>
-      <c r="AB49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>TFPR1_LIST_3</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr"/>
-      <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>(477.2775, 1324.6144, 1801.8919)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>(1074.6314, 1530.7397, 2605.3711)</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr"/>
-      <c r="R50" t="inlineStr"/>
-      <c r="S50" t="inlineStr"/>
-      <c r="T50" t="inlineStr"/>
-      <c r="U50" t="inlineStr"/>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>(2794.6544, 945.4378, 3740.0923)</t>
-        </is>
-      </c>
-      <c r="W50" t="inlineStr"/>
-      <c r="X50" t="inlineStr"/>
-      <c r="Y50" t="inlineStr"/>
-      <c r="Z50" t="inlineStr"/>
-      <c r="AA50" t="inlineStr"/>
-      <c r="AB50" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>Modifications_Count</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>0</v>
-      </c>
-      <c r="C51" t="n">
-        <v>0</v>
-      </c>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="n">
-        <v>7</v>
-      </c>
-      <c r="F51" t="n">
-        <v>10</v>
-      </c>
-      <c r="G51" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" t="n">
-        <v>3</v>
-      </c>
-      <c r="I51" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" t="n">
-        <v>0</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" t="n">
-        <v>0</v>
-      </c>
-      <c r="M51" t="n">
-        <v>2</v>
-      </c>
-      <c r="N51" t="n">
-        <v>1</v>
-      </c>
-      <c r="O51" t="n">
-        <v>1</v>
-      </c>
-      <c r="P51" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>5</v>
-      </c>
-      <c r="R51" t="n">
-        <v>1</v>
-      </c>
-      <c r="S51" t="n">
-        <v>5</v>
-      </c>
-      <c r="T51" t="n">
-        <v>4</v>
-      </c>
-      <c r="U51" t="n">
-        <v>1</v>
-      </c>
-      <c r="V51" t="n">
-        <v>5</v>
-      </c>
-      <c r="W51" t="n">
-        <v>0</v>
-      </c>
-      <c r="X51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>|SIM(A*,B)|</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr"/>
-      <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="n">
-        <v>7</v>
-      </c>
-      <c r="F52" t="n">
-        <v>10</v>
-      </c>
-      <c r="G52" t="n">
-        <v>23</v>
-      </c>
-      <c r="H52" t="n">
-        <v>0</v>
-      </c>
-      <c r="I52" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" t="n">
-        <v>0</v>
-      </c>
-      <c r="K52" t="n">
-        <v>0</v>
-      </c>
-      <c r="L52" t="n">
-        <v>1</v>
-      </c>
-      <c r="M52" t="n">
-        <v>0</v>
-      </c>
-      <c r="N52" t="n">
-        <v>2</v>
-      </c>
-      <c r="O52" t="n">
-        <v>0</v>
-      </c>
-      <c r="P52" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>9</v>
-      </c>
-      <c r="R52" t="n">
-        <v>1</v>
-      </c>
-      <c r="S52" t="n">
-        <v>5</v>
-      </c>
-      <c r="T52" t="n">
-        <v>6</v>
-      </c>
-      <c r="U52" t="n">
-        <v>1</v>
-      </c>
-      <c r="V52" t="n">
-        <v>3</v>
-      </c>
-      <c r="W52" t="n">
-        <v>4</v>
-      </c>
-      <c r="X52" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA52" t="inlineStr"/>
-      <c r="AB52" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>|DIFF(A*,B)|</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr"/>
-      <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="n">
-        <v>1</v>
-      </c>
-      <c r="F53" t="n">
-        <v>2</v>
-      </c>
-      <c r="G53" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" t="n">
-        <v>0</v>
-      </c>
-      <c r="L53" t="n">
-        <v>0</v>
-      </c>
-      <c r="M53" t="n">
-        <v>0</v>
-      </c>
-      <c r="N53" t="n">
-        <v>0</v>
-      </c>
-      <c r="O53" t="n">
-        <v>1</v>
-      </c>
-      <c r="P53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>1</v>
-      </c>
-      <c r="R53" t="n">
-        <v>1</v>
-      </c>
-      <c r="S53" t="n">
-        <v>0</v>
-      </c>
-      <c r="T53" t="n">
-        <v>0</v>
-      </c>
-      <c r="U53" t="n">
-        <v>0</v>
-      </c>
-      <c r="V53" t="n">
-        <v>1</v>
-      </c>
-      <c r="W53" t="n">
-        <v>0</v>
-      </c>
-      <c r="X53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA53" t="inlineStr"/>
-      <c r="AB53" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/pepline/result/Book4.xlsx
+++ b/pepline/result/Book4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kevinmbp/Desktop/2D_spec_dict/pepline/result/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBDA8624-5886-EA40-8151-DBB016534BAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B746031A-EF6E-6C46-8EFA-B877F5B4C371}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11520" yWindow="500" windowWidth="42240" windowHeight="26780" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12800" yWindow="500" windowWidth="34560" windowHeight="20020" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,13 +19,16 @@
     <sheet name="4+_deconv_greedy" sheetId="4" r:id="rId4"/>
     <sheet name="greedy_annot" sheetId="5" r:id="rId5"/>
     <sheet name="greedy_annot_4+_deconv" sheetId="6" r:id="rId6"/>
+    <sheet name="5+_deconv_greedy" sheetId="7" r:id="rId7"/>
+    <sheet name="greedy_annot_5+_deconv" sheetId="8" r:id="rId8"/>
+    <sheet name="greedy_annot_revised" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1684" uniqueCount="731">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2371" uniqueCount="952">
   <si>
     <t>Bond</t>
   </si>
@@ -2218,19 +2221,692 @@
   </si>
   <si>
     <t>(705.3817, 3066.4928, 3771.8745)</t>
+  </si>
+  <si>
+    <t>All Coverage=64.9%</t>
+  </si>
+  <si>
+    <t>b1, y36</t>
+  </si>
+  <si>
+    <t>(129.102, 3874.29)</t>
+  </si>
+  <si>
+    <t>b2, y35</t>
+  </si>
+  <si>
+    <t>(315.182, 3688.211)</t>
+  </si>
+  <si>
+    <t>b3, y34</t>
+  </si>
+  <si>
+    <t>(443.276, 3560.116)</t>
+  </si>
+  <si>
+    <t>b4, y33</t>
+  </si>
+  <si>
+    <t>+3, 0, [1, 4], (0.016, 0.011), [76]</t>
+  </si>
+  <si>
+    <t>(556.361, 3447.032)</t>
+  </si>
+  <si>
+    <t>b5, y32</t>
+  </si>
+  <si>
+    <t>(703.429, 3299.964)</t>
+  </si>
+  <si>
+    <t>b6, y31</t>
+  </si>
+  <si>
+    <t>0, +1, [1, 4], (0.002, 0.012), [107]</t>
+  </si>
+  <si>
+    <t>(831.524, 3171.869)</t>
+  </si>
+  <si>
+    <t>b7, y30</t>
+  </si>
+  <si>
+    <t>0, +2, [1, 3], (0.0, 0.474), [885]</t>
+  </si>
+  <si>
+    <t>0, +2, [1, 4], (0.0, 0.052), [338]</t>
+  </si>
+  <si>
+    <t>+1, +2, [1, 4], (0.019, 0.052), [958]</t>
+  </si>
+  <si>
+    <t>(959.619, 3043.774)</t>
+  </si>
+  <si>
+    <t>b8, y29</t>
+  </si>
+  <si>
+    <t>0, 0, [2, 3], (0.004, 0.003), [56]</t>
+  </si>
+  <si>
+    <t>0, +1, [2, 3], (0.004, 0.004), [10]</t>
+  </si>
+  <si>
+    <t>0, +2, [2, 3], (0.004, 0.0), [8]</t>
+  </si>
+  <si>
+    <t>+1, +2, [2, 3], (0.002, 0.0), [21]</t>
+  </si>
+  <si>
+    <t>+1, +3, [2, 3], (0.002, 0.001), [127]</t>
+  </si>
+  <si>
+    <t>(1072.703, 2930.69)</t>
+  </si>
+  <si>
+    <t>b9, y28</t>
+  </si>
+  <si>
+    <t>0, 0, [2, 3], (0.003, 0.002), [33]</t>
+  </si>
+  <si>
+    <t>0, +1, [2, 3], (0.003, 0.002), [16]</t>
+  </si>
+  <si>
+    <t>+1, +1, [2, 3], (0.005, 0.002), [39]</t>
+  </si>
+  <si>
+    <t>+1, +2, [2, 3], (0.005, 0.001), [22]</t>
+  </si>
+  <si>
+    <t>0, +4, [2, 3], (0.003, 0.01), [320]</t>
+  </si>
+  <si>
+    <t>(1201.746, 2801.647)</t>
+  </si>
+  <si>
+    <t>b10, y27</t>
+  </si>
+  <si>
+    <t>0, 0, [2, 3], (0.004, 0.002), [52]</t>
+  </si>
+  <si>
+    <t>0, +1, [2, 3], (0.004, 0.0), [4]</t>
+  </si>
+  <si>
+    <t>0, +2, [2, 3], (0.004, 0.002), [7]</t>
+  </si>
+  <si>
+    <t>+1, +2, [2, 3], (0.003, 0.002), [29]</t>
+  </si>
+  <si>
+    <t>+3, +1, [2, 3], (0.003, 0.0), [258]</t>
+  </si>
+  <si>
+    <t>(1329.84, 2673.552)</t>
+  </si>
+  <si>
+    <t>b11, y26</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>0, 0, [2, 3], (0.004, 0.002), [81]</t>
+  </si>
+  <si>
+    <t>0, +1, [2, 3], (0.004, 0.002), [17]</t>
+  </si>
+  <si>
+    <t>+1, +1, [2, 3], (0.004, 0.002), [19]</t>
+  </si>
+  <si>
+    <t>+2, +1, [2, 3], (0.005, 0.002), [42]</t>
+  </si>
+  <si>
+    <t>+2, +2, [2, 3], (0.005, 0.003), [579]</t>
+  </si>
+  <si>
+    <t>(1428.909, 2574.484)</t>
+  </si>
+  <si>
+    <t>b12, y25</t>
+  </si>
+  <si>
+    <t>0, +1, [2, 3], (0.0, 0.001), [79]</t>
+  </si>
+  <si>
+    <t>0, +2, [2, 3], (0.0, 0.019), [274]</t>
+  </si>
+  <si>
+    <t>(1485.93, 2517.462)</t>
+  </si>
+  <si>
+    <t>b13, y24</t>
+  </si>
+  <si>
+    <t>(1613.989, 2389.404)</t>
+  </si>
+  <si>
+    <t>b14, y23</t>
+  </si>
+  <si>
+    <t>(1728.032, 2275.361)</t>
+  </si>
+  <si>
+    <t>b15, y22</t>
+  </si>
+  <si>
+    <t>(1841.116, 2162.277)</t>
+  </si>
+  <si>
+    <t>b16, y21</t>
+  </si>
+  <si>
+    <t>+1, 0, [3, 2], (0.006, 0.005), [111]</t>
+  </si>
+  <si>
+    <t>+1, +1, [3, 2], (0.006, 0.001), [549]</t>
+  </si>
+  <si>
+    <t>(1997.217, 2006.176)</t>
+  </si>
+  <si>
+    <t>b17, y20</t>
+  </si>
+  <si>
+    <t>+1, 0, [3, 2], (0.002, 0.001), [50]</t>
+  </si>
+  <si>
+    <t>+1, +1, [3, 2], (0.002, 0.006), [98]</t>
+  </si>
+  <si>
+    <t>+1, +2, [3, 2], (0.002, 0.002), [89]</t>
+  </si>
+  <si>
+    <t>+3, +1, [2, 3], (0.339, 0.019), [369]</t>
+  </si>
+  <si>
+    <t>(2112.244, 1891.149)</t>
+  </si>
+  <si>
+    <t>b18, y19</t>
+  </si>
+  <si>
+    <t>(2169.265, 1834.127)</t>
+  </si>
+  <si>
+    <t>b19, y18</t>
+  </si>
+  <si>
+    <t>(1, 3)</t>
+  </si>
+  <si>
+    <t>+1, +3, [3, 2], (0.49, 0.028), [262]</t>
+  </si>
+  <si>
+    <t>(2282.349, 1721.043)</t>
+  </si>
+  <si>
+    <t>b20, y17</t>
+  </si>
+  <si>
+    <t>(2395.434, 1607.959)</t>
+  </si>
+  <si>
+    <t>b21, y16</t>
+  </si>
+  <si>
+    <t>0, +2, [2, 2], (0.003, 0.025), [617]</t>
+  </si>
+  <si>
+    <t>(2523.529, 1479.864)</t>
+  </si>
+  <si>
+    <t>b22, y15</t>
+  </si>
+  <si>
+    <t>+3, 0, [3, 2], (0.004, 0.339), [414]</t>
+  </si>
+  <si>
+    <t>(2594.566, 1408.827)</t>
+  </si>
+  <si>
+    <t>b23, y14</t>
+  </si>
+  <si>
+    <t>0, 0, [3, 2], (0.002, 0.002), [162]</t>
+  </si>
+  <si>
+    <t>0, +1, [3, 2], (0.002, 0.003), [61]</t>
+  </si>
+  <si>
+    <t>+2, 0, [3, 2], (0.0, 0.002), [23]</t>
+  </si>
+  <si>
+    <t>+2, +1, [3, 2], (0.0, 0.003), [86]</t>
+  </si>
+  <si>
+    <t>+3, +1, [3, 2], (0.002, 0.003), [833]</t>
+  </si>
+  <si>
+    <t>(2651.587, 1351.806)</t>
+  </si>
+  <si>
+    <t>b24, y13</t>
+  </si>
+  <si>
+    <t>P</t>
+  </si>
+  <si>
+    <t>0, 0, [4, 1], (0.005, 0.004), [191]</t>
+  </si>
+  <si>
+    <t>+1, 0, [4, 1], (0.002, 0.004), [62]</t>
+  </si>
+  <si>
+    <t>+2, 0, [4, 1], (0.003, 0.004), [59]</t>
+  </si>
+  <si>
+    <t>+2, +1, [4, 1], (0.003, 0.003), [121]</t>
+  </si>
+  <si>
+    <t>(2748.64, 1254.753)</t>
+  </si>
+  <si>
+    <t>b25, y12</t>
+  </si>
+  <si>
+    <t>+1, 0, [4, 1], (0.004, 0.002), [9]</t>
+  </si>
+  <si>
+    <t>+2, 0, [4, 1], (0.003, 0.002), [40]</t>
+  </si>
+  <si>
+    <t>+2, +1, [4, 1], (0.003, 0.003), [14]</t>
+  </si>
+  <si>
+    <t>+3, +1, [4, 1], (0.017, 0.003), [394]</t>
+  </si>
+  <si>
+    <t>(2819.677, 1183.716)</t>
+  </si>
+  <si>
+    <t>b26, y11</t>
+  </si>
+  <si>
+    <t>0, 0, [4, 1], (0.003, 0.001), [31]</t>
+  </si>
+  <si>
+    <t>+1, 0, [4, 1], (0.003, 0.001), [3]</t>
+  </si>
+  <si>
+    <t>+2, 0, [4, 1], (0.004, 0.001), [2]</t>
+  </si>
+  <si>
+    <t>+3, 0, [4, 1], (0.004, 0.001), [1]</t>
+  </si>
+  <si>
+    <t>+3, +1, [4, 1], (0.004, 0.0), [84]</t>
+  </si>
+  <si>
+    <t>(2918.745, 1084.647)</t>
+  </si>
+  <si>
+    <t>b27, y10</t>
+  </si>
+  <si>
+    <t>0, 0, [4, 1], (0.002, 0.001), [344]</t>
+  </si>
+  <si>
+    <t>+1, 0, [4, 1], (0.003, 0.001), [18]</t>
+  </si>
+  <si>
+    <t>+2, 0, [4, 1], (0.003, 0.001), [38]</t>
+  </si>
+  <si>
+    <t>+3, 0, [4, 1], (0.003, 0.001), [46]</t>
+  </si>
+  <si>
+    <t>(2989.782, 1013.61)</t>
+  </si>
+  <si>
+    <t>b28, y9</t>
+  </si>
+  <si>
+    <t>+1, 0, [4, 1], (0.003, 0.019), [95]</t>
+  </si>
+  <si>
+    <t>+1, +2, [4, 1], (0.003, 0.001), [658]</t>
+  </si>
+  <si>
+    <t>(3088.851, 914.542)</t>
+  </si>
+  <si>
+    <t>b29, y8</t>
+  </si>
+  <si>
+    <t>0, 0, [4, 1], (0.002, 0.001), [458]</t>
+  </si>
+  <si>
+    <t>0, +1, [4, 1], (0.002, 0.002), [55]</t>
+  </si>
+  <si>
+    <t>+2, 0, [4, 1], (0.003, 0.001), [87]</t>
+  </si>
+  <si>
+    <t>+2, +1, [4, 1], (0.003, 0.002), [45]</t>
+  </si>
+  <si>
+    <t>+4, 0, [4, 1], (0.004, 0.001), [476]</t>
+  </si>
+  <si>
+    <t>(3187.919, 815.473)</t>
+  </si>
+  <si>
+    <t>b30, y7</t>
+  </si>
+  <si>
+    <t>+1, 0, [4, 1], (0.005, 0.001), [47]</t>
+  </si>
+  <si>
+    <t>+2, 0, [4, 1], (0.007, 0.001), [35]</t>
+  </si>
+  <si>
+    <t>+2, +1, [4, 1], (0.007, 0.001), [999]</t>
+  </si>
+  <si>
+    <t>(3244.941, 758.452)</t>
+  </si>
+  <si>
+    <t>b31, y6</t>
+  </si>
+  <si>
+    <t>+3, 0, [4, 1], (0.003, 0.001), [194]</t>
+  </si>
+  <si>
+    <t>(3372.999, 630.393)</t>
+  </si>
+  <si>
+    <t>b32, y5</t>
+  </si>
+  <si>
+    <t>0, 0, [4, 1], (0.001, 0.002), [195]</t>
+  </si>
+  <si>
+    <t>+1, 0, [4, 1], (0.001, 0.002), [51]</t>
+  </si>
+  <si>
+    <t>+1, +1, [4, 1], (0.001, 0.002), [113]</t>
+  </si>
+  <si>
+    <t>+3, 0, [4, 1], (0.004, 0.002), [76]</t>
+  </si>
+  <si>
+    <t>(3444.036, 559.356)</t>
+  </si>
+  <si>
+    <t>b33, y4</t>
+  </si>
+  <si>
+    <t>(3545.084, 458.309)</t>
+  </si>
+  <si>
+    <t>b34, y3</t>
+  </si>
+  <si>
+    <t>(3673.143, 330.25)</t>
+  </si>
+  <si>
+    <t>b35, y2</t>
+  </si>
+  <si>
+    <t>(3786.227, 217.166)</t>
+  </si>
+  <si>
+    <t>b36, y1</t>
+  </si>
+  <si>
+    <t>(3857.264, 146.129)</t>
+  </si>
+  <si>
+    <t>(798.73813392, 801.85538116, [1, 4], 503)</t>
+  </si>
+  <si>
+    <t>(884.86905849, 1041.13573441, [1, 3], 847)</t>
+  </si>
+  <si>
+    <t>(753.7833815, 1085.65087081, [1, 3], 382)</t>
+  </si>
+  <si>
+    <t>(689.81316562, 969.57980196, [3, 2], 916)</t>
+  </si>
+  <si>
+    <t>(742.42651163, 816.99928232, [1, 4], 650)</t>
+  </si>
+  <si>
+    <t>(940.56475474, 1063.64703913, [2, 2], 1000)</t>
+  </si>
+  <si>
+    <t>(673.08227134, 995.59251794, [3, 2], 845)</t>
+  </si>
+  <si>
+    <t>(798.7381, 3207.4215, 4006.1597)</t>
+  </si>
+  <si>
+    <t>(884.8691, 3123.4072, 4008.2763)</t>
+  </si>
+  <si>
+    <t>(753.7834, 3256.9526, 4010.736)</t>
+  </si>
+  <si>
+    <t>(2069.4395, 1939.1596, 4008.5991)</t>
+  </si>
+  <si>
+    <t>(742.4265, 3267.9971, 4010.4236)</t>
+  </si>
+  <si>
+    <t>(1881.1295, 2127.2941, 4008.4236)</t>
+  </si>
+  <si>
+    <t>(2019.2468, 1991.185, 4010.4318)</t>
+  </si>
+  <si>
+    <t>(1,2) -348.15</t>
+  </si>
+  <si>
+    <t>(1,3) -113.06</t>
+  </si>
+  <si>
+    <t>0, (+1)-348.155, [2, 1], (0.013, 0.012), [789]</t>
+  </si>
+  <si>
+    <t>0, (+1)-348.155, [2, 1], (0.015, 0.013), [463]</t>
+  </si>
+  <si>
+    <t>0, (+1)-348.155, [2, 1], (0.016, 0.014), [372]</t>
+  </si>
+  <si>
+    <t>0, (+1)-348.155, [2, 1], (0.018, 0.014), [122]</t>
+  </si>
+  <si>
+    <t>0, (0)-113.064, [3, 1], (0.014, 0.015), [114]</t>
+  </si>
+  <si>
+    <t>0, (+1)-348.155, [2, 1], (0.019, 0.015), [94]</t>
+  </si>
+  <si>
+    <t>0, (0)-113.064, [3, 1], (0.014, 0.016), [171]</t>
+  </si>
+  <si>
+    <t>0, (+1)-348.155, [2, 1], (0.02, 0.016), [16]</t>
+  </si>
+  <si>
+    <t>(0)-113.064, 0, [3, 1], (0.006, 0.004), [171]</t>
+  </si>
+  <si>
+    <t>0, (0)-17.992, [3, 1], (0.015, 0.014), [960]</t>
+  </si>
+  <si>
+    <t>0, (+1)-348.155, [2, 1], (0.019, 0.017), [21]</t>
+  </si>
+  <si>
+    <t>(0)-17.992, 0, [3, 1], (0.005, 0.003), [260]</t>
+  </si>
+  <si>
+    <t>(0)-17.992, 0, [3, 1], (0.005, 0.002), [729]</t>
+  </si>
+  <si>
+    <t>b2, y31, [1, 3], (0.001, 0.022), [167]</t>
+  </si>
+  <si>
+    <t>b9, y24, [2, 2], (0.004, 0.016), [216]</t>
+  </si>
+  <si>
+    <t>b10, y23, [2, 2], (0.005, 0.017), [93]</t>
+  </si>
+  <si>
+    <t>b10, y23, [1, 3], (0.006, 0.013), [361]</t>
+  </si>
+  <si>
+    <t>b11, y22, [2, 2], (0.005, 0.014), [80]</t>
+  </si>
+  <si>
+    <t>b12, y21, [2, 2], (0.006, 0.014), [11]</t>
+  </si>
+  <si>
+    <t>b13, y20, [2, 2], (0.006, 0.014), [17]</t>
+  </si>
+  <si>
+    <t>b14, y19, [2, 2], (0.007, 0.012), [19]</t>
+  </si>
+  <si>
+    <t>b15, y18, [2, 2], (0.008, 0.011), [135]</t>
+  </si>
+  <si>
+    <t>b17, y16, [2, 2], (0.009, 0.01), [42]</t>
+  </si>
+  <si>
+    <t>b18, y15, [2, 2], (0.01, 0.01), [49]</t>
+  </si>
+  <si>
+    <t>b19, y14, [2, 2], (0.01, 0.009), [78]</t>
+  </si>
+  <si>
+    <t>b20, y13, [2, 2], (0.012, 0.007), [226]</t>
+  </si>
+  <si>
+    <t>b21, y12, [2, 2], (0.012, 0.007), [236]</t>
+  </si>
+  <si>
+    <t>b22, y11, [2, 2], (0.013, 0.006), [164]</t>
+  </si>
+  <si>
+    <t>b22, (y11+1)-348.155, [2, 1], (0.013, 0.012), [789]</t>
+  </si>
+  <si>
+    <t>b22, y11, [3, 1], (0.01, 0.008), [194]</t>
+  </si>
+  <si>
+    <t>b23, y10, [2, 2], (0.015, 0.005), [25]</t>
+  </si>
+  <si>
+    <t>b23, (y10+1)-348.155, [2, 1], (0.015, 0.013), [463]</t>
+  </si>
+  <si>
+    <t>b23, y10, [3, 1], (0.011, 0.007), [45]</t>
+  </si>
+  <si>
+    <t>b24, y9, [2, 2], (0.016, 0.005), [54]</t>
+  </si>
+  <si>
+    <t>b24, (y9+1)-348.155, [2, 1], (0.016, 0.014), [372]</t>
+  </si>
+  <si>
+    <t>b24, y9, [3, 1], (0.012, 0.007), [128]</t>
+  </si>
+  <si>
+    <t>b25, y8, [2, 2], (0.018, 0.004), [107]</t>
+  </si>
+  <si>
+    <t>b25, y8, [3, 1], (0.014, 0.006), [27]</t>
+  </si>
+  <si>
+    <t>b25, (y8+1)-348.155, [2, 1], (0.018, 0.014), [122]</t>
+  </si>
+  <si>
+    <t>b25, (y8)-113.064, [3, 1], (0.014, 0.015), [114]</t>
+  </si>
+  <si>
+    <t>b26, y7, [2, 2], (0.019, 0.003), [22]</t>
+  </si>
+  <si>
+    <t>b26, y7, [3, 1], (0.014, 0.005), [6]</t>
+  </si>
+  <si>
+    <t>b26, (y7+1)-348.155, [2, 1], (0.019, 0.015), [94]</t>
+  </si>
+  <si>
+    <t>b26, (y7)-113.064, [3, 1], (0.014, 0.016), [171]</t>
+  </si>
+  <si>
+    <t>b27, y6, [2, 2], (0.02, 0.003), [424]</t>
+  </si>
+  <si>
+    <t>b27, y6, [3, 1], (0.015, 0.004), [4]</t>
+  </si>
+  <si>
+    <t>b27, (y6+1)-348.155, [2, 1], (0.02, 0.016), [16]</t>
+  </si>
+  <si>
+    <t>(b27)-113.064, y6, [3, 1], (0.006, 0.004), [171]</t>
+  </si>
+  <si>
+    <t>b27, (y6)-17.992, [3, 1], (0.015, 0.014), [960]</t>
+  </si>
+  <si>
+    <t>b28, y5, [3, 1], (0.016, 0.003), [15]</t>
+  </si>
+  <si>
+    <t>b28, (y5+1)-348.155, [2, 1], (0.019, 0.017), [21]</t>
+  </si>
+  <si>
+    <t>b29, y4, [3, 1], (0.017, 0.003), [1]</t>
+  </si>
+  <si>
+    <t>(b29)-17.992, y4, [3, 1], (0.005, 0.003), [260]</t>
+  </si>
+  <si>
+    <t>b30, y3, [3, 1], (0.018, 0.002), [7]</t>
+  </si>
+  <si>
+    <t>(b30)-17.992, y3, [3, 1], (0.005, 0.002), [729]</t>
+  </si>
+  <si>
+    <t>b31, y2, [3, 1], (0.018, 0.001), [8]</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Aptos Narrow"/>
     </font>
     <font>
       <b/>
@@ -2261,7 +2937,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -2329,11 +3005,41 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -2345,6 +3051,12 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -10147,4 +10859,2984 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1:K57"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="32.83203125" defaultRowHeight="16"/>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>731</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="5" t="s">
+        <v>732</v>
+      </c>
+      <c r="B2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="5" t="s">
+        <v>734</v>
+      </c>
+      <c r="B3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="5" t="s">
+        <v>736</v>
+      </c>
+      <c r="B4" t="s">
+        <v>127</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="5" t="s">
+        <v>738</v>
+      </c>
+      <c r="B5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" t="s">
+        <v>164</v>
+      </c>
+      <c r="H5" t="s">
+        <v>739</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="5" t="s">
+        <v>741</v>
+      </c>
+      <c r="B6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" t="s">
+        <v>13</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" s="5" t="s">
+        <v>743</v>
+      </c>
+      <c r="B7" t="s">
+        <v>127</v>
+      </c>
+      <c r="C7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" t="s">
+        <v>160</v>
+      </c>
+      <c r="F7" t="s">
+        <v>744</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" s="5" t="s">
+        <v>746</v>
+      </c>
+      <c r="B8" t="s">
+        <v>127</v>
+      </c>
+      <c r="C8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" t="s">
+        <v>332</v>
+      </c>
+      <c r="F8" t="s">
+        <v>747</v>
+      </c>
+      <c r="G8" t="s">
+        <v>748</v>
+      </c>
+      <c r="H8" t="s">
+        <v>749</v>
+      </c>
+      <c r="J8">
+        <v>3</v>
+      </c>
+      <c r="K8" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="5" t="s">
+        <v>751</v>
+      </c>
+      <c r="B9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" t="s">
+        <v>176</v>
+      </c>
+      <c r="E9" t="s">
+        <v>752</v>
+      </c>
+      <c r="F9" t="s">
+        <v>753</v>
+      </c>
+      <c r="G9" t="s">
+        <v>754</v>
+      </c>
+      <c r="H9" t="s">
+        <v>755</v>
+      </c>
+      <c r="I9" t="s">
+        <v>756</v>
+      </c>
+      <c r="J9">
+        <v>5</v>
+      </c>
+      <c r="K9" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" s="5" t="s">
+        <v>758</v>
+      </c>
+      <c r="B10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" t="s">
+        <v>176</v>
+      </c>
+      <c r="E10" t="s">
+        <v>759</v>
+      </c>
+      <c r="F10" t="s">
+        <v>760</v>
+      </c>
+      <c r="G10" t="s">
+        <v>761</v>
+      </c>
+      <c r="H10" t="s">
+        <v>762</v>
+      </c>
+      <c r="I10" t="s">
+        <v>763</v>
+      </c>
+      <c r="J10">
+        <v>5</v>
+      </c>
+      <c r="K10" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" s="5" t="s">
+        <v>765</v>
+      </c>
+      <c r="B11" t="s">
+        <v>127</v>
+      </c>
+      <c r="C11" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" t="s">
+        <v>176</v>
+      </c>
+      <c r="E11" t="s">
+        <v>766</v>
+      </c>
+      <c r="F11" t="s">
+        <v>767</v>
+      </c>
+      <c r="G11" t="s">
+        <v>768</v>
+      </c>
+      <c r="H11" t="s">
+        <v>769</v>
+      </c>
+      <c r="I11" t="s">
+        <v>770</v>
+      </c>
+      <c r="J11">
+        <v>5</v>
+      </c>
+      <c r="K11" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="5" t="s">
+        <v>772</v>
+      </c>
+      <c r="B12" t="s">
+        <v>773</v>
+      </c>
+      <c r="C12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" t="s">
+        <v>176</v>
+      </c>
+      <c r="E12" t="s">
+        <v>774</v>
+      </c>
+      <c r="F12" t="s">
+        <v>775</v>
+      </c>
+      <c r="G12" t="s">
+        <v>776</v>
+      </c>
+      <c r="H12" t="s">
+        <v>777</v>
+      </c>
+      <c r="I12" t="s">
+        <v>778</v>
+      </c>
+      <c r="J12">
+        <v>5</v>
+      </c>
+      <c r="K12" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" s="5" t="s">
+        <v>780</v>
+      </c>
+      <c r="B13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" t="s">
+        <v>160</v>
+      </c>
+      <c r="F13" t="s">
+        <v>781</v>
+      </c>
+      <c r="G13" t="s">
+        <v>782</v>
+      </c>
+      <c r="J13">
+        <v>2</v>
+      </c>
+      <c r="K13" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" s="5" t="s">
+        <v>784</v>
+      </c>
+      <c r="B14" t="s">
+        <v>118</v>
+      </c>
+      <c r="C14" t="s">
+        <v>13</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" s="5" t="s">
+        <v>786</v>
+      </c>
+      <c r="B15" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" t="s">
+        <v>13</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="B16" t="s">
+        <v>54</v>
+      </c>
+      <c r="C16" t="s">
+        <v>13</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" s="5" t="s">
+        <v>790</v>
+      </c>
+      <c r="B17" t="s">
+        <v>76</v>
+      </c>
+      <c r="C17" t="s">
+        <v>17</v>
+      </c>
+      <c r="D17" t="s">
+        <v>167</v>
+      </c>
+      <c r="F17" t="s">
+        <v>791</v>
+      </c>
+      <c r="G17" t="s">
+        <v>792</v>
+      </c>
+      <c r="J17">
+        <v>2</v>
+      </c>
+      <c r="K17" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" s="5" t="s">
+        <v>794</v>
+      </c>
+      <c r="B18" t="s">
+        <v>21</v>
+      </c>
+      <c r="C18" t="s">
+        <v>17</v>
+      </c>
+      <c r="D18" t="s">
+        <v>167</v>
+      </c>
+      <c r="F18" t="s">
+        <v>795</v>
+      </c>
+      <c r="G18" t="s">
+        <v>796</v>
+      </c>
+      <c r="H18" t="s">
+        <v>797</v>
+      </c>
+      <c r="I18" t="s">
+        <v>798</v>
+      </c>
+      <c r="J18">
+        <v>4</v>
+      </c>
+      <c r="K18" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" s="5" t="s">
+        <v>800</v>
+      </c>
+      <c r="B19" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" t="s">
+        <v>13</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" s="5" t="s">
+        <v>802</v>
+      </c>
+      <c r="B20" t="s">
+        <v>54</v>
+      </c>
+      <c r="C20" t="s">
+        <v>17</v>
+      </c>
+      <c r="D20" t="s">
+        <v>803</v>
+      </c>
+      <c r="I20" t="s">
+        <v>804</v>
+      </c>
+      <c r="J20">
+        <v>1</v>
+      </c>
+      <c r="K20" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" s="5" t="s">
+        <v>806</v>
+      </c>
+      <c r="B21" t="s">
+        <v>54</v>
+      </c>
+      <c r="C21" t="s">
+        <v>13</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" s="5" t="s">
+        <v>808</v>
+      </c>
+      <c r="B22" t="s">
+        <v>127</v>
+      </c>
+      <c r="C22" t="s">
+        <v>17</v>
+      </c>
+      <c r="D22" t="s">
+        <v>332</v>
+      </c>
+      <c r="F22" t="s">
+        <v>809</v>
+      </c>
+      <c r="J22">
+        <v>1</v>
+      </c>
+      <c r="K22" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" s="5" t="s">
+        <v>811</v>
+      </c>
+      <c r="B23" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" t="s">
+        <v>17</v>
+      </c>
+      <c r="D23" t="s">
+        <v>164</v>
+      </c>
+      <c r="H23" t="s">
+        <v>812</v>
+      </c>
+      <c r="J23">
+        <v>1</v>
+      </c>
+      <c r="K23" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" s="5" t="s">
+        <v>814</v>
+      </c>
+      <c r="B24" t="s">
+        <v>24</v>
+      </c>
+      <c r="C24" t="s">
+        <v>17</v>
+      </c>
+      <c r="D24" t="s">
+        <v>176</v>
+      </c>
+      <c r="E24" t="s">
+        <v>815</v>
+      </c>
+      <c r="F24" t="s">
+        <v>816</v>
+      </c>
+      <c r="G24" t="s">
+        <v>817</v>
+      </c>
+      <c r="H24" t="s">
+        <v>818</v>
+      </c>
+      <c r="I24" t="s">
+        <v>819</v>
+      </c>
+      <c r="J24">
+        <v>5</v>
+      </c>
+      <c r="K24" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" s="5" t="s">
+        <v>821</v>
+      </c>
+      <c r="B25" t="s">
+        <v>822</v>
+      </c>
+      <c r="C25" t="s">
+        <v>17</v>
+      </c>
+      <c r="D25" t="s">
+        <v>176</v>
+      </c>
+      <c r="E25" t="s">
+        <v>823</v>
+      </c>
+      <c r="F25" t="s">
+        <v>824</v>
+      </c>
+      <c r="G25" t="s">
+        <v>825</v>
+      </c>
+      <c r="H25" t="s">
+        <v>826</v>
+      </c>
+      <c r="J25">
+        <v>4</v>
+      </c>
+      <c r="K25" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" s="5" t="s">
+        <v>828</v>
+      </c>
+      <c r="B26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" t="s">
+        <v>17</v>
+      </c>
+      <c r="D26" t="s">
+        <v>167</v>
+      </c>
+      <c r="F26" t="s">
+        <v>829</v>
+      </c>
+      <c r="G26" t="s">
+        <v>830</v>
+      </c>
+      <c r="H26" t="s">
+        <v>831</v>
+      </c>
+      <c r="I26" t="s">
+        <v>832</v>
+      </c>
+      <c r="J26">
+        <v>4</v>
+      </c>
+      <c r="K26" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" s="5" t="s">
+        <v>834</v>
+      </c>
+      <c r="B27" t="s">
+        <v>773</v>
+      </c>
+      <c r="C27" t="s">
+        <v>17</v>
+      </c>
+      <c r="D27" t="s">
+        <v>176</v>
+      </c>
+      <c r="E27" t="s">
+        <v>835</v>
+      </c>
+      <c r="F27" t="s">
+        <v>836</v>
+      </c>
+      <c r="G27" t="s">
+        <v>837</v>
+      </c>
+      <c r="H27" t="s">
+        <v>838</v>
+      </c>
+      <c r="I27" t="s">
+        <v>839</v>
+      </c>
+      <c r="J27">
+        <v>5</v>
+      </c>
+      <c r="K27" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" s="5" t="s">
+        <v>841</v>
+      </c>
+      <c r="B28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C28" t="s">
+        <v>17</v>
+      </c>
+      <c r="D28" t="s">
+        <v>176</v>
+      </c>
+      <c r="E28" t="s">
+        <v>842</v>
+      </c>
+      <c r="F28" t="s">
+        <v>843</v>
+      </c>
+      <c r="G28" t="s">
+        <v>844</v>
+      </c>
+      <c r="H28" t="s">
+        <v>845</v>
+      </c>
+      <c r="J28">
+        <v>4</v>
+      </c>
+      <c r="K28" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" s="5" t="s">
+        <v>847</v>
+      </c>
+      <c r="B29" t="s">
+        <v>773</v>
+      </c>
+      <c r="C29" t="s">
+        <v>17</v>
+      </c>
+      <c r="D29" t="s">
+        <v>167</v>
+      </c>
+      <c r="F29" t="s">
+        <v>848</v>
+      </c>
+      <c r="H29" t="s">
+        <v>849</v>
+      </c>
+      <c r="J29">
+        <v>2</v>
+      </c>
+      <c r="K29" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" s="5" t="s">
+        <v>851</v>
+      </c>
+      <c r="B30" t="s">
+        <v>773</v>
+      </c>
+      <c r="C30" t="s">
+        <v>17</v>
+      </c>
+      <c r="D30" t="s">
+        <v>176</v>
+      </c>
+      <c r="E30" t="s">
+        <v>852</v>
+      </c>
+      <c r="F30" t="s">
+        <v>853</v>
+      </c>
+      <c r="G30" t="s">
+        <v>854</v>
+      </c>
+      <c r="H30" t="s">
+        <v>855</v>
+      </c>
+      <c r="I30" t="s">
+        <v>856</v>
+      </c>
+      <c r="J30">
+        <v>5</v>
+      </c>
+      <c r="K30" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31" s="5" t="s">
+        <v>858</v>
+      </c>
+      <c r="B31" t="s">
+        <v>24</v>
+      </c>
+      <c r="C31" t="s">
+        <v>17</v>
+      </c>
+      <c r="D31" t="s">
+        <v>167</v>
+      </c>
+      <c r="F31" t="s">
+        <v>859</v>
+      </c>
+      <c r="G31" t="s">
+        <v>860</v>
+      </c>
+      <c r="H31" t="s">
+        <v>861</v>
+      </c>
+      <c r="J31">
+        <v>3</v>
+      </c>
+      <c r="K31" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32" s="5" t="s">
+        <v>863</v>
+      </c>
+      <c r="B32" t="s">
+        <v>118</v>
+      </c>
+      <c r="C32" t="s">
+        <v>17</v>
+      </c>
+      <c r="D32" t="s">
+        <v>164</v>
+      </c>
+      <c r="H32" t="s">
+        <v>864</v>
+      </c>
+      <c r="J32">
+        <v>1</v>
+      </c>
+      <c r="K32" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11">
+      <c r="A33" s="5" t="s">
+        <v>866</v>
+      </c>
+      <c r="B33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" t="s">
+        <v>17</v>
+      </c>
+      <c r="D33" t="s">
+        <v>176</v>
+      </c>
+      <c r="E33" t="s">
+        <v>867</v>
+      </c>
+      <c r="F33" t="s">
+        <v>868</v>
+      </c>
+      <c r="G33" t="s">
+        <v>869</v>
+      </c>
+      <c r="H33" t="s">
+        <v>870</v>
+      </c>
+      <c r="J33">
+        <v>4</v>
+      </c>
+      <c r="K33" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11">
+      <c r="A34" s="5" t="s">
+        <v>872</v>
+      </c>
+      <c r="B34" t="s">
+        <v>50</v>
+      </c>
+      <c r="C34" t="s">
+        <v>13</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11">
+      <c r="A35" s="5" t="s">
+        <v>874</v>
+      </c>
+      <c r="B35" t="s">
+        <v>118</v>
+      </c>
+      <c r="C35" t="s">
+        <v>13</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11">
+      <c r="A36" s="5" t="s">
+        <v>876</v>
+      </c>
+      <c r="B36" t="s">
+        <v>54</v>
+      </c>
+      <c r="C36" t="s">
+        <v>13</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11">
+      <c r="A37" s="5" t="s">
+        <v>878</v>
+      </c>
+      <c r="B37" t="s">
+        <v>16</v>
+      </c>
+      <c r="C37" t="s">
+        <v>13</v>
+      </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11">
+      <c r="A38" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="B38" t="s">
+        <v>127</v>
+      </c>
+      <c r="C38" t="s">
+        <v>17</v>
+      </c>
+      <c r="E38">
+        <v>10</v>
+      </c>
+      <c r="F38">
+        <v>19</v>
+      </c>
+      <c r="G38">
+        <v>16</v>
+      </c>
+      <c r="H38">
+        <v>18</v>
+      </c>
+      <c r="I38">
+        <v>10</v>
+      </c>
+      <c r="J38">
+        <v>36</v>
+      </c>
+      <c r="K38">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11">
+      <c r="A39" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="E39">
+        <v>14</v>
+      </c>
+      <c r="F39">
+        <v>40</v>
+      </c>
+      <c r="G39">
+        <v>40</v>
+      </c>
+      <c r="H39">
+        <v>34</v>
+      </c>
+      <c r="I39">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11">
+      <c r="A40" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="E40">
+        <v>1</v>
+      </c>
+      <c r="F40">
+        <v>0</v>
+      </c>
+      <c r="G40">
+        <v>3</v>
+      </c>
+      <c r="H40">
+        <v>0</v>
+      </c>
+      <c r="I40">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11">
+      <c r="A41" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="E41">
+        <v>0</v>
+      </c>
+      <c r="F41">
+        <v>0</v>
+      </c>
+      <c r="G41">
+        <v>0</v>
+      </c>
+      <c r="H41">
+        <v>0</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11">
+      <c r="A42" s="5" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11">
+      <c r="A43" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="E43" t="s">
+        <v>880</v>
+      </c>
+      <c r="G43" t="s">
+        <v>881</v>
+      </c>
+      <c r="I43" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11">
+      <c r="A44" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="G44" t="s">
+        <v>883</v>
+      </c>
+      <c r="I44" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11">
+      <c r="A45" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="G45" t="s">
+        <v>885</v>
+      </c>
+      <c r="I45" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11">
+      <c r="A46" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="E46" t="s">
+        <v>887</v>
+      </c>
+      <c r="G46" t="s">
+        <v>888</v>
+      </c>
+      <c r="I46" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11">
+      <c r="A47" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="G47" t="s">
+        <v>890</v>
+      </c>
+      <c r="I47" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11">
+      <c r="A48" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="G48" t="s">
+        <v>892</v>
+      </c>
+      <c r="I48" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11">
+      <c r="A49" s="5" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11">
+      <c r="A50" s="5" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11">
+      <c r="A51" s="5" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11">
+      <c r="A52" s="5" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11">
+      <c r="A53" s="5" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11">
+      <c r="A54" s="5" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11">
+      <c r="A55" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="B55">
+        <v>0</v>
+      </c>
+      <c r="C55">
+        <v>0</v>
+      </c>
+      <c r="E55">
+        <v>0</v>
+      </c>
+      <c r="F55">
+        <v>0</v>
+      </c>
+      <c r="G55">
+        <v>0</v>
+      </c>
+      <c r="H55">
+        <v>0</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>0</v>
+      </c>
+      <c r="K55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11">
+      <c r="A56" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="E56">
+        <v>10</v>
+      </c>
+      <c r="F56">
+        <v>10</v>
+      </c>
+      <c r="G56">
+        <v>10</v>
+      </c>
+      <c r="H56">
+        <v>10</v>
+      </c>
+      <c r="I56">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11">
+      <c r="A57" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="E57">
+        <v>0</v>
+      </c>
+      <c r="F57">
+        <v>9</v>
+      </c>
+      <c r="G57">
+        <v>6</v>
+      </c>
+      <c r="H57">
+        <v>8</v>
+      </c>
+      <c r="I57">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="A1:K49"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>894</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>895</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" t="s">
+        <v>13</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" t="s">
+        <v>13</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" t="s">
+        <v>13</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" t="s">
+        <v>38</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+      <c r="K10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" t="s">
+        <v>42</v>
+      </c>
+      <c r="G11" t="s">
+        <v>43</v>
+      </c>
+      <c r="J11">
+        <v>2</v>
+      </c>
+      <c r="K11" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12" t="s">
+        <v>46</v>
+      </c>
+      <c r="C12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" t="s">
+        <v>47</v>
+      </c>
+      <c r="J12">
+        <v>1</v>
+      </c>
+      <c r="K12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" t="s">
+        <v>51</v>
+      </c>
+      <c r="J13">
+        <v>1</v>
+      </c>
+      <c r="K13" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B14" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14" t="s">
+        <v>55</v>
+      </c>
+      <c r="J14">
+        <v>1</v>
+      </c>
+      <c r="K14" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B15" t="s">
+        <v>58</v>
+      </c>
+      <c r="C15" t="s">
+        <v>17</v>
+      </c>
+      <c r="D15" t="s">
+        <v>59</v>
+      </c>
+      <c r="J15">
+        <v>1</v>
+      </c>
+      <c r="K15" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B16" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" t="s">
+        <v>17</v>
+      </c>
+      <c r="D16" t="s">
+        <v>62</v>
+      </c>
+      <c r="J16">
+        <v>1</v>
+      </c>
+      <c r="K16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="B17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C17" t="s">
+        <v>13</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="B18" t="s">
+        <v>58</v>
+      </c>
+      <c r="C18" t="s">
+        <v>17</v>
+      </c>
+      <c r="D18" t="s">
+        <v>67</v>
+      </c>
+      <c r="J18">
+        <v>1</v>
+      </c>
+      <c r="K18" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="B19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" t="s">
+        <v>17</v>
+      </c>
+      <c r="D19" t="s">
+        <v>70</v>
+      </c>
+      <c r="J19">
+        <v>1</v>
+      </c>
+      <c r="K19" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="B20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" t="s">
+        <v>17</v>
+      </c>
+      <c r="D20" t="s">
+        <v>73</v>
+      </c>
+      <c r="J20">
+        <v>1</v>
+      </c>
+      <c r="K20" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="B21" t="s">
+        <v>76</v>
+      </c>
+      <c r="C21" t="s">
+        <v>17</v>
+      </c>
+      <c r="D21" t="s">
+        <v>77</v>
+      </c>
+      <c r="J21">
+        <v>1</v>
+      </c>
+      <c r="K21" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="B22" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22" t="s">
+        <v>17</v>
+      </c>
+      <c r="D22" t="s">
+        <v>80</v>
+      </c>
+      <c r="J22">
+        <v>1</v>
+      </c>
+      <c r="K22" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B23" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" t="s">
+        <v>17</v>
+      </c>
+      <c r="D23" t="s">
+        <v>83</v>
+      </c>
+      <c r="F23" t="s">
+        <v>896</v>
+      </c>
+      <c r="G23" t="s">
+        <v>85</v>
+      </c>
+      <c r="J23">
+        <v>3</v>
+      </c>
+      <c r="K23" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="B24" t="s">
+        <v>54</v>
+      </c>
+      <c r="C24" t="s">
+        <v>17</v>
+      </c>
+      <c r="D24" t="s">
+        <v>88</v>
+      </c>
+      <c r="F24" t="s">
+        <v>897</v>
+      </c>
+      <c r="G24" t="s">
+        <v>90</v>
+      </c>
+      <c r="J24">
+        <v>3</v>
+      </c>
+      <c r="K24" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="B25" t="s">
+        <v>46</v>
+      </c>
+      <c r="C25" t="s">
+        <v>17</v>
+      </c>
+      <c r="D25" t="s">
+        <v>93</v>
+      </c>
+      <c r="F25" t="s">
+        <v>898</v>
+      </c>
+      <c r="G25" t="s">
+        <v>95</v>
+      </c>
+      <c r="J25">
+        <v>3</v>
+      </c>
+      <c r="K25" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="B26" t="s">
+        <v>98</v>
+      </c>
+      <c r="C26" t="s">
+        <v>17</v>
+      </c>
+      <c r="D26" t="s">
+        <v>99</v>
+      </c>
+      <c r="E26" t="s">
+        <v>100</v>
+      </c>
+      <c r="F26" t="s">
+        <v>899</v>
+      </c>
+      <c r="H26" t="s">
+        <v>900</v>
+      </c>
+      <c r="J26">
+        <v>4</v>
+      </c>
+      <c r="K26" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B27" t="s">
+        <v>58</v>
+      </c>
+      <c r="C27" t="s">
+        <v>17</v>
+      </c>
+      <c r="D27" t="s">
+        <v>105</v>
+      </c>
+      <c r="E27" t="s">
+        <v>106</v>
+      </c>
+      <c r="F27" t="s">
+        <v>901</v>
+      </c>
+      <c r="H27" t="s">
+        <v>902</v>
+      </c>
+      <c r="J27">
+        <v>4</v>
+      </c>
+      <c r="K27" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="B28" t="s">
+        <v>54</v>
+      </c>
+      <c r="C28" t="s">
+        <v>17</v>
+      </c>
+      <c r="D28" t="s">
+        <v>111</v>
+      </c>
+      <c r="E28" t="s">
+        <v>112</v>
+      </c>
+      <c r="F28" t="s">
+        <v>903</v>
+      </c>
+      <c r="H28" t="s">
+        <v>904</v>
+      </c>
+      <c r="I28" t="s">
+        <v>905</v>
+      </c>
+      <c r="J28">
+        <v>5</v>
+      </c>
+      <c r="K28" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="B29" t="s">
+        <v>118</v>
+      </c>
+      <c r="C29" t="s">
+        <v>17</v>
+      </c>
+      <c r="E29" t="s">
+        <v>119</v>
+      </c>
+      <c r="F29" t="s">
+        <v>906</v>
+      </c>
+      <c r="J29">
+        <v>2</v>
+      </c>
+      <c r="K29" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="B30" t="s">
+        <v>50</v>
+      </c>
+      <c r="C30" t="s">
+        <v>17</v>
+      </c>
+      <c r="E30" t="s">
+        <v>123</v>
+      </c>
+      <c r="I30" t="s">
+        <v>907</v>
+      </c>
+      <c r="J30">
+        <v>2</v>
+      </c>
+      <c r="K30" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="B31" t="s">
+        <v>127</v>
+      </c>
+      <c r="C31" t="s">
+        <v>17</v>
+      </c>
+      <c r="E31" t="s">
+        <v>128</v>
+      </c>
+      <c r="I31" t="s">
+        <v>908</v>
+      </c>
+      <c r="J31">
+        <v>2</v>
+      </c>
+      <c r="K31" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="B32" t="s">
+        <v>54</v>
+      </c>
+      <c r="C32" t="s">
+        <v>17</v>
+      </c>
+      <c r="E32" t="s">
+        <v>132</v>
+      </c>
+      <c r="J32">
+        <v>1</v>
+      </c>
+      <c r="K32" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11">
+      <c r="A33" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B33" t="s">
+        <v>50</v>
+      </c>
+      <c r="C33" t="s">
+        <v>13</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11">
+      <c r="A34" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="B34" t="s">
+        <v>21</v>
+      </c>
+      <c r="C34" t="s">
+        <v>17</v>
+      </c>
+      <c r="D34">
+        <v>18</v>
+      </c>
+      <c r="E34">
+        <v>8</v>
+      </c>
+      <c r="F34">
+        <v>7</v>
+      </c>
+      <c r="G34">
+        <v>4</v>
+      </c>
+      <c r="H34">
+        <v>3</v>
+      </c>
+      <c r="I34">
+        <v>3</v>
+      </c>
+      <c r="J34">
+        <v>32</v>
+      </c>
+      <c r="K34">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11">
+      <c r="A35" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D35">
+        <v>18</v>
+      </c>
+      <c r="E35">
+        <v>9</v>
+      </c>
+      <c r="F35">
+        <v>11</v>
+      </c>
+      <c r="G35">
+        <v>4</v>
+      </c>
+      <c r="H35">
+        <v>3</v>
+      </c>
+      <c r="I35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11">
+      <c r="A36" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="D36">
+        <v>0</v>
+      </c>
+      <c r="E36">
+        <v>0</v>
+      </c>
+      <c r="F36">
+        <v>0</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11">
+      <c r="A37" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="D37">
+        <v>0</v>
+      </c>
+      <c r="E37">
+        <v>0</v>
+      </c>
+      <c r="F37">
+        <v>0</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11">
+      <c r="A38" s="6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11">
+      <c r="A39" s="6" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11">
+      <c r="A40" s="6" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11">
+      <c r="A41" s="6" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11">
+      <c r="A42" s="6" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11">
+      <c r="A43" s="6" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11">
+      <c r="A44" s="6" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11">
+      <c r="A45" s="6" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11">
+      <c r="A46" s="6" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11">
+      <c r="A47" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11">
+      <c r="A48" s="6" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" s="6" t="s">
+        <v>151</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <dimension ref="A1:K49"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="32.83203125" defaultRowHeight="16"/>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>894</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>895</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s">
+        <v>909</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" t="s">
+        <v>13</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" t="s">
+        <v>13</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" t="s">
+        <v>13</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" t="s">
+        <v>910</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+      <c r="K10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" t="s">
+        <v>911</v>
+      </c>
+      <c r="G11" t="s">
+        <v>912</v>
+      </c>
+      <c r="J11">
+        <v>2</v>
+      </c>
+      <c r="K11" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12" t="s">
+        <v>46</v>
+      </c>
+      <c r="C12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" t="s">
+        <v>913</v>
+      </c>
+      <c r="J12">
+        <v>1</v>
+      </c>
+      <c r="K12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" t="s">
+        <v>914</v>
+      </c>
+      <c r="J13">
+        <v>1</v>
+      </c>
+      <c r="K13" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B14" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14" t="s">
+        <v>915</v>
+      </c>
+      <c r="J14">
+        <v>1</v>
+      </c>
+      <c r="K14" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B15" t="s">
+        <v>58</v>
+      </c>
+      <c r="C15" t="s">
+        <v>17</v>
+      </c>
+      <c r="D15" t="s">
+        <v>916</v>
+      </c>
+      <c r="J15">
+        <v>1</v>
+      </c>
+      <c r="K15" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B16" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" t="s">
+        <v>17</v>
+      </c>
+      <c r="D16" t="s">
+        <v>917</v>
+      </c>
+      <c r="J16">
+        <v>1</v>
+      </c>
+      <c r="K16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="B17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C17" t="s">
+        <v>13</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="B18" t="s">
+        <v>58</v>
+      </c>
+      <c r="C18" t="s">
+        <v>17</v>
+      </c>
+      <c r="D18" t="s">
+        <v>918</v>
+      </c>
+      <c r="J18">
+        <v>1</v>
+      </c>
+      <c r="K18" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="B19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" t="s">
+        <v>17</v>
+      </c>
+      <c r="D19" t="s">
+        <v>919</v>
+      </c>
+      <c r="J19">
+        <v>1</v>
+      </c>
+      <c r="K19" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="B20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" t="s">
+        <v>17</v>
+      </c>
+      <c r="D20" t="s">
+        <v>920</v>
+      </c>
+      <c r="J20">
+        <v>1</v>
+      </c>
+      <c r="K20" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="B21" t="s">
+        <v>76</v>
+      </c>
+      <c r="C21" t="s">
+        <v>17</v>
+      </c>
+      <c r="D21" t="s">
+        <v>921</v>
+      </c>
+      <c r="J21">
+        <v>1</v>
+      </c>
+      <c r="K21" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="B22" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22" t="s">
+        <v>17</v>
+      </c>
+      <c r="D22" t="s">
+        <v>922</v>
+      </c>
+      <c r="J22">
+        <v>1</v>
+      </c>
+      <c r="K22" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B23" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" t="s">
+        <v>17</v>
+      </c>
+      <c r="D23" t="s">
+        <v>923</v>
+      </c>
+      <c r="F23" t="s">
+        <v>924</v>
+      </c>
+      <c r="G23" t="s">
+        <v>925</v>
+      </c>
+      <c r="J23">
+        <v>3</v>
+      </c>
+      <c r="K23" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="B24" t="s">
+        <v>54</v>
+      </c>
+      <c r="C24" t="s">
+        <v>17</v>
+      </c>
+      <c r="D24" t="s">
+        <v>926</v>
+      </c>
+      <c r="F24" t="s">
+        <v>927</v>
+      </c>
+      <c r="G24" t="s">
+        <v>928</v>
+      </c>
+      <c r="J24">
+        <v>3</v>
+      </c>
+      <c r="K24" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="B25" t="s">
+        <v>46</v>
+      </c>
+      <c r="C25" t="s">
+        <v>17</v>
+      </c>
+      <c r="D25" t="s">
+        <v>929</v>
+      </c>
+      <c r="F25" t="s">
+        <v>930</v>
+      </c>
+      <c r="G25" t="s">
+        <v>931</v>
+      </c>
+      <c r="J25">
+        <v>3</v>
+      </c>
+      <c r="K25" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="B26" t="s">
+        <v>98</v>
+      </c>
+      <c r="C26" t="s">
+        <v>17</v>
+      </c>
+      <c r="D26" t="s">
+        <v>932</v>
+      </c>
+      <c r="E26" t="s">
+        <v>933</v>
+      </c>
+      <c r="F26" t="s">
+        <v>934</v>
+      </c>
+      <c r="H26" t="s">
+        <v>935</v>
+      </c>
+      <c r="J26">
+        <v>4</v>
+      </c>
+      <c r="K26" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B27" t="s">
+        <v>58</v>
+      </c>
+      <c r="C27" t="s">
+        <v>17</v>
+      </c>
+      <c r="D27" t="s">
+        <v>936</v>
+      </c>
+      <c r="E27" t="s">
+        <v>937</v>
+      </c>
+      <c r="F27" t="s">
+        <v>938</v>
+      </c>
+      <c r="H27" t="s">
+        <v>939</v>
+      </c>
+      <c r="J27">
+        <v>4</v>
+      </c>
+      <c r="K27" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="B28" t="s">
+        <v>54</v>
+      </c>
+      <c r="C28" t="s">
+        <v>17</v>
+      </c>
+      <c r="D28" t="s">
+        <v>940</v>
+      </c>
+      <c r="E28" t="s">
+        <v>941</v>
+      </c>
+      <c r="F28" t="s">
+        <v>942</v>
+      </c>
+      <c r="H28" t="s">
+        <v>943</v>
+      </c>
+      <c r="I28" t="s">
+        <v>944</v>
+      </c>
+      <c r="J28">
+        <v>5</v>
+      </c>
+      <c r="K28" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="B29" t="s">
+        <v>118</v>
+      </c>
+      <c r="C29" t="s">
+        <v>17</v>
+      </c>
+      <c r="E29" t="s">
+        <v>945</v>
+      </c>
+      <c r="F29" t="s">
+        <v>946</v>
+      </c>
+      <c r="J29">
+        <v>2</v>
+      </c>
+      <c r="K29" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="B30" t="s">
+        <v>50</v>
+      </c>
+      <c r="C30" t="s">
+        <v>17</v>
+      </c>
+      <c r="E30" t="s">
+        <v>947</v>
+      </c>
+      <c r="I30" t="s">
+        <v>948</v>
+      </c>
+      <c r="J30">
+        <v>2</v>
+      </c>
+      <c r="K30" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="B31" t="s">
+        <v>127</v>
+      </c>
+      <c r="C31" t="s">
+        <v>17</v>
+      </c>
+      <c r="E31" t="s">
+        <v>949</v>
+      </c>
+      <c r="I31" t="s">
+        <v>950</v>
+      </c>
+      <c r="J31">
+        <v>2</v>
+      </c>
+      <c r="K31" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="B32" t="s">
+        <v>54</v>
+      </c>
+      <c r="C32" t="s">
+        <v>17</v>
+      </c>
+      <c r="E32" t="s">
+        <v>951</v>
+      </c>
+      <c r="J32">
+        <v>1</v>
+      </c>
+      <c r="K32" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11">
+      <c r="A33" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B33" t="s">
+        <v>50</v>
+      </c>
+      <c r="C33" t="s">
+        <v>13</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11">
+      <c r="A34" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="B34" t="s">
+        <v>21</v>
+      </c>
+      <c r="C34" t="s">
+        <v>17</v>
+      </c>
+      <c r="D34">
+        <v>18</v>
+      </c>
+      <c r="E34">
+        <v>8</v>
+      </c>
+      <c r="F34">
+        <v>7</v>
+      </c>
+      <c r="G34">
+        <v>4</v>
+      </c>
+      <c r="H34">
+        <v>3</v>
+      </c>
+      <c r="I34">
+        <v>3</v>
+      </c>
+      <c r="J34">
+        <v>32</v>
+      </c>
+      <c r="K34">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11">
+      <c r="A35" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D35">
+        <v>18</v>
+      </c>
+      <c r="E35">
+        <v>9</v>
+      </c>
+      <c r="F35">
+        <v>11</v>
+      </c>
+      <c r="G35">
+        <v>4</v>
+      </c>
+      <c r="H35">
+        <v>3</v>
+      </c>
+      <c r="I35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11">
+      <c r="A36" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="D36">
+        <v>0</v>
+      </c>
+      <c r="E36">
+        <v>0</v>
+      </c>
+      <c r="F36">
+        <v>0</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11">
+      <c r="A37" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="D37">
+        <v>0</v>
+      </c>
+      <c r="E37">
+        <v>0</v>
+      </c>
+      <c r="F37">
+        <v>0</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11">
+      <c r="A38" s="6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11">
+      <c r="A39" s="6" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11">
+      <c r="A40" s="6" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11">
+      <c r="A41" s="6" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11">
+      <c r="A42" s="6" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11">
+      <c r="A43" s="6" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11">
+      <c r="A44" s="6" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11">
+      <c r="A45" s="6" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11">
+      <c r="A46" s="6" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11">
+      <c r="A47" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11">
+      <c r="A48" s="6" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" s="6" t="s">
+        <v>151</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/pepline/result/Book4.xlsx
+++ b/pepline/result/Book4.xlsx
@@ -16,6 +16,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="greedy_annot_5+_deconv" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="greedy_annot_revised" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="greedy_annot_LLG" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="greedy_annot_revised_LLG" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -800,6 +801,2221 @@
           <t>0</t>
         </is>
       </c>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>(114.091, 4378.499)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>b2, y35</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>(227.175, 4265.414)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>b3, y34</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>(284.197, 4208.393)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>b4, y33</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>(399.224, 4093.366)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>b5, y32</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>(546.292, 3946.298)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>b6, y31</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>(693.361, 3799.229)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>b7, y30</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>0, +1, [1, 5], (0.0, 0.002), [136]</t>
+        </is>
+      </c>
+      <c r="AA8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>(849.462, 3643.128)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>b8, y29</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>0, +1, [1, 5], (0.001, 0.002), [37]</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>(0)-226.169, +1, [1, 4], (0.002, 0.001), [32]</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>+1, +1, [1, 5], (0.0, 0.002), [24]</t>
+        </is>
+      </c>
+      <c r="AA9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>(977.557, 3515.033)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>b9, y28</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>0, +1, [1, 5], (0.001, 0.002), [129]</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>+1, +1, [2, 4], (0.001, 0.0), [57]</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>+1, 0, [2, 4], (0.001, 0.0), [145]</t>
+        </is>
+      </c>
+      <c r="AA10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>(1064.589, 3428.001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>b10, y27</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>0, +1, [1, 5], (0.0, 0.002), [169]</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>+1, +1, [2, 4], (0.0, 0.0), [3]</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>+1, 0, [2, 4], (0.0, 0.001), [38]</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>0, (0)-16.006, [2, 4], (0.0, 0.01), [224]</t>
+        </is>
+      </c>
+      <c r="AA11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>(1192.684, 3299.906)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>b11, y26</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>0, +1, [1, 5], (0.001, 0.002), [126]</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>+1, +1, [2, 4], (0.0, 0.0), [10]</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>0, +1, [2, 4], (0.001, 0.0), [70]</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>(0)-17.009, +1, [2, 4], (0.001, 0.0), [103]</t>
+        </is>
+      </c>
+      <c r="AA12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>(1321.726, 3170.864)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>b12, y25</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>+1, +1, [2, 4], (0.0, 0.001), [16]</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>???, +1, [2, 4], ('n/a', 0.001), [647]</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>(0)-226.168, +1, [2, 3], (0.0, 0.002), [150]</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>(0)-225.165, +1, [2, 3], (0.0, 0.002), [144]</t>
+        </is>
+      </c>
+      <c r="AA13" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>(1449.821, 3042.769)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>b13, y24</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>(0)-226.168, +1, [2, 3], (0.0, 0.001), [276]</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>0, +1, [2, 4], (0.0, 0.0), [86]</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>+1, +1, [2, 4], (0.0, 0.0), [22]</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>(0)-18.008, +1, [2, 4], (0.002, 0.0), [104]</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>(0)-17.005, +1, [2, 4], (0.002, 0.0), [189]</t>
+        </is>
+      </c>
+      <c r="AA14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>(1562.905, 2929.685)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>b14, y23</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>0, +1, [2, 4], (0.002, 0.001), [173]</t>
+        </is>
+      </c>
+      <c r="AA15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>(1619.927, 2872.663)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>b15, y22</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>(1748.022, 2744.568)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>b16, y21</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>+1, 0, [2, 4], (0.001, 0.001), [13]</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>+1, +1, [2, 4], (0.001, 0.001), [2]</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>(0)-17.004, 0, [2, 4], (0.002, 0.001), [192]</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>(0)-16.001, 0, [2, 4], (0.002, 0.001), [98]</t>
+        </is>
+      </c>
+      <c r="AA17" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>(1877.064, 2615.526)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>b17, y20</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>(2024.133, 2468.457)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>b18, y19</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>(2152.228, 2340.362)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>b19, y18</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>(2308.329, 2184.261)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>b20, y17</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>(2421.413, 2071.177)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>b21, y16</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>(2520.481, 1972.109)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>b22, y15</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>(2648.54, 1844.05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>b23, y14</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>(+1)-226.168, 0, [3, 2], (0.004, 0.0), [180]</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>+1, 0, [4, 2], (0.001, 0.0), [89]</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>+1, +1, [4, 2], (0.001, 0.0), [47]</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>(+1)-225.165, 0, [3, 2], (0.0, 0.0), [106]</t>
+        </is>
+      </c>
+      <c r="AA24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>(2804.641, 1687.949)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>b24, y13</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>(2917.725, 1574.865)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>b25, y12</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>+1, +1, [4, 2], (0.003, 0.0), [100]</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>+1, 0, [4, 2], (0.003, 0.001), [73]</t>
+        </is>
+      </c>
+      <c r="AA26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>(3045.82, 1446.77)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>b26, y11</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>+1, +1, [4, 2], (0.0, 0.0), [52]</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>0, +1, [4, 2], (0.0, 0.0), [58]</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>(0)-226.168, +1, [3, 2], (0.002, 0.0), [21]</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>(+1)-225.165, 0, [3, 2], (0.003, 0.0), [1]</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>(0)-16.006, 0, [4, 2], (0.008, 0.0), [721]</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>(0)-112.082, ???, [3, 2], (0.004, 'n/a'), [199]</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>(0)-113.085, ???, [3, 2], (0.002, 'n/a'), [125]</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>(+1)-224.161, 0, [3, 2], (0.002, 0.0), [23]</t>
+        </is>
+      </c>
+      <c r="AA27" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>(3160.847, 1331.743)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>b27, y10</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>(3307.915, 1184.675)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>b28, y9</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>(3420.999, 1071.59)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>b29, y8</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>+1, 0, [5, 1], (0.004, 0.0), [153]</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>+1, +1, [5, 1], (0.004, 0.0), [77]</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>(+1)-225.167, 0, [4, 1], (0.0, 0.0), [84]</t>
+        </is>
+      </c>
+      <c r="AA30" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>(3577.1, 915.489)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>b30, y7</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>+1, 0, [5, 1], (0.002, 0.0), [137]</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>(+1)-226.169, 0, [4, 1], (0.0, 0.0), [227]</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>(+1)-225.167, 0, [4, 1], (0.0, 0.0), [131]</t>
+        </is>
+      </c>
+      <c r="AA31" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>(3691.143, 801.446)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>b31, y6</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>(3804.227, 688.362)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>b32, y5</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>(+1)-226.169, 0, [4, 1], (0.002, 0.001), [259]</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>(+1)-225.167, 0, [4, 1], (0.003, 0.001), [204]</t>
+        </is>
+      </c>
+      <c r="AA33" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>(3903.296, 589.294)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>b33, y4</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>(4000.349, 492.241)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>b34, y3</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>(4156.45, 336.14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>b35, y2</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>(4257.497, 235.092)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>b36, y1</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>(4386.54, 106.05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>Col Count</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>7</v>
+      </c>
+      <c r="E38" t="n">
+        <v>6</v>
+      </c>
+      <c r="F38" t="n">
+        <v>6</v>
+      </c>
+      <c r="G38" t="n">
+        <v>4</v>
+      </c>
+      <c r="H38" t="n">
+        <v>4</v>
+      </c>
+      <c r="I38" t="n">
+        <v>3</v>
+      </c>
+      <c r="J38" t="n">
+        <v>3</v>
+      </c>
+      <c r="K38" t="n">
+        <v>3</v>
+      </c>
+      <c r="L38" t="n">
+        <v>3</v>
+      </c>
+      <c r="M38" t="n">
+        <v>2</v>
+      </c>
+      <c r="N38" t="n">
+        <v>2</v>
+      </c>
+      <c r="O38" t="n">
+        <v>2</v>
+      </c>
+      <c r="P38" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>1</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1</v>
+      </c>
+      <c r="S38" t="n">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>36</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>FFC</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>9</v>
+      </c>
+      <c r="E39" t="n">
+        <v>17</v>
+      </c>
+      <c r="F39" t="n">
+        <v>12</v>
+      </c>
+      <c r="G39" t="n">
+        <v>6</v>
+      </c>
+      <c r="H39" t="n">
+        <v>7</v>
+      </c>
+      <c r="I39" t="n">
+        <v>3</v>
+      </c>
+      <c r="J39" t="n">
+        <v>9</v>
+      </c>
+      <c r="K39" t="n">
+        <v>8</v>
+      </c>
+      <c r="L39" t="n">
+        <v>5</v>
+      </c>
+      <c r="M39" t="n">
+        <v>3</v>
+      </c>
+      <c r="N39" t="n">
+        <v>5</v>
+      </c>
+      <c r="O39" t="n">
+        <v>9</v>
+      </c>
+      <c r="P39" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>4</v>
+      </c>
+      <c r="R39" t="n">
+        <v>3</v>
+      </c>
+      <c r="S39" t="n">
+        <v>3</v>
+      </c>
+      <c r="T39" t="n">
+        <v>4</v>
+      </c>
+      <c r="U39" t="n">
+        <v>3</v>
+      </c>
+      <c r="V39" t="n">
+        <v>5</v>
+      </c>
+      <c r="W39" t="n">
+        <v>7</v>
+      </c>
+      <c r="X39" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>FPR0</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>1</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>2</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" t="n">
+        <v>4</v>
+      </c>
+      <c r="W40" t="n">
+        <v>2</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>FPR1</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" t="n">
+        <v>10</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>6</v>
+      </c>
+      <c r="K41" t="n">
+        <v>3</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>7</v>
+      </c>
+      <c r="P41" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>2</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1</v>
+      </c>
+      <c r="S41" t="n">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>3</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1</v>
+      </c>
+      <c r="W41" t="n">
+        <v>5</v>
+      </c>
+      <c r="X41" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>FPR0_LIST_1</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>(np.float64(725.41971821), np.float64(761.94949729), [np.float64(2.0), np.float64(4.0)], np.float64(292.0))</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>(np.float64(652.36145807), np.float64(793.973287), [np.float64(2.0), np.float64(4.0)], np.float64(35.0))</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>(np.float64(655.13850436), np.float64(930.03167634), [np.float64(4.0), np.float64(2.0)], np.float64(43.0))</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>(np.float64(746.76848202), np.float64(747.26890317), [np.float64(4.0), np.float64(2.0)], np.float64(898.0))</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>(np.float64(667.37839561), np.float64(791.46927924), [np.float64(2.0), np.float64(4.0)], np.float64(486.0))</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>(np.float64(749.60417422), np.float64(750.10522637), [np.float64(2.0), np.float64(4.0)], np.float64(156.0))</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>FPR0_LIST_2</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>(np.float64(733.67866521), np.float64(772.95160064), [np.float64(4.0), np.float64(2.0)], np.float64(127.0))</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>(np.float64(655.38912494), np.float64(930.03167634), [np.float64(4.0), np.float64(2.0)], np.float64(193.0))</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>(np.float64(597.84923948), np.float64(826.23420531), [np.float64(2.0), np.float64(4.0)], np.float64(133.0))</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>FPR0_LIST_3</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>(np.float64(655.13850436), np.float64(930.53294749), [np.float64(4.0), np.float64(2.0)], np.float64(83.0))</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>TFPR0_LIST_1</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>(np.float64(1450.8394), np.float64(3047.798), np.float64(4498.6374))</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>(np.float64(1304.7229), np.float64(3175.8931), np.float64(4480.6161))</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>(np.float64(2620.554), np.float64(1860.0634), np.float64(4480.6174))</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>(np.float64(2987.0739), np.float64(1494.5378), np.float64(4481.6117))</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>(np.float64(1334.7568), np.float64(3165.8771), np.float64(4500.6339))</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>(np.float64(1499.2083), np.float64(3000.4209), np.float64(4499.6293))</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="8" t="inlineStr">
+        <is>
+          <t>TFPR0_LIST_2</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>(np.float64(2934.7147), np.float64(1545.9032), np.float64(4480.6179))</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>(np.float64(2621.5565), np.float64(1860.0634), np.float64(4481.6199))</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>(np.float64(1195.6985), np.float64(3304.9368), np.float64(4500.6353))</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t>TFPR0_LIST_3</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>(np.float64(2620.554), np.float64(1861.0659), np.float64(4481.6199))</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="8" t="inlineStr">
+        <is>
+          <t>FPR1_LIST_1</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>???, 0, [2, 4], ('n/a', 0.002), [51]|</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>???, +1, [2, 4], ('n/a', 0.001), [647]|</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>???, 0, [4, 2], ('n/a', 0.0), [62]|</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>(0)-226.168, ???, [2, 3], (0.0, 'n/a'), [147]|</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0, ???, [1, 5], (0.0, 'n/a'), [71]|</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>(0)-226.17, ???, [1, 4], (0.003, 'n/a'), [18]|</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>(0)-226.17, ???, [1, 4], (0.003, 'n/a'), [110]|</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>(0)-112.082, ???, [3, 2], (0.004, 'n/a'), [199]|</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>(0)-113.085, ???, [3, 2], (0.002, 'n/a'), [125]|</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>(0)-225.165, ???, [2, 3], (0.0, 'n/a'), [410]|</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>0, ???, [1, 5], (0.0, 'n/a'), [17]|</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>+1, ???, [2, 4], (0.001, 'n/a'), [215]|</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>0, ???, [2, 4], (0.0, 'n/a'), [859]|</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>???, +1, [4, 2], ('n/a', 0.0), [271]|</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>0, ???, [2, 4], (0.0, 'n/a'), [44]|</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>???, 0, [5, 1], ('n/a', 0.0), [81]|</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="8" t="inlineStr">
+        <is>
+          <t>FPR1_LIST_2</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0, ???, [2, 4], (0.0, 'n/a'), [4]|</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>???, 0, [2, 4], ('n/a', 0.001), [15]|</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>(0)-226.168, ???, [3, 2], (0.002, 'n/a'), [75]|</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0, ???, [1, 5], (0.001, 'n/a'), [20]|</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>(0)-226.17, ???, [1, 4], (0.003, 'n/a'), [50]|</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>(0)-225.165, ???, [3, 2], (0.003, 'n/a'), [90]|</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>0, ???, [1, 5], (0.0, 'n/a'), [148]|</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>0, ???, [2, 4], (0.0, 'n/a'), [112]|</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>0, ???, [2, 4], (0.0, 'n/a'), [74]|</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>0, ???, [2, 4], (0.0, 'n/a'), [67]|</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>0, ???, [1, 5], (0.0, 'n/a'), [183]|</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="8" t="inlineStr">
+        <is>
+          <t>FPR1_LIST_3</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0, ???, [2, 4], (0.001, 'n/a'), [42]|</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0, ???, [2, 4], (0.0, 'n/a'), [5]|</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>(0)-226.168, ???, [2, 3], (0.0, 'n/a'), [94]|</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0, ???, [1, 5], (0.0, 'n/a'), [184]|</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>0, ???, [1, 5], (0.0, 'n/a'), [19]|</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>+1, ???, [2, 4], (0.0, 'n/a'), [109]|</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>???, +1, [2, 4], ('n/a', 0.001), [41]|</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>+1, ???, [2, 4], (0.001, 'n/a'), [134]|</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>+1, ???, [1, 5], (0.0, 'n/a'), [121]|</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="8" t="inlineStr">
+        <is>
+          <t>TFPR1_LIST_1</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>(1452.8359, 3045.7906, 4498.6265)</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>(1450.8394, 3046.7943, 4497.6338)</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>(2809.6692, 1688.9572, 4498.6264)</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>(1224.6604, 3046.7921, 4271.4526)</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>(3305.9408, 1192.6841, 4498.6249)</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>(751.3892, 3520.0639, 4271.4531)</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>(3175.8931, 1095.5588, 4271.452)</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>(1334.7568, 3050.7849, 4385.5417)</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>(1334.7568, 3049.7803, 4384.5371)</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>(1338.748, 2933.7088, 4272.4568)</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>(284.1971, 4214.428, 4498.6251)</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>(2602.5256, 1879.0767, 4481.6023)</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>(1450.8287, 3049.8027, 4500.6313)</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>(2809.6692, 1689.96, 4499.6293)</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>(1065.5966, 3434.0302, 4499.6268)</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>(3584.1372, 915.4897, 4499.6269)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="8" t="inlineStr">
+        <is>
+          <t>TFPR1_LIST_2</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>(1450.8287, 3047.798, 4498.6266)</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>(2618.5485, 1880.0787, 4498.6272)</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>(1334.7568, 2936.6965, 4271.4533)</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>(3521.0687, 977.5575, 4498.6262)</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>(3304.9368, 966.5161, 4271.4529)</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>(1334.7568, 2937.7007, 4272.4575)</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>(227.1757, 4271.4525, 4498.6282)</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>(1193.6919, 3306.9401, 4500.632)</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>(2935.7168, 1563.913, 4499.6298)</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>(1450.8287, 3048.7996, 4499.6282)</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>(3306.9443, 1192.6841, 4499.6283)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="8" t="inlineStr">
+        <is>
+          <t>TFPR1_LIST_3</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>(1322.7335, 3175.8931, 4498.6267)</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>(2934.7147, 1563.913, 4498.6276)</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>(1337.7446, 2933.7088, 4271.4534)</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>(3649.1645, 849.4619, 4498.6265)</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>(399.2242, 4099.404, 4498.6282)</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>(1451.8325, 3048.7996, 4500.6321)</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>(2619.5513, 1880.0787, 4499.63)</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>(1066.5993, 3433.0304, 4499.6297)</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>(3521.0687, 978.5605, 4499.6292)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AJ53"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>Bond</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="C1" s="8" t="inlineStr">
+        <is>
+          <t>Coverage=59.5%</t>
+        </is>
+      </c>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>(2,4) +2.01</t>
+        </is>
+      </c>
+      <c r="E1" s="8" t="inlineStr">
+        <is>
+          <t>(2,4) +3.01</t>
+        </is>
+      </c>
+      <c r="F1" s="8" t="inlineStr">
+        <is>
+          <t>(5,1) +2.01</t>
+        </is>
+      </c>
+      <c r="G1" s="8" t="inlineStr">
+        <is>
+          <t>(5,1) +1.01</t>
+        </is>
+      </c>
+      <c r="H1" s="8" t="inlineStr">
+        <is>
+          <t>(1,4) -225.17</t>
+        </is>
+      </c>
+      <c r="I1" s="8" t="inlineStr">
+        <is>
+          <t>(5,1) +3.01</t>
+        </is>
+      </c>
+      <c r="J1" s="8" t="inlineStr">
+        <is>
+          <t>(2,3) -225.16</t>
+        </is>
+      </c>
+      <c r="K1" s="8" t="inlineStr">
+        <is>
+          <t>(2,4) +1.01</t>
+        </is>
+      </c>
+      <c r="L1" s="8" t="inlineStr">
+        <is>
+          <t>(2,3) -226.17</t>
+        </is>
+      </c>
+      <c r="M1" s="8" t="inlineStr">
+        <is>
+          <t>(4,2) +2.01</t>
+        </is>
+      </c>
+      <c r="N1" s="8" t="inlineStr">
+        <is>
+          <t>(2,4) -16.00</t>
+        </is>
+      </c>
+      <c r="O1" s="8" t="inlineStr">
+        <is>
+          <t>(1,4) -226.17</t>
+        </is>
+      </c>
+      <c r="P1" s="8" t="inlineStr">
+        <is>
+          <t>(2,3) -224.16</t>
+        </is>
+      </c>
+      <c r="Q1" s="8" t="inlineStr">
+        <is>
+          <t>(1,5) +2.01</t>
+        </is>
+      </c>
+      <c r="R1" s="8" t="inlineStr">
+        <is>
+          <t>(4,2) +1.01</t>
+        </is>
+      </c>
+      <c r="S1" s="8" t="inlineStr">
+        <is>
+          <t>(4,2) +3.01</t>
+        </is>
+      </c>
+      <c r="T1" s="8" t="inlineStr">
+        <is>
+          <t>(2,4) +4.02</t>
+        </is>
+      </c>
+      <c r="U1" s="8" t="inlineStr">
+        <is>
+          <t>(4,1) -224.16</t>
+        </is>
+      </c>
+      <c r="V1" s="8" t="inlineStr">
+        <is>
+          <t>(4,1) -225.16</t>
+        </is>
+      </c>
+      <c r="W1" s="8" t="inlineStr">
+        <is>
+          <t>(4,1) -226.17</t>
+        </is>
+      </c>
+      <c r="X1" s="8" t="inlineStr">
+        <is>
+          <t>(2,4) -111.07</t>
+        </is>
+      </c>
+      <c r="Y1" s="8" t="inlineStr">
+        <is>
+          <t>(1,4) -224.16</t>
+        </is>
+      </c>
+      <c r="Z1" s="8" t="inlineStr">
+        <is>
+          <t>(1,4) -113.09</t>
+        </is>
+      </c>
+      <c r="AA1" s="8" t="inlineStr">
+        <is>
+          <t>(2,3) -112.08</t>
+        </is>
+      </c>
+      <c r="AB1" s="8" t="inlineStr">
+        <is>
+          <t>(2,4) -17.00</t>
+        </is>
+      </c>
+      <c r="AC1" s="8" t="inlineStr">
+        <is>
+          <t>(4,2) -15.00</t>
+        </is>
+      </c>
+      <c r="AD1" s="8" t="inlineStr">
+        <is>
+          <t>(4,2) -16.00</t>
+        </is>
+      </c>
+      <c r="AE1" s="8" t="inlineStr">
+        <is>
+          <t>(1,5) -60.03</t>
+        </is>
+      </c>
+      <c r="AF1" s="8" t="inlineStr">
+        <is>
+          <t>(4,2) +4.02</t>
+        </is>
+      </c>
+      <c r="AG1" s="8" t="inlineStr">
+        <is>
+          <t>(2,4) -14.99</t>
+        </is>
+      </c>
+      <c r="AH1" s="8" t="inlineStr">
+        <is>
+          <t>(2,3) -242.19</t>
+        </is>
+      </c>
+      <c r="AI1" s="8" t="inlineStr">
+        <is>
+          <t>Row Count</t>
+        </is>
+      </c>
+      <c r="AJ1" s="8" t="inlineStr">
+        <is>
+          <t>theoretical mass</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>b1, y36</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
@@ -823,10 +3039,18 @@
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
         <is>
           <t>(114.091, 4378.499)</t>
         </is>
@@ -845,7 +3069,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -861,7 +3085,11 @@
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>b2, y35+2, [1, 5], (0.0, 0.002), [196]</t>
+        </is>
+      </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
@@ -871,10 +3099,18 @@
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
         <is>
           <t>(227.175, 4265.414)</t>
         </is>
@@ -893,7 +3129,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -909,7 +3145,11 @@
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>b3, y34+2, [1, 5], (0.0, 0.001), [17]</t>
+        </is>
+      </c>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
@@ -919,10 +3159,18 @@
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
         <is>
           <t>(284.197, 4208.393)</t>
         </is>
@@ -941,7 +3189,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -957,7 +3205,11 @@
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>b4, y33+2, [1, 5], (0.001, 0.001), [19]</t>
+        </is>
+      </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
@@ -967,10 +3219,18 @@
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
         <is>
           <t>(399.224, 4093.366)</t>
         </is>
@@ -989,7 +3249,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -1005,7 +3265,11 @@
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>b5, y32+2, [1, 5], (0.0, 0.0), [266]</t>
+        </is>
+      </c>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
@@ -1015,10 +3279,18 @@
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
         <is>
           <t>(546.292, 3946.298)</t>
         </is>
@@ -1063,10 +3335,18 @@
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
         <is>
           <t>(693.361, 3799.229)</t>
         </is>
@@ -1088,22 +3368,38 @@
           <t>+</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>0, +1, [1, 5], (0.0, 0.002), [136]</t>
-        </is>
-      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>b7, y30+2, [1, 5], (0.001, 0.0), [238]</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>b7, y30+1, [1, 5], (0.001, 0.0), [165]</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(b7)-226.169, y30+2, [1, 4], (0.001, 0.0), [84]</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>b7, y30+3, [1, 5], (0.001, 0.0), [171]</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>(b7)-226.167, y30+1, [1, 4], (0.001, 0.003), [59]</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
@@ -1113,12 +3409,24 @@
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>(b7)-226.168, y30+3, [1, 4], (0.0, 0.001), [132]</t>
+        </is>
+      </c>
       <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
         <is>
           <t>(849.462, 3643.128)</t>
         </is>
@@ -1142,16 +3450,32 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0, +1, [1, 5], (0.001, 0.002), [37]</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+          <t>b8, y29+2, [2, 4], (0.0, 0.002), [173]</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>b8, y29+3, [2, 4], (0.0, 0.001), [369]</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>b8, y29+2, [1, 5], (0.001, 0.001), [21]</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>b8, y29+1, [1, 5], (0.001, 0.0), [38]</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(b8)-225.165, y29+1, [1, 4], (0.001, 0.002), [96]</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>(0)-226.169, +1, [1, 4], (0.002, 0.001), [32]</t>
+          <t>b8+1, y29+2, [1, 5], (0.001, 0.001), [140]</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
@@ -1161,7 +3485,7 @@
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
-          <t>+1, +1, [1, 5], (0.0, 0.002), [24]</t>
+          <t>(b8+1)-226.167, y29, [1, 4], (0.001, 0.003), [123]</t>
         </is>
       </c>
       <c r="P9" t="inlineStr"/>
@@ -1173,12 +3497,28 @@
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>(b8)-225.164, y29+2, [1, 4], (0.0, 0.002), [257]</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>(b8)-113.089, y29+1, [1, 4], (0.007, 0.002), [985]</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
         <is>
           <t>(977.557, 3515.033)</t>
         </is>
@@ -1202,27 +3542,47 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0, +1, [1, 5], (0.001, 0.002), [129]</t>
+          <t>b9, y28+2, [2, 4], (0.001, 0.0), [26]</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>+1, +1, [2, 4], (0.001, 0.0), [57]</t>
+          <t>b9, y28+3, [2, 4], (0.001, 0.003), [45]</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+1, 0, [2, 4], (0.001, 0.0), [145]</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
+          <t>b9+1, y28+1, [1, 5], (0.002, 0.001), [153]</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>b9, y28+1, [1, 5], (0.001, 0.001), [148]</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(b9)-226.169, y28+2, [1, 4], (0.001, 0.0), [521]</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>b9+1, y28+2, [1, 5], (0.002, 0.001), [380]</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>b9+1, y28, [2, 4], (0.0, 0.001), [178]</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>(b9)-18.01, y28+2, [2, 4], (0.0, 0.0), [151]</t>
+        </is>
+      </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
@@ -1235,10 +3595,22 @@
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="n">
-        <v>3</v>
-      </c>
+      <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr">
+        <is>
+          <t>(b9)-18.007, y28+1, [2, 4], (0.003, 0.001), [136]</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
         <is>
           <t>(1064.589, 3428.001)</t>
         </is>
@@ -1262,47 +3634,87 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0, +1, [1, 5], (0.0, 0.002), [169]</t>
+          <t>b10+1, y27+1, [2, 4], (0.0, 0.002), [3]</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>+1, +1, [2, 4], (0.0, 0.0), [3]</t>
+          <t>b10, y27+3, [2, 4], (0.001, 0.001), [47]</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+1, 0, [2, 4], (0.0, 0.001), [38]</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
+          <t>b10, y27+2, [1, 5], (0.001, 0.002), [72]</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>b10, y27+1, [1, 5], (0.001, 0.001), [217]</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>b10, y27+3, [1, 5], (0.001, 0.002), [234]</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>0, (0)-16.006, [2, 4], (0.0, 0.01), [224]</t>
-        </is>
-      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>b10+1, y27, [2, 4], (0.0, 0.002), [37]</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>b10, (y27)-16.003, [2, 4], (0.001, 0.011), [297]</t>
+        </is>
+      </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>b10+1, y27+3, [2, 4], (0.0, 0.001), [166]</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>(b10)-225.163, y27+2, [1, 4], (0.001, 0.002), [642]</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>(b10)-225.165, y27+1, [1, 4], (0.001, 0.002), [135]</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>(b10+1)-226.167, y27, [1, 4], (0.001, 0.002), [335]</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>(b10)-112.077, y27+1, [2, 4], (0.003, 0.002), [218]</t>
+        </is>
+      </c>
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
         <is>
           <t>(1192.684, 3299.906)</t>
         </is>
@@ -1326,47 +3738,91 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0, +1, [1, 5], (0.001, 0.002), [126]</t>
+          <t>b11, y26+2, [2, 4], (0.0, 0.001), [42]</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>+1, +1, [2, 4], (0.0, 0.0), [10]</t>
+          <t>b11, y26+3, [2, 4], (0.0, 0.001), [56]</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0, +1, [2, 4], (0.001, 0.0), [70]</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
+          <t>b11+1, y26+1, [1, 5], (0.001, 0.001), [94]</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>b11+1, y26, [1, 5], (0.001, 0.0), [493]</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>b11+1, y26+2, [1, 5], (0.001, 0.001), [268]</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>(0)-17.009, +1, [2, 4], (0.001, 0.0), [103]</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>b11, y26+1, [2, 4], (0.0, 0.002), [67]</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>(b11)-16.003, y26, [2, 4], (0.001, 0.002), [149]</t>
+        </is>
+      </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>(b11)-225.163, y26+2, [1, 4], (0.0, 0.001), [292]</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>(b11)-225.165, y26+1, [1, 4], (0.002, 0.002), [239]</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>(b11)-226.167, y26+1, [1, 4], (0.0, 0.002), [146]</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>(b11)-112.077, y26+1, [2, 4], (0.004, 0.002), [543]</t>
+        </is>
+      </c>
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="inlineStr"/>
-      <c r="AA12" t="n">
-        <v>4</v>
-      </c>
+      <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="inlineStr">
+        <is>
+          <t>(b11)-17.003, y26, [2, 4], (0.005, 0.002), [144]</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>(b11)-17.002, y26+2, [2, 4], (0.006, 0.001), [172]</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="n">
+        <v>13</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
         <is>
           <t>(1321.726, 3170.864)</t>
         </is>
@@ -1388,49 +3844,73 @@
           <t>+</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>b12+2, y25, [2, 4], (0.001, 0.0), [52]</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>+1, +1, [2, 4], (0.0, 0.001), [16]</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>???, +1, [2, 4], ('n/a', 0.001), [647]</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>(0)-226.168, +1, [2, 3], (0.0, 0.002), [150]</t>
-        </is>
-      </c>
+          <t>b12, y25+3, [2, 4], (0.0, 0.001), [68]</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>(b12)-225.164, y25+1, [2, 3], (0.0, 0.003), [182]</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>(0)-225.165, +1, [2, 3], (0.0, 0.002), [144]</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
+          <t>b12, y25+1, [2, 4], (0.0, 0.0), [27]</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>(b12)-226.167, y25+1, [2, 3], (0.001, 0.003), [177]</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>b12+1, (y25)-17.007, [2, 4], (0.001, 0.011), [579]</t>
+        </is>
+      </c>
       <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>(b12)-226.168, y25+3, [2, 3], (0.0, 0.001), [992]</t>
+        </is>
+      </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>b12+1, y25+3, [2, 4], (0.001, 0.001), [124]</t>
+        </is>
+      </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr"/>
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="inlineStr"/>
-      <c r="AA13" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB13" t="inlineStr">
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
         <is>
           <t>(1449.821, 3042.769)</t>
         </is>
@@ -1455,39 +3935,43 @@
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>(0)-226.168, +1, [2, 3], (0.0, 0.001), [276]</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>0, +1, [2, 4], (0.0, 0.0), [86]</t>
-        </is>
-      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>+1, +1, [2, 4], (0.0, 0.0), [22]</t>
+          <t>(b13)-226.167, y24+2, [2, 3], (0.001, 0.003), [102]</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>(b13)-226.167, y24+1, [2, 3], (0.001, 0.0), [345]</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>(0)-18.008, +1, [2, 4], (0.002, 0.0), [104]</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>(0)-17.005, +1, [2, 4], (0.002, 0.0), [189]</t>
-        </is>
-      </c>
+          <t>b13, y24+2, [2, 4], (0.0, 0.001), [6]</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>(b13)-225.164, y24+2, [2, 3], (0.0, 0.003), [661]</t>
+        </is>
+      </c>
       <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>b13, y24+1, [2, 4], (0.0, 0.002), [88]</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>b13, y24+3, [2, 4], (0.0, 0.0), [77]</t>
+        </is>
+      </c>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
@@ -1495,10 +3979,30 @@
       <c r="X14" t="inlineStr"/>
       <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="inlineStr"/>
-      <c r="AA14" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB14" t="inlineStr">
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>(b13)-16.004, y24+1, [2, 4], (0.0, 0.002), [245]</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>(b13)-15.999, y24, [2, 4], (0.005, 0.002), [116]</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>b13+1, y24+3, [2, 4], (0.0, 0.0), [577]</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr"/>
+      <c r="AI14" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
         <is>
           <t>(1562.905, 2929.685)</t>
         </is>
@@ -1524,22 +4028,30 @@
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>0, +1, [2, 4], (0.002, 0.001), [173]</t>
-        </is>
-      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>b14+1, y23+1, [2, 4], (0.0, 0.0), [147]</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>b14+1, y23, [2, 4], (0.0, 0.012), [582]</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>b14+1, y23+2, [2, 4], (0.0, 0.001), [180]</t>
+        </is>
+      </c>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr"/>
@@ -1547,10 +4059,18 @@
       <c r="X15" t="inlineStr"/>
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="inlineStr"/>
-      <c r="AA15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB15" t="inlineStr">
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr"/>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr"/>
+      <c r="AI15" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
         <is>
           <t>(1619.927, 2872.663)</t>
         </is>
@@ -1569,7 +4089,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -1578,10 +4098,22 @@
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>(b15)-226.167, y22+2, [2, 3], (0.002, 0.0), [394]</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>(b15)-226.167, y22+1, [2, 3], (0.002, 0.002), [448]</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>b15, y22+2, [2, 4], (0.001, 0.001), [249]</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
@@ -1595,10 +4127,18 @@
       <c r="X16" t="inlineStr"/>
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr"/>
-      <c r="AA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB16" t="inlineStr">
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr"/>
+      <c r="AE16" t="inlineStr"/>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="inlineStr"/>
+      <c r="AI16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
         <is>
           <t>(1748.022, 2744.568)</t>
         </is>
@@ -1624,34 +4164,34 @@
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>+1, 0, [2, 4], (0.001, 0.001), [13]</t>
-        </is>
-      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>+1, +1, [2, 4], (0.001, 0.001), [2]</t>
+          <t>(b16)-225.164, y21+1, [2, 3], (0.001, 0.0), [824]</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>(0)-17.004, 0, [2, 4], (0.002, 0.001), [192]</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>(0)-16.001, 0, [2, 4], (0.002, 0.001), [98]</t>
-        </is>
-      </c>
+          <t>b16+2, y21, [2, 4], (0.001, 0.0), [15]</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>b16+1, y21, [2, 4], (0.002, 0.0), [13]</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>b16+3, y21, [2, 4], (0.001, 0.0), [107]</t>
+        </is>
+      </c>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr"/>
@@ -1659,10 +4199,30 @@
       <c r="X17" t="inlineStr"/>
       <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="inlineStr"/>
-      <c r="AA17" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB17" t="inlineStr">
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>b16+1, (y21)-16.004, [2, 4], (0.002, 0.019), [244]</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>(b16)-15.999, y21, [2, 4], (0.003, 0.0), [105]</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr"/>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>b16, y21???, [2, 4], (0.003, 'n/a'), [185]</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="inlineStr"/>
+      <c r="AI17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
         <is>
           <t>(1877.064, 2615.526)</t>
         </is>
@@ -1707,10 +4267,18 @@
       <c r="X18" t="inlineStr"/>
       <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="inlineStr"/>
-      <c r="AA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB18" t="inlineStr">
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr"/>
+      <c r="AE18" t="inlineStr"/>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="inlineStr"/>
+      <c r="AI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
         <is>
           <t>(2024.133, 2468.457)</t>
         </is>
@@ -1755,10 +4323,18 @@
       <c r="X19" t="inlineStr"/>
       <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="inlineStr"/>
-      <c r="AA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB19" t="inlineStr">
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr"/>
+      <c r="AE19" t="inlineStr"/>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="inlineStr"/>
+      <c r="AH19" t="inlineStr"/>
+      <c r="AI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
         <is>
           <t>(2152.228, 2340.362)</t>
         </is>
@@ -1803,10 +4379,18 @@
       <c r="X20" t="inlineStr"/>
       <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="inlineStr"/>
-      <c r="AA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB20" t="inlineStr">
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr"/>
+      <c r="AC20" t="inlineStr"/>
+      <c r="AD20" t="inlineStr"/>
+      <c r="AE20" t="inlineStr"/>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="inlineStr"/>
+      <c r="AH20" t="inlineStr"/>
+      <c r="AI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
         <is>
           <t>(2308.329, 2184.261)</t>
         </is>
@@ -1851,10 +4435,18 @@
       <c r="X21" t="inlineStr"/>
       <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="inlineStr"/>
-      <c r="AA21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB21" t="inlineStr">
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="inlineStr"/>
+      <c r="AC21" t="inlineStr"/>
+      <c r="AD21" t="inlineStr"/>
+      <c r="AE21" t="inlineStr"/>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="inlineStr"/>
+      <c r="AH21" t="inlineStr"/>
+      <c r="AI21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
         <is>
           <t>(2421.413, 2071.177)</t>
         </is>
@@ -1899,10 +4491,18 @@
       <c r="X22" t="inlineStr"/>
       <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="inlineStr"/>
-      <c r="AA22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB22" t="inlineStr">
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr"/>
+      <c r="AC22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr"/>
+      <c r="AE22" t="inlineStr"/>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="inlineStr"/>
+      <c r="AH22" t="inlineStr"/>
+      <c r="AI22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
         <is>
           <t>(2520.481, 1972.109)</t>
         </is>
@@ -1947,10 +4547,18 @@
       <c r="X23" t="inlineStr"/>
       <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="inlineStr"/>
-      <c r="AA23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB23" t="inlineStr">
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr"/>
+      <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr"/>
+      <c r="AE23" t="inlineStr"/>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="inlineStr"/>
+      <c r="AH23" t="inlineStr"/>
+      <c r="AI23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
         <is>
           <t>(2648.54, 1844.05)</t>
         </is>
@@ -1975,35 +4583,39 @@
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>(+1)-226.168, 0, [3, 2], (0.004, 0.0), [180]</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>+1, 0, [4, 2], (0.001, 0.0), [89]</t>
-        </is>
-      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>+1, +1, [4, 2], (0.001, 0.0), [47]</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>(+1)-225.165, 0, [3, 2], (0.0, 0.0), [106]</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
+          <t>(b23+1)-225.164, y14, [3, 2], (0.0, 0.001), [117]</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>(b23)-226.167, y14+1, [3, 2], (0.0, 0.001), [99]</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>b23+2, y14, [4, 2], (0.001, 0.001), [61]</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr"/>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>b23+1, y14, [4, 2], (0.0, 0.001), [92]</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>b23+2, y14+1, [4, 2], (0.001, 0.001), [366]</t>
+        </is>
+      </c>
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="inlineStr"/>
@@ -2011,10 +4623,22 @@
       <c r="X24" t="inlineStr"/>
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="inlineStr"/>
-      <c r="AA24" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB24" t="inlineStr">
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>(b23+1)-112.08, y14, [3, 2], (0.002, 0.001), [337]</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr"/>
+      <c r="AE24" t="inlineStr"/>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="inlineStr"/>
+      <c r="AH24" t="inlineStr"/>
+      <c r="AI24" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
         <is>
           <t>(2804.641, 1687.949)</t>
         </is>
@@ -2059,10 +4683,18 @@
       <c r="X25" t="inlineStr"/>
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="inlineStr"/>
-      <c r="AA25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB25" t="inlineStr">
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="inlineStr"/>
+      <c r="AD25" t="inlineStr"/>
+      <c r="AE25" t="inlineStr"/>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="inlineStr"/>
+      <c r="AH25" t="inlineStr"/>
+      <c r="AI25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
         <is>
           <t>(2917.725, 1574.865)</t>
         </is>
@@ -2084,27 +4716,43 @@
           <t>+</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>b25, y12+2, [4, 2], (0.007, 0.0), [379]</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>+1, +1, [4, 2], (0.003, 0.0), [100]</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>+1, 0, [4, 2], (0.003, 0.001), [73]</t>
-        </is>
-      </c>
+          <t>b25+3, y12, [4, 2], (0.002, 0.0), [211]</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>(b25+1)-225.164, y12, [3, 2], (0.001, 0.0), [137]</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>b25, y12+1, [4, 2], (0.007, 0.001), [542]</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>(b25+1)-226.167, y12, [3, 2], (0.003, 0.0), [235]</t>
+        </is>
+      </c>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>b25, (y12+1)-224.161, [3, 2], (0.043, 0.041), [992]</t>
+        </is>
+      </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr"/>
@@ -2115,10 +4763,18 @@
       <c r="X26" t="inlineStr"/>
       <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="inlineStr"/>
-      <c r="AA26" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB26" t="inlineStr">
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr"/>
+      <c r="AC26" t="inlineStr"/>
+      <c r="AD26" t="inlineStr"/>
+      <c r="AE26" t="inlineStr"/>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="inlineStr"/>
+      <c r="AH26" t="inlineStr"/>
+      <c r="AI26" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
         <is>
           <t>(3045.82, 1446.77)</t>
         </is>
@@ -2140,65 +4796,85 @@
           <t>+</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>b26, y11+2, [4, 2], (0.001, 0.0), [141]</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>+1, +1, [4, 2], (0.0, 0.0), [52]</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>0, +1, [4, 2], (0.0, 0.0), [58]</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>(0)-226.168, +1, [3, 2], (0.002, 0.0), [21]</t>
-        </is>
-      </c>
+          <t>b26, y11+3, [4, 2], (0.001, 0.002), [526]</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>(b26+1)-225.164, y11, [3, 2], (0.003, 0.001), [1]</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>(+1)-225.165, 0, [3, 2], (0.003, 0.0), [1]</t>
+          <t>b26, y11+1, [4, 2], (0.001, 0.001), [57]</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>(0)-16.006, 0, [4, 2], (0.008, 0.0), [721]</t>
+          <t>(b26)-226.167, y11+1, [3, 2], (0.002, 0.001), [18]</t>
         </is>
       </c>
       <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>(b26)-17.007, y11+1, [4, 2], (0.004, 0.001), [937]</t>
+        </is>
+      </c>
       <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>(b26+1)-224.161, y11, [3, 2], (0.003, 0.001), [23]</t>
+        </is>
+      </c>
       <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>(0)-112.082, ???, [3, 2], (0.004, 'n/a'), [199]</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>(0)-113.085, ???, [3, 2], (0.002, 'n/a'), [125]</t>
-        </is>
-      </c>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr">
         <is>
-          <t>(+1)-224.161, 0, [3, 2], (0.002, 0.0), [23]</t>
+          <t>b26+2, y11+2, [4, 2], (0.001, 0.0), [782]</t>
         </is>
       </c>
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="inlineStr"/>
       <c r="W27" t="inlineStr"/>
-      <c r="X27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>(b26)-111.074, y11, [4, 2], (0.004, 0.001), [307]</t>
+        </is>
+      </c>
       <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="inlineStr"/>
-      <c r="AA27" t="n">
-        <v>8</v>
-      </c>
-      <c r="AB27" t="inlineStr">
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>(b26+1)-112.08, y11, [3, 2], (0.001, 0.001), [65]</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr"/>
+      <c r="AC27" t="inlineStr"/>
+      <c r="AD27" t="inlineStr"/>
+      <c r="AE27" t="inlineStr"/>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="inlineStr"/>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>(b26)-242.188, y11+1, [3, 2], (0.004, 0.001), [594]</t>
+        </is>
+      </c>
+      <c r="AI27" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
         <is>
           <t>(3160.847, 1331.743)</t>
         </is>
@@ -2243,10 +4919,18 @@
       <c r="X28" t="inlineStr"/>
       <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="inlineStr"/>
-      <c r="AA28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB28" t="inlineStr">
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr"/>
+      <c r="AD28" t="inlineStr"/>
+      <c r="AE28" t="inlineStr"/>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="inlineStr"/>
+      <c r="AH28" t="inlineStr"/>
+      <c r="AI28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
         <is>
           <t>(3307.915, 1184.675)</t>
         </is>
@@ -2291,10 +4975,18 @@
       <c r="X29" t="inlineStr"/>
       <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="inlineStr"/>
-      <c r="AA29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB29" t="inlineStr">
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr"/>
+      <c r="AE29" t="inlineStr"/>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="inlineStr"/>
+      <c r="AH29" t="inlineStr"/>
+      <c r="AI29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
         <is>
           <t>(3420.999, 1071.59)</t>
         </is>
@@ -2316,45 +5008,69 @@
           <t>+</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>+1, 0, [5, 1], (0.004, 0.0), [153]</t>
-        </is>
-      </c>
+      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>b29+1, y8+1, [5, 1], (0.002, 0.0), [79]</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>b29+1, y8, [5, 1], (0.002, 0.001), [194]</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>b29+3, (y8)-227.172, [4, 1], (0.045, 0.046), [184]</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>b29+3, y8, [5, 1], (0.003, 0.001), [83]</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>+1, +1, [5, 1], (0.004, 0.0), [77]</t>
-        </is>
-      </c>
+      <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>(+1)-225.167, 0, [4, 1], (0.0, 0.0), [84]</t>
-        </is>
-      </c>
+      <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
-      <c r="W30" t="inlineStr"/>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>(b29+1)-224.16, y8, [4, 1], (0.001, 0.008), [419]</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>(b29+1)-225.165, y8, [4, 1], (0.0, 0.001), [86]</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>(b29+1)-226.167, y8, [4, 1], (0.002, 0.001), [130]</t>
+        </is>
+      </c>
       <c r="X30" t="inlineStr"/>
       <c r="Y30" t="inlineStr"/>
       <c r="Z30" t="inlineStr"/>
-      <c r="AA30" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB30" t="inlineStr">
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="inlineStr"/>
+      <c r="AD30" t="inlineStr"/>
+      <c r="AE30" t="inlineStr"/>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="inlineStr"/>
+      <c r="AH30" t="inlineStr"/>
+      <c r="AI30" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
         <is>
           <t>(3577.1, 915.489)</t>
         </is>
@@ -2376,18 +5092,26 @@
           <t>+</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>+1, 0, [5, 1], (0.002, 0.0), [137]</t>
-        </is>
-      </c>
+      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>b30+2, y7, [5, 1], (0.003, 0.0), [104]</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>b30+1, y7, [5, 1], (0.0, 0.0), [163]</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(b30+1)-225.165, y7, [4, 1], (0.0, 0.0), [159]</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>(+1)-226.169, 0, [4, 1], (0.0, 0.0), [227]</t>
+          <t>b30+3, y7, [5, 1], (0.001, 0.0), [216]</t>
         </is>
       </c>
       <c r="J31" t="inlineStr"/>
@@ -2395,12 +5119,12 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>(+1)-225.167, 0, [4, 1], (0.0, 0.0), [131]</t>
-        </is>
-      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>(b30+1)-226.167, y7, [4, 1], (0.001, 0.0), [305]</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr"/>
@@ -2409,12 +5133,32 @@
       <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr"/>
       <c r="X31" t="inlineStr"/>
-      <c r="Y31" t="inlineStr"/>
-      <c r="Z31" t="inlineStr"/>
-      <c r="AA31" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB31" t="inlineStr">
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>(b30+1)-224.161, y7, [4, 1], (0.004, 0.0), [206]</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>(b30+1)-113.089, y7, [4, 1], (0.006, 0.0), [492]</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr"/>
+      <c r="AB31" t="inlineStr"/>
+      <c r="AC31" t="inlineStr"/>
+      <c r="AD31" t="inlineStr"/>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>b30+2, (y7)-62.041, [5, 1], (0.025, 0.019), [168]</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="inlineStr"/>
+      <c r="AH31" t="inlineStr"/>
+      <c r="AI31" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
         <is>
           <t>(3691.143, 801.446)</t>
         </is>
@@ -2433,14 +5177,18 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(b31+1)-225.165, y6, [4, 1], (0.0, 0.001), [184]</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
@@ -2459,10 +5207,18 @@
       <c r="X32" t="inlineStr"/>
       <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="inlineStr"/>
-      <c r="AA32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB32" t="inlineStr">
+      <c r="AA32" t="inlineStr"/>
+      <c r="AB32" t="inlineStr"/>
+      <c r="AC32" t="inlineStr"/>
+      <c r="AD32" t="inlineStr"/>
+      <c r="AE32" t="inlineStr"/>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="inlineStr"/>
+      <c r="AH32" t="inlineStr"/>
+      <c r="AI32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
         <is>
           <t>(3804.227, 688.362)</t>
         </is>
@@ -2488,23 +5244,23 @@
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>(+1)-226.169, 0, [4, 1], (0.002, 0.001), [259]</t>
-        </is>
-      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(b32+1)-225.165, y5, [4, 1], (0.003, 0.001), [281]</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>(+1)-225.167, 0, [4, 1], (0.003, 0.001), [204]</t>
-        </is>
-      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>(b32+1)-226.167, y5, [4, 1], (0.001, 0.001), [356]</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr"/>
@@ -2515,10 +5271,22 @@
       <c r="X33" t="inlineStr"/>
       <c r="Y33" t="inlineStr"/>
       <c r="Z33" t="inlineStr"/>
-      <c r="AA33" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB33" t="inlineStr">
+      <c r="AA33" t="inlineStr"/>
+      <c r="AB33" t="inlineStr"/>
+      <c r="AC33" t="inlineStr"/>
+      <c r="AD33" t="inlineStr"/>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>(b32)-60.034, y5, [5, 1], (0.008, 0.001), [294]</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="inlineStr"/>
+      <c r="AH33" t="inlineStr"/>
+      <c r="AI33" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
         <is>
           <t>(3903.296, 589.294)</t>
         </is>
@@ -2563,10 +5331,18 @@
       <c r="X34" t="inlineStr"/>
       <c r="Y34" t="inlineStr"/>
       <c r="Z34" t="inlineStr"/>
-      <c r="AA34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB34" t="inlineStr">
+      <c r="AA34" t="inlineStr"/>
+      <c r="AB34" t="inlineStr"/>
+      <c r="AC34" t="inlineStr"/>
+      <c r="AD34" t="inlineStr"/>
+      <c r="AE34" t="inlineStr"/>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="inlineStr"/>
+      <c r="AH34" t="inlineStr"/>
+      <c r="AI34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
         <is>
           <t>(4000.349, 492.241)</t>
         </is>
@@ -2611,10 +5387,18 @@
       <c r="X35" t="inlineStr"/>
       <c r="Y35" t="inlineStr"/>
       <c r="Z35" t="inlineStr"/>
-      <c r="AA35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB35" t="inlineStr">
+      <c r="AA35" t="inlineStr"/>
+      <c r="AB35" t="inlineStr"/>
+      <c r="AC35" t="inlineStr"/>
+      <c r="AD35" t="inlineStr"/>
+      <c r="AE35" t="inlineStr"/>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="inlineStr"/>
+      <c r="AH35" t="inlineStr"/>
+      <c r="AI35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
         <is>
           <t>(4156.45, 336.14)</t>
         </is>
@@ -2659,10 +5443,18 @@
       <c r="X36" t="inlineStr"/>
       <c r="Y36" t="inlineStr"/>
       <c r="Z36" t="inlineStr"/>
-      <c r="AA36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB36" t="inlineStr">
+      <c r="AA36" t="inlineStr"/>
+      <c r="AB36" t="inlineStr"/>
+      <c r="AC36" t="inlineStr"/>
+      <c r="AD36" t="inlineStr"/>
+      <c r="AE36" t="inlineStr"/>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="inlineStr"/>
+      <c r="AH36" t="inlineStr"/>
+      <c r="AI36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
         <is>
           <t>(4257.497, 235.092)</t>
         </is>
@@ -2707,10 +5499,18 @@
       <c r="X37" t="inlineStr"/>
       <c r="Y37" t="inlineStr"/>
       <c r="Z37" t="inlineStr"/>
-      <c r="AA37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB37" t="inlineStr">
+      <c r="AA37" t="inlineStr"/>
+      <c r="AB37" t="inlineStr"/>
+      <c r="AC37" t="inlineStr"/>
+      <c r="AD37" t="inlineStr"/>
+      <c r="AE37" t="inlineStr"/>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="inlineStr"/>
+      <c r="AH37" t="inlineStr"/>
+      <c r="AI37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ37" t="inlineStr">
         <is>
           <t>(4386.54, 106.05)</t>
         </is>
@@ -2736,75 +5536,99 @@
         <v>7</v>
       </c>
       <c r="E38" t="n">
+        <v>7</v>
+      </c>
+      <c r="F38" t="n">
+        <v>7</v>
+      </c>
+      <c r="G38" t="n">
+        <v>7</v>
+      </c>
+      <c r="H38" t="n">
+        <v>7</v>
+      </c>
+      <c r="I38" t="n">
+        <v>7</v>
+      </c>
+      <c r="J38" t="n">
+        <v>7</v>
+      </c>
+      <c r="K38" t="n">
         <v>6</v>
       </c>
-      <c r="F38" t="n">
+      <c r="L38" t="n">
         <v>6</v>
       </c>
-      <c r="G38" t="n">
+      <c r="M38" t="n">
+        <v>5</v>
+      </c>
+      <c r="N38" t="n">
+        <v>5</v>
+      </c>
+      <c r="O38" t="n">
         <v>4</v>
       </c>
-      <c r="H38" t="n">
+      <c r="P38" t="n">
         <v>4</v>
       </c>
-      <c r="I38" t="n">
+      <c r="Q38" t="n">
+        <v>4</v>
+      </c>
+      <c r="R38" t="n">
+        <v>4</v>
+      </c>
+      <c r="S38" t="n">
+        <v>4</v>
+      </c>
+      <c r="T38" t="n">
         <v>3</v>
       </c>
-      <c r="J38" t="n">
+      <c r="U38" t="n">
         <v>3</v>
       </c>
-      <c r="K38" t="n">
+      <c r="V38" t="n">
         <v>3</v>
       </c>
-      <c r="L38" t="n">
+      <c r="W38" t="n">
         <v>3</v>
       </c>
-      <c r="M38" t="n">
+      <c r="X38" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z38" t="n">
         <v>2</v>
       </c>
-      <c r="N38" t="n">
+      <c r="AA38" t="n">
         <v>2</v>
       </c>
-      <c r="O38" t="n">
+      <c r="AB38" t="n">
         <v>2</v>
       </c>
-      <c r="P38" t="n">
+      <c r="AC38" t="n">
         <v>2</v>
       </c>
-      <c r="Q38" t="n">
+      <c r="AD38" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG38" t="n">
         <v>1</v>
       </c>
-      <c r="R38" t="n">
+      <c r="AH38" t="n">
         <v>1</v>
       </c>
-      <c r="S38" t="n">
-        <v>1</v>
-      </c>
-      <c r="T38" t="n">
-        <v>1</v>
-      </c>
-      <c r="U38" t="n">
-        <v>0</v>
-      </c>
-      <c r="V38" t="n">
-        <v>0</v>
-      </c>
-      <c r="W38" t="n">
-        <v>0</v>
-      </c>
-      <c r="X38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA38" t="n">
+      <c r="AI38" t="n">
         <v>36</v>
       </c>
-      <c r="AB38" t="n">
+      <c r="AJ38" t="n">
         <v>36</v>
       </c>
     </row>
@@ -2817,76 +5641,100 @@
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="n">
+        <v>19</v>
+      </c>
+      <c r="E39" t="n">
+        <v>20</v>
+      </c>
+      <c r="F39" t="n">
+        <v>13</v>
+      </c>
+      <c r="G39" t="n">
+        <v>11</v>
+      </c>
+      <c r="H39" t="n">
+        <v>8</v>
+      </c>
+      <c r="I39" t="n">
         <v>9</v>
       </c>
-      <c r="E39" t="n">
-        <v>17</v>
-      </c>
-      <c r="F39" t="n">
+      <c r="J39" t="n">
         <v>12</v>
       </c>
-      <c r="G39" t="n">
+      <c r="K39" t="n">
+        <v>14</v>
+      </c>
+      <c r="L39" t="n">
+        <v>9</v>
+      </c>
+      <c r="M39" t="n">
+        <v>12</v>
+      </c>
+      <c r="N39" t="n">
+        <v>8</v>
+      </c>
+      <c r="O39" t="n">
+        <v>5</v>
+      </c>
+      <c r="P39" t="n">
         <v>6</v>
       </c>
-      <c r="H39" t="n">
-        <v>7</v>
-      </c>
-      <c r="I39" t="n">
-        <v>3</v>
-      </c>
-      <c r="J39" t="n">
+      <c r="Q39" t="n">
+        <v>5</v>
+      </c>
+      <c r="R39" t="n">
         <v>9</v>
       </c>
-      <c r="K39" t="n">
-        <v>8</v>
-      </c>
-      <c r="L39" t="n">
-        <v>5</v>
-      </c>
-      <c r="M39" t="n">
-        <v>3</v>
-      </c>
-      <c r="N39" t="n">
-        <v>5</v>
-      </c>
-      <c r="O39" t="n">
-        <v>9</v>
-      </c>
-      <c r="P39" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q39" t="n">
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="n">
+        <v>6</v>
+      </c>
+      <c r="U39" t="n">
         <v>4</v>
-      </c>
-      <c r="R39" t="n">
-        <v>3</v>
-      </c>
-      <c r="S39" t="n">
-        <v>3</v>
-      </c>
-      <c r="T39" t="n">
-        <v>4</v>
-      </c>
-      <c r="U39" t="n">
-        <v>3</v>
       </c>
       <c r="V39" t="n">
         <v>5</v>
       </c>
       <c r="W39" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="X39" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y39" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="Z39" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA39" t="inlineStr"/>
-      <c r="AB39" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI39" t="inlineStr"/>
+      <c r="AJ39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
@@ -2921,52 +5769,76 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z40" t="n">
         <v>1</v>
       </c>
-      <c r="M40" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" t="n">
+      <c r="AA40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="n">
         <v>2</v>
       </c>
-      <c r="O40" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
-      <c r="R40" t="n">
-        <v>0</v>
-      </c>
-      <c r="S40" t="n">
-        <v>0</v>
-      </c>
-      <c r="T40" t="n">
-        <v>0</v>
-      </c>
-      <c r="U40" t="n">
-        <v>0</v>
-      </c>
-      <c r="V40" t="n">
-        <v>4</v>
-      </c>
-      <c r="W40" t="n">
-        <v>2</v>
-      </c>
-      <c r="X40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA40" t="inlineStr"/>
-      <c r="AB40" t="inlineStr"/>
+      <c r="AI40" t="inlineStr"/>
+      <c r="AJ40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
@@ -2980,10 +5852,10 @@
         <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -2995,10 +5867,10 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -3010,43 +5882,67 @@
         <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
         <v>2</v>
       </c>
       <c r="U41" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA41" t="inlineStr"/>
-      <c r="AB41" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI41" t="inlineStr"/>
+      <c r="AJ41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="8" t="inlineStr">
@@ -3059,7 +5955,7 @@
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>(np.float64(725.41971821), np.float64(761.94949729), [np.float64(2.0), np.float64(4.0)], np.float64(292.0))</t>
+          <t>(np.float64(749.60447243), np.float64(750.10552478), [np.float64(2.0), np.float64(4.0)], np.float64(191.0))</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
@@ -3068,17 +5964,9 @@
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>(np.float64(652.36145807), np.float64(793.973287), [np.float64(2.0), np.float64(4.0)], np.float64(35.0))</t>
-        </is>
-      </c>
+      <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>(np.float64(655.13850436), np.float64(930.03167634), [np.float64(4.0), np.float64(2.0)], np.float64(43.0))</t>
-        </is>
-      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr"/>
@@ -3086,25 +5974,33 @@
       <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr"/>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>(np.float64(746.76848202), np.float64(747.26890317), [np.float64(4.0), np.float64(2.0)], np.float64(898.0))</t>
-        </is>
-      </c>
-      <c r="W42" t="inlineStr">
-        <is>
-          <t>(np.float64(667.37839561), np.float64(791.46927924), [np.float64(2.0), np.float64(4.0)], np.float64(486.0))</t>
-        </is>
-      </c>
+      <c r="V42" t="inlineStr"/>
+      <c r="W42" t="inlineStr"/>
       <c r="X42" t="inlineStr"/>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>(np.float64(749.60417422), np.float64(750.10522637), [np.float64(2.0), np.float64(4.0)], np.float64(156.0))</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr"/>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>(np.float64(854.49133634), np.float64(882.25668732), [np.float64(1.0), np.float64(4.0)], np.float64(900.0))</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr"/>
       <c r="AB42" t="inlineStr"/>
+      <c r="AC42" t="inlineStr"/>
+      <c r="AD42" t="inlineStr"/>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>(np.float64(199.18076157), np.float64(847.48236744), [np.float64(1.0), np.float64(5.0)], np.float64(585.0))</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="inlineStr"/>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>(np.float64(612.33046753), np.float64(1009.92284968), [np.float64(2.0), np.float64(3.0)], np.float64(200.0))</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr"/>
+      <c r="AJ42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
@@ -3124,11 +6020,7 @@
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>(np.float64(733.67866521), np.float64(772.95160064), [np.float64(4.0), np.float64(2.0)], np.float64(127.0))</t>
-        </is>
-      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr"/>
@@ -3136,21 +6028,25 @@
       <c r="S43" t="inlineStr"/>
       <c r="T43" t="inlineStr"/>
       <c r="U43" t="inlineStr"/>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>(np.float64(655.38912494), np.float64(930.03167634), [np.float64(4.0), np.float64(2.0)], np.float64(193.0))</t>
-        </is>
-      </c>
-      <c r="W43" t="inlineStr">
-        <is>
-          <t>(np.float64(597.84923948), np.float64(826.23420531), [np.float64(2.0), np.float64(4.0)], np.float64(133.0))</t>
-        </is>
-      </c>
+      <c r="V43" t="inlineStr"/>
+      <c r="W43" t="inlineStr"/>
       <c r="X43" t="inlineStr"/>
       <c r="Y43" t="inlineStr"/>
       <c r="Z43" t="inlineStr"/>
       <c r="AA43" t="inlineStr"/>
       <c r="AB43" t="inlineStr"/>
+      <c r="AC43" t="inlineStr"/>
+      <c r="AD43" t="inlineStr"/>
+      <c r="AE43" t="inlineStr"/>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="inlineStr"/>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>(np.float64(612.83236088), np.float64(1009.58849011), [np.float64(2.0), np.float64(3.0)], np.float64(210.0))</t>
+        </is>
+      </c>
+      <c r="AI43" t="inlineStr"/>
+      <c r="AJ43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
@@ -3178,17 +6074,21 @@
       <c r="S44" t="inlineStr"/>
       <c r="T44" t="inlineStr"/>
       <c r="U44" t="inlineStr"/>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>(np.float64(655.13850436), np.float64(930.53294749), [np.float64(4.0), np.float64(2.0)], np.float64(83.0))</t>
-        </is>
-      </c>
+      <c r="V44" t="inlineStr"/>
       <c r="W44" t="inlineStr"/>
       <c r="X44" t="inlineStr"/>
       <c r="Y44" t="inlineStr"/>
       <c r="Z44" t="inlineStr"/>
       <c r="AA44" t="inlineStr"/>
       <c r="AB44" t="inlineStr"/>
+      <c r="AC44" t="inlineStr"/>
+      <c r="AD44" t="inlineStr"/>
+      <c r="AE44" t="inlineStr"/>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="inlineStr"/>
+      <c r="AH44" t="inlineStr"/>
+      <c r="AI44" t="inlineStr"/>
+      <c r="AJ44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
@@ -3201,7 +6101,7 @@
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>(np.float64(1450.8394), np.float64(3047.798), np.float64(4498.6374))</t>
+          <t>(np.float64(1499.2089), np.float64(3000.4221), np.float64(4499.631))</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
@@ -3210,17 +6110,9 @@
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>(np.float64(1304.7229), np.float64(3175.8931), np.float64(4480.6161))</t>
-        </is>
-      </c>
+      <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>(np.float64(2620.554), np.float64(1860.0634), np.float64(4480.6174))</t>
-        </is>
-      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr"/>
@@ -3228,25 +6120,33 @@
       <c r="S45" t="inlineStr"/>
       <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr"/>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>(np.float64(2987.0739), np.float64(1494.5378), np.float64(4481.6117))</t>
-        </is>
-      </c>
-      <c r="W45" t="inlineStr">
-        <is>
-          <t>(np.float64(1334.7568), np.float64(3165.8771), np.float64(4500.6339))</t>
-        </is>
-      </c>
+      <c r="V45" t="inlineStr"/>
+      <c r="W45" t="inlineStr"/>
       <c r="X45" t="inlineStr"/>
-      <c r="Y45" t="inlineStr">
-        <is>
-          <t>(np.float64(1499.2083), np.float64(3000.4209), np.float64(4499.6293))</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr"/>
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>(np.float64(854.4913), np.float64(3529.0267), np.float64(4383.5181))</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr"/>
       <c r="AB45" t="inlineStr"/>
+      <c r="AC45" t="inlineStr"/>
+      <c r="AD45" t="inlineStr"/>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>(np.float64(199.1808), np.float64(4237.4118), np.float64(4436.5926))</t>
+        </is>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="inlineStr"/>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>(np.float64(1224.6609), np.float64(3029.7685), np.float64(4254.4295))</t>
+        </is>
+      </c>
+      <c r="AI45" t="inlineStr"/>
+      <c r="AJ45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
@@ -3266,11 +6166,7 @@
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>(np.float64(2934.7147), np.float64(1545.9032), np.float64(4480.6179))</t>
-        </is>
-      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr"/>
@@ -3278,21 +6174,25 @@
       <c r="S46" t="inlineStr"/>
       <c r="T46" t="inlineStr"/>
       <c r="U46" t="inlineStr"/>
-      <c r="V46" t="inlineStr">
-        <is>
-          <t>(np.float64(2621.5565), np.float64(1860.0634), np.float64(4481.6199))</t>
-        </is>
-      </c>
-      <c r="W46" t="inlineStr">
-        <is>
-          <t>(np.float64(1195.6985), np.float64(3304.9368), np.float64(4500.6353))</t>
-        </is>
-      </c>
+      <c r="V46" t="inlineStr"/>
+      <c r="W46" t="inlineStr"/>
       <c r="X46" t="inlineStr"/>
       <c r="Y46" t="inlineStr"/>
       <c r="Z46" t="inlineStr"/>
       <c r="AA46" t="inlineStr"/>
       <c r="AB46" t="inlineStr"/>
+      <c r="AC46" t="inlineStr"/>
+      <c r="AD46" t="inlineStr"/>
+      <c r="AE46" t="inlineStr"/>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="inlineStr"/>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>(np.float64(1225.6647), np.float64(3028.7655), np.float64(4254.4302))</t>
+        </is>
+      </c>
+      <c r="AI46" t="inlineStr"/>
+      <c r="AJ46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
@@ -3320,17 +6220,21 @@
       <c r="S47" t="inlineStr"/>
       <c r="T47" t="inlineStr"/>
       <c r="U47" t="inlineStr"/>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t>(np.float64(2620.554), np.float64(1861.0659), np.float64(4481.6199))</t>
-        </is>
-      </c>
+      <c r="V47" t="inlineStr"/>
       <c r="W47" t="inlineStr"/>
       <c r="X47" t="inlineStr"/>
       <c r="Y47" t="inlineStr"/>
       <c r="Z47" t="inlineStr"/>
       <c r="AA47" t="inlineStr"/>
       <c r="AB47" t="inlineStr"/>
+      <c r="AC47" t="inlineStr"/>
+      <c r="AD47" t="inlineStr"/>
+      <c r="AE47" t="inlineStr"/>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="inlineStr"/>
+      <c r="AH47" t="inlineStr"/>
+      <c r="AI47" t="inlineStr"/>
+      <c r="AJ47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
@@ -3341,94 +6245,46 @@
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>???, 0, [2, 4], ('n/a', 0.002), [51]|</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>???, +1, [2, 4], ('n/a', 0.001), [647]|</t>
-        </is>
-      </c>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>???, 0, [4, 2], ('n/a', 0.0), [62]|</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>(0)-226.168, ???, [2, 3], (0.0, 'n/a'), [147]|</t>
-        </is>
-      </c>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>0, ???, [1, 5], (0.0, 'n/a'), [71]|</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>(0)-226.17, ???, [1, 4], (0.003, 'n/a'), [18]|</t>
-        </is>
-      </c>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>(0)-226.17, ???, [1, 4], (0.003, 'n/a'), [110]|</t>
-        </is>
-      </c>
-      <c r="R48" t="inlineStr">
-        <is>
-          <t>(0)-112.082, ???, [3, 2], (0.004, 'n/a'), [199]|</t>
-        </is>
-      </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>(0)-113.085, ???, [3, 2], (0.002, 'n/a'), [125]|</t>
-        </is>
-      </c>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="inlineStr"/>
       <c r="T48" t="inlineStr">
         <is>
-          <t>(0)-225.165, ???, [2, 3], (0.0, 'n/a'), [410]|</t>
-        </is>
-      </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>0, ???, [1, 5], (0.0, 'n/a'), [17]|</t>
-        </is>
-      </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>+1, ???, [2, 4], (0.001, 'n/a'), [215]|</t>
-        </is>
-      </c>
-      <c r="W48" t="inlineStr">
-        <is>
-          <t>0, ???, [2, 4], (0.0, 'n/a'), [859]|</t>
-        </is>
-      </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>???, +1, [4, 2], ('n/a', 0.0), [271]|</t>
-        </is>
-      </c>
-      <c r="Y48" t="inlineStr">
-        <is>
-          <t>0, ???, [2, 4], (0.0, 'n/a'), [44]|</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>???, 0, [5, 1], ('n/a', 0.0), [81]|</t>
-        </is>
-      </c>
+          <t>b10, y27???, [2, 4], (0.001, 'n/a'), [125]|</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr"/>
+      <c r="V48" t="inlineStr"/>
+      <c r="W48" t="inlineStr"/>
+      <c r="X48" t="inlineStr"/>
+      <c r="Y48" t="inlineStr"/>
+      <c r="Z48" t="inlineStr"/>
       <c r="AA48" t="inlineStr"/>
       <c r="AB48" t="inlineStr"/>
+      <c r="AC48" t="inlineStr"/>
+      <c r="AD48" t="inlineStr"/>
+      <c r="AE48" t="inlineStr"/>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>b13, y24???, [2, 4], (0.0, 'n/a'), [298]|</t>
+        </is>
+      </c>
+      <c r="AG48" t="inlineStr"/>
+      <c r="AH48" t="inlineStr"/>
+      <c r="AI48" t="inlineStr"/>
+      <c r="AJ48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
@@ -3439,74 +6295,46 @@
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>0, ???, [2, 4], (0.0, 'n/a'), [4]|</t>
-        </is>
-      </c>
+      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>???, 0, [2, 4], ('n/a', 0.001), [15]|</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>(0)-226.168, ???, [3, 2], (0.002, 'n/a'), [75]|</t>
-        </is>
-      </c>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>0, ???, [1, 5], (0.001, 'n/a'), [20]|</t>
-        </is>
-      </c>
+      <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>(0)-226.17, ???, [1, 4], (0.003, 'n/a'), [50]|</t>
-        </is>
-      </c>
+      <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr">
         <is>
-          <t>(0)-225.165, ???, [3, 2], (0.003, 'n/a'), [90]|</t>
-        </is>
-      </c>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>0, ???, [1, 5], (0.0, 'n/a'), [148]|</t>
-        </is>
-      </c>
+          <t>b26???, y11, [4, 2], ('n/a', 0.001), [82]|</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr"/>
       <c r="V49" t="inlineStr"/>
-      <c r="W49" t="inlineStr">
-        <is>
-          <t>0, ???, [2, 4], (0.0, 'n/a'), [112]|</t>
-        </is>
-      </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>0, ???, [2, 4], (0.0, 'n/a'), [74]|</t>
-        </is>
-      </c>
-      <c r="Y49" t="inlineStr">
-        <is>
-          <t>0, ???, [2, 4], (0.0, 'n/a'), [67]|</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>0, ???, [1, 5], (0.0, 'n/a'), [183]|</t>
-        </is>
-      </c>
+      <c r="W49" t="inlineStr"/>
+      <c r="X49" t="inlineStr"/>
+      <c r="Y49" t="inlineStr"/>
+      <c r="Z49" t="inlineStr"/>
       <c r="AA49" t="inlineStr"/>
       <c r="AB49" t="inlineStr"/>
+      <c r="AC49" t="inlineStr"/>
+      <c r="AD49" t="inlineStr"/>
+      <c r="AE49" t="inlineStr"/>
+      <c r="AF49" t="inlineStr">
+        <is>
+          <t>b16, y21???, [2, 4], (0.003, 'n/a'), [185]|</t>
+        </is>
+      </c>
+      <c r="AG49" t="inlineStr"/>
+      <c r="AH49" t="inlineStr"/>
+      <c r="AI49" t="inlineStr"/>
+      <c r="AJ49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
@@ -3517,66 +6345,38 @@
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>0, ???, [2, 4], (0.001, 'n/a'), [42]|</t>
-        </is>
-      </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>0, ???, [2, 4], (0.0, 'n/a'), [5]|</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>(0)-226.168, ???, [2, 3], (0.0, 'n/a'), [94]|</t>
-        </is>
-      </c>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>0, ???, [1, 5], (0.0, 'n/a'), [184]|</t>
-        </is>
-      </c>
+      <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
       <c r="S50" t="inlineStr"/>
       <c r="T50" t="inlineStr"/>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>0, ???, [1, 5], (0.0, 'n/a'), [19]|</t>
-        </is>
-      </c>
+      <c r="U50" t="inlineStr"/>
       <c r="V50" t="inlineStr"/>
-      <c r="W50" t="inlineStr">
-        <is>
-          <t>+1, ???, [2, 4], (0.0, 'n/a'), [109]|</t>
-        </is>
-      </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>???, +1, [2, 4], ('n/a', 0.001), [41]|</t>
-        </is>
-      </c>
-      <c r="Y50" t="inlineStr">
-        <is>
-          <t>+1, ???, [2, 4], (0.001, 'n/a'), [134]|</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>+1, ???, [1, 5], (0.0, 'n/a'), [121]|</t>
-        </is>
-      </c>
+      <c r="W50" t="inlineStr"/>
+      <c r="X50" t="inlineStr"/>
+      <c r="Y50" t="inlineStr"/>
+      <c r="Z50" t="inlineStr"/>
       <c r="AA50" t="inlineStr"/>
       <c r="AB50" t="inlineStr"/>
+      <c r="AC50" t="inlineStr"/>
+      <c r="AD50" t="inlineStr"/>
+      <c r="AE50" t="inlineStr"/>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="inlineStr"/>
+      <c r="AH50" t="inlineStr"/>
+      <c r="AI50" t="inlineStr"/>
+      <c r="AJ50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
@@ -3587,94 +6387,46 @@
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>(1452.8359, 3045.7906, 4498.6265)</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>(1450.8394, 3046.7943, 4497.6338)</t>
-        </is>
-      </c>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>(2809.6692, 1688.9572, 4498.6264)</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>(1224.6604, 3046.7921, 4271.4526)</t>
-        </is>
-      </c>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>(3305.9408, 1192.6841, 4498.6249)</t>
-        </is>
-      </c>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>(751.3892, 3520.0639, 4271.4531)</t>
-        </is>
-      </c>
-      <c r="Q51" t="inlineStr">
-        <is>
-          <t>(3175.8931, 1095.5588, 4271.452)</t>
-        </is>
-      </c>
-      <c r="R51" t="inlineStr">
-        <is>
-          <t>(1334.7568, 3050.7849, 4385.5417)</t>
-        </is>
-      </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>(1334.7568, 3049.7803, 4384.5371)</t>
-        </is>
-      </c>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr"/>
+      <c r="S51" t="inlineStr"/>
       <c r="T51" t="inlineStr">
         <is>
-          <t>(1338.748, 2933.7088, 4272.4568)</t>
-        </is>
-      </c>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>(284.1971, 4214.428, 4498.6251)</t>
-        </is>
-      </c>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>(2602.5256, 1879.0767, 4481.6023)</t>
-        </is>
-      </c>
-      <c r="W51" t="inlineStr">
-        <is>
-          <t>(1450.8287, 3049.8027, 4500.6313)</t>
-        </is>
-      </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>(2809.6692, 1689.96, 4499.6293)</t>
-        </is>
-      </c>
-      <c r="Y51" t="inlineStr">
-        <is>
-          <t>(1065.5966, 3434.0302, 4499.6268)</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>(3584.1372, 915.4897, 4499.6269)</t>
-        </is>
-      </c>
+          <t>(1193.6924, 3306.9415, 4500.6338)</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr"/>
+      <c r="V51" t="inlineStr"/>
+      <c r="W51" t="inlineStr"/>
+      <c r="X51" t="inlineStr"/>
+      <c r="Y51" t="inlineStr"/>
+      <c r="Z51" t="inlineStr"/>
       <c r="AA51" t="inlineStr"/>
       <c r="AB51" t="inlineStr"/>
+      <c r="AC51" t="inlineStr"/>
+      <c r="AD51" t="inlineStr"/>
+      <c r="AE51" t="inlineStr"/>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>(2936.7189, 1563.9136, 4500.6324)</t>
+        </is>
+      </c>
+      <c r="AG51" t="inlineStr"/>
+      <c r="AH51" t="inlineStr"/>
+      <c r="AI51" t="inlineStr"/>
+      <c r="AJ51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="8" t="inlineStr">
@@ -3685,74 +6437,46 @@
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>(1450.8287, 3047.798, 4498.6266)</t>
-        </is>
-      </c>
+      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>(2618.5485, 1880.0787, 4498.6272)</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>(1334.7568, 2936.6965, 4271.4533)</t>
-        </is>
-      </c>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>(3521.0687, 977.5575, 4498.6262)</t>
-        </is>
-      </c>
+      <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr">
-        <is>
-          <t>(3304.9368, 966.5161, 4271.4529)</t>
-        </is>
-      </c>
+      <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr"/>
       <c r="S52" t="inlineStr"/>
       <c r="T52" t="inlineStr">
         <is>
-          <t>(1334.7568, 2937.7007, 4272.4575)</t>
-        </is>
-      </c>
-      <c r="U52" t="inlineStr">
-        <is>
-          <t>(227.1757, 4271.4525, 4498.6282)</t>
-        </is>
-      </c>
+          <t>(1332.7517, 3167.8839, 4500.6356)</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr"/>
       <c r="V52" t="inlineStr"/>
-      <c r="W52" t="inlineStr">
-        <is>
-          <t>(1193.6919, 3306.9401, 4500.632)</t>
-        </is>
-      </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>(2935.7168, 1563.913, 4499.6298)</t>
-        </is>
-      </c>
-      <c r="Y52" t="inlineStr">
-        <is>
-          <t>(1450.8287, 3048.7996, 4499.6282)</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>(3306.9443, 1192.6841, 4499.6283)</t>
-        </is>
-      </c>
+      <c r="W52" t="inlineStr"/>
+      <c r="X52" t="inlineStr"/>
+      <c r="Y52" t="inlineStr"/>
+      <c r="Z52" t="inlineStr"/>
       <c r="AA52" t="inlineStr"/>
       <c r="AB52" t="inlineStr"/>
+      <c r="AC52" t="inlineStr"/>
+      <c r="AD52" t="inlineStr"/>
+      <c r="AE52" t="inlineStr"/>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>(2622.5634, 1878.0751, 4500.6384)</t>
+        </is>
+      </c>
+      <c r="AG52" t="inlineStr"/>
+      <c r="AH52" t="inlineStr"/>
+      <c r="AI52" t="inlineStr"/>
+      <c r="AJ52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
@@ -3763,66 +6487,38 @@
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>(1322.7335, 3175.8931, 4498.6267)</t>
-        </is>
-      </c>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>(2934.7147, 1563.913, 4498.6276)</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>(1337.7446, 2933.7088, 4271.4534)</t>
-        </is>
-      </c>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>(3649.1645, 849.4619, 4498.6265)</t>
-        </is>
-      </c>
+      <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr"/>
       <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr"/>
       <c r="S53" t="inlineStr"/>
       <c r="T53" t="inlineStr"/>
-      <c r="U53" t="inlineStr">
-        <is>
-          <t>(399.2242, 4099.404, 4498.6282)</t>
-        </is>
-      </c>
+      <c r="U53" t="inlineStr"/>
       <c r="V53" t="inlineStr"/>
-      <c r="W53" t="inlineStr">
-        <is>
-          <t>(1451.8325, 3048.7996, 4500.6321)</t>
-        </is>
-      </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>(2619.5513, 1880.0787, 4499.63)</t>
-        </is>
-      </c>
-      <c r="Y53" t="inlineStr">
-        <is>
-          <t>(1066.5993, 3433.0304, 4499.6297)</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>(3521.0687, 978.5605, 4499.6292)</t>
-        </is>
-      </c>
+      <c r="W53" t="inlineStr"/>
+      <c r="X53" t="inlineStr"/>
+      <c r="Y53" t="inlineStr"/>
+      <c r="Z53" t="inlineStr"/>
       <c r="AA53" t="inlineStr"/>
       <c r="AB53" t="inlineStr"/>
+      <c r="AC53" t="inlineStr"/>
+      <c r="AD53" t="inlineStr"/>
+      <c r="AE53" t="inlineStr"/>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="inlineStr"/>
+      <c r="AH53" t="inlineStr"/>
+      <c r="AI53" t="inlineStr"/>
+      <c r="AJ53" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
